--- a/indicator_update_map.xlsx
+++ b/indicator_update_map.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="680" windowWidth="34200" windowHeight="21460" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="680" windowWidth="34200" windowHeight="19660" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="📋 Все индикаторы" sheetId="1" state="visible" r:id="rId1"/>
@@ -21,7 +21,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="8">
+  <fonts count="9">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -62,15 +62,22 @@
       <sz val="10"/>
     </font>
     <font>
+      <name val="Calibri"/>
+      <family val="2"/>
       <b val="1"/>
-      <color rgb="00FFFFFF"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <family val="2"/>
       <sz val="10"/>
     </font>
     <font>
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="14">
+  <fills count="17">
     <fill>
       <patternFill/>
     </fill>
@@ -119,7 +126,22 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="004472C4"/>
+        <fgColor rgb="FF4472C4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
       </patternFill>
     </fill>
     <fill>
@@ -167,26 +189,6 @@
       <top style="thin">
         <color auto="1"/>
       </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
       <bottom style="thin">
         <color auto="1"/>
       </bottom>
@@ -205,11 +207,31 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="44">
+  <cellXfs count="56">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -283,41 +305,73 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="11" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="11" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="12" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="12" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="13" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="13" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="13" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="13" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="15" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="15" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="16" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="16" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="16" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="16" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
   </cellXfs>
@@ -685,29 +739,30 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M157"/>
+  <dimension ref="A1:M161"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
-    <col width="10" customWidth="1" style="26" min="1" max="1"/>
-    <col width="55" customWidth="1" style="26" min="2" max="2"/>
-    <col width="15" customWidth="1" style="26" min="3" max="3"/>
-    <col width="14" customWidth="1" style="26" min="4" max="4"/>
-    <col width="28" customWidth="1" style="26" min="5" max="5"/>
-    <col width="30" customWidth="1" style="26" min="6" max="6"/>
-    <col width="28" customWidth="1" style="26" min="7" max="8"/>
-    <col width="18" customWidth="1" style="26" min="9" max="9"/>
-    <col width="20" customWidth="1" style="26" min="10" max="10"/>
-    <col width="55" customWidth="1" style="26" min="11" max="11"/>
+    <col width="13.83203125" customWidth="1" style="41" min="1" max="1"/>
+    <col width="55" customWidth="1" style="41" min="2" max="2"/>
+    <col width="15" customWidth="1" style="41" min="3" max="3"/>
+    <col width="14" customWidth="1" style="41" min="4" max="4"/>
+    <col width="28" customWidth="1" style="41" min="5" max="5"/>
+    <col width="30" customWidth="1" style="41" min="6" max="6"/>
+    <col width="28" customWidth="1" style="41" min="7" max="8"/>
+    <col width="18" customWidth="1" style="41" min="9" max="9"/>
+    <col width="20" customWidth="1" style="41" min="10" max="10"/>
+    <col width="55" customWidth="1" style="41" min="11" max="11"/>
+    <col width="39.33203125" customWidth="1" style="41" min="12" max="12"/>
   </cols>
   <sheetData>
-    <row r="1" ht="22" customHeight="1" s="26">
-      <c r="A1" s="25" t="inlineStr">
+    <row r="1" ht="22" customHeight="1" s="41">
+      <c r="A1" s="38" t="inlineStr">
         <is>
           <t>🗺️ Карта обновления индикаторов | Realestate Dashboard | 25.05.2026</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="30" customHeight="1" s="26">
+    <row r="2" ht="30" customHeight="1" s="41">
       <c r="A2" s="1" t="inlineStr">
         <is>
           <t>Код</t>
@@ -748,12 +803,12 @@
           <t>Последняя точка</t>
         </is>
       </c>
-      <c r="I2" s="37" t="inlineStr">
+      <c r="I2" s="42" t="inlineStr">
         <is>
           <t>Актуальный период</t>
         </is>
       </c>
-      <c r="J2" s="37" t="inlineStr">
+      <c r="J2" s="42" t="inlineStr">
         <is>
           <t>Статус</t>
         </is>
@@ -769,7 +824,7 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="90" customHeight="1" s="26">
+    <row r="3" ht="90" customHeight="1" s="41">
       <c r="A3" s="2" t="inlineStr">
         <is>
           <t>1.1</t>
@@ -810,12 +865,12 @@
           <t>01.01.2025</t>
         </is>
       </c>
-      <c r="I3" s="38" t="inlineStr">
+      <c r="I3" s="48" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="J3" s="39" t="inlineStr">
+      <c r="J3" s="49" t="inlineStr">
         <is>
           <t>✅ Актуально</t>
         </is>
@@ -829,7 +884,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="30" customHeight="1" s="26">
+    <row r="4" ht="30" customHeight="1" s="41">
       <c r="A4" s="5" t="inlineStr">
         <is>
           <t>1.2</t>
@@ -870,12 +925,12 @@
           <t>01.10.2025</t>
         </is>
       </c>
-      <c r="I4" s="40" t="inlineStr">
+      <c r="I4" s="50" t="inlineStr">
         <is>
           <t>4 кв. 2025</t>
         </is>
       </c>
-      <c r="J4" s="41" t="inlineStr">
+      <c r="J4" s="51" t="inlineStr">
         <is>
           <t>⚠️ Просрочено</t>
         </is>
@@ -889,7 +944,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="75" customHeight="1" s="26">
+    <row r="5" ht="75" customHeight="1" s="41">
       <c r="A5" s="5" t="inlineStr">
         <is>
           <t>1.2.y</t>
@@ -930,12 +985,12 @@
           <t>01.01.2024</t>
         </is>
       </c>
-      <c r="I5" s="40" t="inlineStr">
+      <c r="I5" s="50" t="inlineStr">
         <is>
           <t>2024</t>
         </is>
       </c>
-      <c r="J5" s="41" t="inlineStr">
+      <c r="J5" s="51" t="inlineStr">
         <is>
           <t>⚠️ Просрочено</t>
         </is>
@@ -949,7 +1004,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="30" customHeight="1" s="26">
+    <row r="6" ht="30" customHeight="1" s="41">
       <c r="A6" s="5" t="inlineStr">
         <is>
           <t>1.3</t>
@@ -990,12 +1045,12 @@
           <t>01.10.2025</t>
         </is>
       </c>
-      <c r="I6" s="40" t="inlineStr">
+      <c r="I6" s="50" t="inlineStr">
         <is>
           <t>4 кв. 2025</t>
         </is>
       </c>
-      <c r="J6" s="41" t="inlineStr">
+      <c r="J6" s="51" t="inlineStr">
         <is>
           <t>⚠️ Просрочено</t>
         </is>
@@ -1009,7 +1064,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="75" customHeight="1" s="26">
+    <row r="7" ht="75" customHeight="1" s="41">
       <c r="A7" s="2" t="inlineStr">
         <is>
           <t>1.3.y</t>
@@ -1050,12 +1105,12 @@
           <t>01.01.2025</t>
         </is>
       </c>
-      <c r="I7" s="38" t="inlineStr">
+      <c r="I7" s="48" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="J7" s="39" t="inlineStr">
+      <c r="J7" s="49" t="inlineStr">
         <is>
           <t>✅ Актуально</t>
         </is>
@@ -1069,7 +1124,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="75" customHeight="1" s="26">
+    <row r="8" ht="75" customHeight="1" s="41">
       <c r="A8" s="5" t="inlineStr">
         <is>
           <t>2.1</t>
@@ -1110,12 +1165,12 @@
           <t>01.04.2026</t>
         </is>
       </c>
-      <c r="I8" s="38" t="inlineStr">
+      <c r="I8" s="48" t="inlineStr">
         <is>
           <t>апрель 2026</t>
         </is>
       </c>
-      <c r="J8" s="39" t="inlineStr">
+      <c r="J8" s="49" t="inlineStr">
         <is>
           <t>✅ Актуально</t>
         </is>
@@ -1129,7 +1184,7 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="75" customHeight="1" s="26">
+    <row r="9" ht="75" customHeight="1" s="41">
       <c r="A9" s="5" t="inlineStr">
         <is>
           <t>2.2</t>
@@ -1170,12 +1225,12 @@
           <t>01.04.2026</t>
         </is>
       </c>
-      <c r="I9" s="38" t="inlineStr">
+      <c r="I9" s="48" t="inlineStr">
         <is>
           <t>апрель 2026</t>
         </is>
       </c>
-      <c r="J9" s="39" t="inlineStr">
+      <c r="J9" s="49" t="inlineStr">
         <is>
           <t>✅ Актуально</t>
         </is>
@@ -1189,7 +1244,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="75" customHeight="1" s="26">
+    <row r="10" ht="75" customHeight="1" s="41">
       <c r="A10" s="5" t="inlineStr">
         <is>
           <t>2.3</t>
@@ -1230,12 +1285,12 @@
           <t>01.04.2026</t>
         </is>
       </c>
-      <c r="I10" s="38" t="inlineStr">
+      <c r="I10" s="48" t="inlineStr">
         <is>
           <t>апрель 2026</t>
         </is>
       </c>
-      <c r="J10" s="39" t="inlineStr">
+      <c r="J10" s="49" t="inlineStr">
         <is>
           <t>✅ Актуально</t>
         </is>
@@ -1249,7 +1304,7 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="90" customHeight="1" s="26">
+    <row r="11" ht="90" customHeight="1" s="41">
       <c r="A11" s="2" t="inlineStr">
         <is>
           <t>2.6</t>
@@ -1290,12 +1345,12 @@
           <t>01.12.2025</t>
         </is>
       </c>
-      <c r="I11" s="40" t="inlineStr">
+      <c r="I11" s="50" t="inlineStr">
         <is>
           <t>декабрь 2025</t>
         </is>
       </c>
-      <c r="J11" s="41" t="inlineStr">
+      <c r="J11" s="51" t="inlineStr">
         <is>
           <t>⚠️ Просрочено</t>
         </is>
@@ -1309,7 +1364,7 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="90" customHeight="1" s="26">
+    <row r="12" ht="90" customHeight="1" s="41">
       <c r="A12" s="2" t="inlineStr">
         <is>
           <t>2.7</t>
@@ -1350,12 +1405,12 @@
           <t>01.12.2025</t>
         </is>
       </c>
-      <c r="I12" s="40" t="inlineStr">
+      <c r="I12" s="50" t="inlineStr">
         <is>
           <t>декабрь 2025</t>
         </is>
       </c>
-      <c r="J12" s="41" t="inlineStr">
+      <c r="J12" s="51" t="inlineStr">
         <is>
           <t>⚠️ Просрочено</t>
         </is>
@@ -1369,7 +1424,7 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="90" customHeight="1" s="26">
+    <row r="13" ht="90" customHeight="1" s="41">
       <c r="A13" s="2" t="inlineStr">
         <is>
           <t>2.8</t>
@@ -1410,12 +1465,12 @@
           <t>01.12.2025</t>
         </is>
       </c>
-      <c r="I13" s="40" t="inlineStr">
+      <c r="I13" s="50" t="inlineStr">
         <is>
           <t>декабрь 2025</t>
         </is>
       </c>
-      <c r="J13" s="41" t="inlineStr">
+      <c r="J13" s="51" t="inlineStr">
         <is>
           <t>⚠️ Просрочено</t>
         </is>
@@ -1429,7 +1484,7 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="75" customHeight="1" s="26">
+    <row r="14" ht="75" customHeight="1" s="41">
       <c r="A14" s="5" t="inlineStr">
         <is>
           <t>2.9</t>
@@ -1470,12 +1525,12 @@
           <t>01.01.2025</t>
         </is>
       </c>
-      <c r="I14" s="38" t="inlineStr">
+      <c r="I14" s="48" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="J14" s="39" t="inlineStr">
+      <c r="J14" s="49" t="inlineStr">
         <is>
           <t>✅ Актуально</t>
         </is>
@@ -1489,7 +1544,7 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="75" customHeight="1" s="26">
+    <row r="15" ht="75" customHeight="1" s="41">
       <c r="A15" s="2" t="inlineStr">
         <is>
           <t>2.10</t>
@@ -1530,12 +1585,12 @@
           <t>01.01.2024</t>
         </is>
       </c>
-      <c r="I15" s="38" t="inlineStr">
+      <c r="I15" s="48" t="inlineStr">
         <is>
           <t>2024</t>
         </is>
       </c>
-      <c r="J15" s="39" t="inlineStr">
+      <c r="J15" s="49" t="inlineStr">
         <is>
           <t>✅ Актуально</t>
         </is>
@@ -1549,7 +1604,7 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="75" customHeight="1" s="26">
+    <row r="16" ht="75" customHeight="1" s="41">
       <c r="A16" s="5" t="inlineStr">
         <is>
           <t>2.11</t>
@@ -1590,12 +1645,12 @@
           <t>01.01.2025</t>
         </is>
       </c>
-      <c r="I16" s="38" t="inlineStr">
+      <c r="I16" s="48" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="J16" s="39" t="inlineStr">
+      <c r="J16" s="49" t="inlineStr">
         <is>
           <t>✅ Актуально</t>
         </is>
@@ -1609,7 +1664,7 @@
         </is>
       </c>
     </row>
-    <row r="17" ht="75" customHeight="1" s="26">
+    <row r="17" ht="75" customHeight="1" s="41">
       <c r="A17" s="5" t="inlineStr">
         <is>
           <t>2.12</t>
@@ -1650,12 +1705,12 @@
           <t>01.01.2025</t>
         </is>
       </c>
-      <c r="I17" s="38" t="inlineStr">
+      <c r="I17" s="48" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="J17" s="39" t="inlineStr">
+      <c r="J17" s="49" t="inlineStr">
         <is>
           <t>✅ Актуально</t>
         </is>
@@ -1669,7 +1724,7 @@
         </is>
       </c>
     </row>
-    <row r="18" ht="75" customHeight="1" s="26">
+    <row r="18" ht="75" customHeight="1" s="41">
       <c r="A18" s="5" t="inlineStr">
         <is>
           <t>2.13</t>
@@ -1710,12 +1765,12 @@
           <t>01.01.2025</t>
         </is>
       </c>
-      <c r="I18" s="38" t="inlineStr">
+      <c r="I18" s="48" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="J18" s="39" t="inlineStr">
+      <c r="J18" s="49" t="inlineStr">
         <is>
           <t>✅ Актуально</t>
         </is>
@@ -1770,12 +1825,12 @@
           <t>01.01.2015</t>
         </is>
       </c>
-      <c r="I19" s="42" t="inlineStr">
+      <c r="I19" s="52" t="inlineStr">
         <is>
           <t>2015</t>
         </is>
       </c>
-      <c r="J19" s="43" t="inlineStr">
+      <c r="J19" s="53" t="inlineStr">
         <is>
           <t>⛔ Отключён</t>
         </is>
@@ -1789,7 +1844,7 @@
         </is>
       </c>
     </row>
-    <row r="20" ht="75" customHeight="1" s="26">
+    <row r="20" ht="75" customHeight="1" s="41">
       <c r="A20" s="5" t="inlineStr">
         <is>
           <t>3.1</t>
@@ -1830,12 +1885,12 @@
           <t>01.05.2026</t>
         </is>
       </c>
-      <c r="I20" s="38" t="inlineStr">
+      <c r="I20" s="48" t="inlineStr">
         <is>
           <t>май 2026</t>
         </is>
       </c>
-      <c r="J20" s="39" t="inlineStr">
+      <c r="J20" s="49" t="inlineStr">
         <is>
           <t>✅ Актуально</t>
         </is>
@@ -1849,7 +1904,7 @@
         </is>
       </c>
     </row>
-    <row r="21" ht="75" customHeight="1" s="26">
+    <row r="21" ht="75" customHeight="1" s="41">
       <c r="A21" s="5" t="inlineStr">
         <is>
           <t>3.2</t>
@@ -1890,12 +1945,12 @@
           <t>01.05.2026</t>
         </is>
       </c>
-      <c r="I21" s="38" t="inlineStr">
+      <c r="I21" s="48" t="inlineStr">
         <is>
           <t>май 2026</t>
         </is>
       </c>
-      <c r="J21" s="39" t="inlineStr">
+      <c r="J21" s="49" t="inlineStr">
         <is>
           <t>✅ Актуально</t>
         </is>
@@ -1909,7 +1964,7 @@
         </is>
       </c>
     </row>
-    <row r="22" ht="75" customHeight="1" s="26">
+    <row r="22" ht="75" customHeight="1" s="41">
       <c r="A22" s="5" t="inlineStr">
         <is>
           <t>3.3</t>
@@ -1950,12 +2005,12 @@
           <t>01.05.2026</t>
         </is>
       </c>
-      <c r="I22" s="38" t="inlineStr">
+      <c r="I22" s="48" t="inlineStr">
         <is>
           <t>май 2026</t>
         </is>
       </c>
-      <c r="J22" s="39" t="inlineStr">
+      <c r="J22" s="49" t="inlineStr">
         <is>
           <t>✅ Актуально</t>
         </is>
@@ -1969,7 +2024,7 @@
         </is>
       </c>
     </row>
-    <row r="23" ht="75" customHeight="1" s="26">
+    <row r="23" ht="75" customHeight="1" s="41">
       <c r="A23" s="5" t="inlineStr">
         <is>
           <t>3.4</t>
@@ -2010,12 +2065,12 @@
           <t>01.05.2026</t>
         </is>
       </c>
-      <c r="I23" s="38" t="inlineStr">
+      <c r="I23" s="48" t="inlineStr">
         <is>
           <t>май 2026</t>
         </is>
       </c>
-      <c r="J23" s="39" t="inlineStr">
+      <c r="J23" s="49" t="inlineStr">
         <is>
           <t>✅ Актуально</t>
         </is>
@@ -2029,7 +2084,7 @@
         </is>
       </c>
     </row>
-    <row r="24" ht="90" customHeight="1" s="26">
+    <row r="24" ht="90" customHeight="1" s="41">
       <c r="A24" s="2" t="inlineStr">
         <is>
           <t>3.5</t>
@@ -2070,12 +2125,12 @@
           <t>01.05.2026</t>
         </is>
       </c>
-      <c r="I24" s="38" t="inlineStr">
+      <c r="I24" s="48" t="inlineStr">
         <is>
           <t>май 2026</t>
         </is>
       </c>
-      <c r="J24" s="39" t="inlineStr">
+      <c r="J24" s="49" t="inlineStr">
         <is>
           <t>✅ Актуально</t>
         </is>
@@ -2089,7 +2144,7 @@
         </is>
       </c>
     </row>
-    <row r="25" ht="75" customHeight="1" s="26">
+    <row r="25" ht="75" customHeight="1" s="41">
       <c r="A25" s="8" t="inlineStr">
         <is>
           <t>3.6</t>
@@ -2130,12 +2185,12 @@
           <t>01.05.2026</t>
         </is>
       </c>
-      <c r="I25" s="38" t="inlineStr">
+      <c r="I25" s="48" t="inlineStr">
         <is>
           <t>май 2026</t>
         </is>
       </c>
-      <c r="J25" s="39" t="inlineStr">
+      <c r="J25" s="49" t="inlineStr">
         <is>
           <t>✅ Актуально</t>
         </is>
@@ -2149,7 +2204,7 @@
         </is>
       </c>
     </row>
-    <row r="26" ht="75" customHeight="1" s="26">
+    <row r="26" ht="75" customHeight="1" s="41">
       <c r="A26" s="2" t="inlineStr">
         <is>
           <t>3.7</t>
@@ -2190,12 +2245,12 @@
           <t>01.01.2024</t>
         </is>
       </c>
-      <c r="I26" s="40" t="inlineStr">
+      <c r="I26" s="50" t="inlineStr">
         <is>
           <t>2024</t>
         </is>
       </c>
-      <c r="J26" s="41" t="inlineStr">
+      <c r="J26" s="51" t="inlineStr">
         <is>
           <t>⚠️ Просрочено</t>
         </is>
@@ -2209,7 +2264,7 @@
         </is>
       </c>
     </row>
-    <row r="27" ht="75" customHeight="1" s="26">
+    <row r="27" ht="75" customHeight="1" s="41">
       <c r="A27" s="5" t="inlineStr">
         <is>
           <t>3.17</t>
@@ -2250,12 +2305,12 @@
           <t>01.05.2026</t>
         </is>
       </c>
-      <c r="I27" s="38" t="inlineStr">
+      <c r="I27" s="48" t="inlineStr">
         <is>
           <t>май 2026</t>
         </is>
       </c>
-      <c r="J27" s="39" t="inlineStr">
+      <c r="J27" s="49" t="inlineStr">
         <is>
           <t>✅ Актуально</t>
         </is>
@@ -2269,7 +2324,7 @@
         </is>
       </c>
     </row>
-    <row r="28" ht="75" customHeight="1" s="26">
+    <row r="28" ht="75" customHeight="1" s="41">
       <c r="A28" s="5" t="inlineStr">
         <is>
           <t>3.18</t>
@@ -2310,12 +2365,12 @@
           <t>01.05.2026</t>
         </is>
       </c>
-      <c r="I28" s="38" t="inlineStr">
+      <c r="I28" s="48" t="inlineStr">
         <is>
           <t>май 2026</t>
         </is>
       </c>
-      <c r="J28" s="39" t="inlineStr">
+      <c r="J28" s="49" t="inlineStr">
         <is>
           <t>✅ Актуально</t>
         </is>
@@ -2329,7 +2384,7 @@
         </is>
       </c>
     </row>
-    <row r="29" ht="75" customHeight="1" s="26">
+    <row r="29" ht="75" customHeight="1" s="41">
       <c r="A29" s="5" t="inlineStr">
         <is>
           <t>3.19</t>
@@ -2370,12 +2425,12 @@
           <t>01.05.2026</t>
         </is>
       </c>
-      <c r="I29" s="38" t="inlineStr">
+      <c r="I29" s="48" t="inlineStr">
         <is>
           <t>май 2026</t>
         </is>
       </c>
-      <c r="J29" s="39" t="inlineStr">
+      <c r="J29" s="49" t="inlineStr">
         <is>
           <t>✅ Актуально</t>
         </is>
@@ -2389,7 +2444,7 @@
         </is>
       </c>
     </row>
-    <row r="30" ht="75" customHeight="1" s="26">
+    <row r="30" ht="75" customHeight="1" s="41">
       <c r="A30" s="8" t="inlineStr">
         <is>
           <t>4.1</t>
@@ -2430,12 +2485,12 @@
           <t>01.04.2026</t>
         </is>
       </c>
-      <c r="I30" s="38" t="inlineStr">
+      <c r="I30" s="48" t="inlineStr">
         <is>
           <t>апрель 2026</t>
         </is>
       </c>
-      <c r="J30" s="39" t="inlineStr">
+      <c r="J30" s="49" t="inlineStr">
         <is>
           <t>✅ Актуально</t>
         </is>
@@ -2490,12 +2545,12 @@
           <t>01.01.2026</t>
         </is>
       </c>
-      <c r="I31" s="38" t="inlineStr">
+      <c r="I31" s="48" t="inlineStr">
         <is>
           <t>1 кв. 2026</t>
         </is>
       </c>
-      <c r="J31" s="39" t="inlineStr">
+      <c r="J31" s="49" t="inlineStr">
         <is>
           <t>✅ Актуально</t>
         </is>
@@ -2509,7 +2564,7 @@
         </is>
       </c>
     </row>
-    <row r="32" ht="30" customHeight="1" s="26">
+    <row r="32" ht="30" customHeight="1" s="41">
       <c r="A32" s="5" t="inlineStr">
         <is>
           <t>4.4.1</t>
@@ -2550,12 +2605,12 @@
           <t>01.01.2026</t>
         </is>
       </c>
-      <c r="I32" s="38" t="inlineStr">
+      <c r="I32" s="48" t="inlineStr">
         <is>
           <t>1 кв. 2026</t>
         </is>
       </c>
-      <c r="J32" s="39" t="inlineStr">
+      <c r="J32" s="49" t="inlineStr">
         <is>
           <t>✅ Актуально</t>
         </is>
@@ -2569,7 +2624,7 @@
         </is>
       </c>
     </row>
-    <row r="33" ht="30" customHeight="1" s="26">
+    <row r="33" ht="30" customHeight="1" s="41">
       <c r="A33" s="5" t="inlineStr">
         <is>
           <t>4.4.2</t>
@@ -2610,12 +2665,12 @@
           <t>01.01.2026</t>
         </is>
       </c>
-      <c r="I33" s="38" t="inlineStr">
+      <c r="I33" s="48" t="inlineStr">
         <is>
           <t>1 кв. 2026</t>
         </is>
       </c>
-      <c r="J33" s="39" t="inlineStr">
+      <c r="J33" s="49" t="inlineStr">
         <is>
           <t>✅ Актуально</t>
         </is>
@@ -2670,12 +2725,12 @@
           <t>01.01.2026</t>
         </is>
       </c>
-      <c r="I34" s="38" t="inlineStr">
+      <c r="I34" s="48" t="inlineStr">
         <is>
           <t>1 кв. 2026</t>
         </is>
       </c>
-      <c r="J34" s="39" t="inlineStr">
+      <c r="J34" s="49" t="inlineStr">
         <is>
           <t>✅ Актуально</t>
         </is>
@@ -2730,12 +2785,12 @@
           <t>01.01.2026</t>
         </is>
       </c>
-      <c r="I35" s="38" t="inlineStr">
+      <c r="I35" s="48" t="inlineStr">
         <is>
           <t>1 кв. 2026</t>
         </is>
       </c>
-      <c r="J35" s="39" t="inlineStr">
+      <c r="J35" s="49" t="inlineStr">
         <is>
           <t>✅ Актуально</t>
         </is>
@@ -2749,7 +2804,7 @@
         </is>
       </c>
     </row>
-    <row r="36" ht="30" customHeight="1" s="26">
+    <row r="36" ht="30" customHeight="1" s="41">
       <c r="A36" s="5" t="inlineStr">
         <is>
           <t>4.5.1</t>
@@ -2790,12 +2845,12 @@
           <t>01.01.2026</t>
         </is>
       </c>
-      <c r="I36" s="38" t="inlineStr">
+      <c r="I36" s="48" t="inlineStr">
         <is>
           <t>1 кв. 2026</t>
         </is>
       </c>
-      <c r="J36" s="39" t="inlineStr">
+      <c r="J36" s="49" t="inlineStr">
         <is>
           <t>✅ Актуально</t>
         </is>
@@ -2809,7 +2864,7 @@
         </is>
       </c>
     </row>
-    <row r="37" ht="30" customHeight="1" s="26">
+    <row r="37" ht="30" customHeight="1" s="41">
       <c r="A37" s="5" t="inlineStr">
         <is>
           <t>4.5.2</t>
@@ -2850,12 +2905,12 @@
           <t>01.01.2026</t>
         </is>
       </c>
-      <c r="I37" s="38" t="inlineStr">
+      <c r="I37" s="48" t="inlineStr">
         <is>
           <t>1 кв. 2026</t>
         </is>
       </c>
-      <c r="J37" s="39" t="inlineStr">
+      <c r="J37" s="49" t="inlineStr">
         <is>
           <t>✅ Актуально</t>
         </is>
@@ -2869,7 +2924,7 @@
         </is>
       </c>
     </row>
-    <row r="38" ht="30" customHeight="1" s="26">
+    <row r="38" ht="30" customHeight="1" s="41">
       <c r="A38" s="5" t="inlineStr">
         <is>
           <t>4.5.3</t>
@@ -2910,12 +2965,12 @@
           <t>01.01.2026</t>
         </is>
       </c>
-      <c r="I38" s="38" t="inlineStr">
+      <c r="I38" s="48" t="inlineStr">
         <is>
           <t>1 кв. 2026</t>
         </is>
       </c>
-      <c r="J38" s="39" t="inlineStr">
+      <c r="J38" s="49" t="inlineStr">
         <is>
           <t>✅ Актуально</t>
         </is>
@@ -2970,12 +3025,12 @@
           <t>01.01.2026</t>
         </is>
       </c>
-      <c r="I39" s="38" t="inlineStr">
+      <c r="I39" s="48" t="inlineStr">
         <is>
           <t>1 кв. 2026</t>
         </is>
       </c>
-      <c r="J39" s="39" t="inlineStr">
+      <c r="J39" s="49" t="inlineStr">
         <is>
           <t>✅ Актуально</t>
         </is>
@@ -2989,7 +3044,7 @@
         </is>
       </c>
     </row>
-    <row r="40" ht="75" customHeight="1" s="26">
+    <row r="40" ht="75" customHeight="1" s="41">
       <c r="A40" s="8" t="inlineStr">
         <is>
           <t>4.8</t>
@@ -3030,12 +3085,12 @@
           <t>01.04.2026</t>
         </is>
       </c>
-      <c r="I40" s="38" t="inlineStr">
+      <c r="I40" s="48" t="inlineStr">
         <is>
           <t>апрель 2026</t>
         </is>
       </c>
-      <c r="J40" s="39" t="inlineStr">
+      <c r="J40" s="49" t="inlineStr">
         <is>
           <t>✅ Актуально</t>
         </is>
@@ -3049,7 +3104,7 @@
         </is>
       </c>
     </row>
-    <row r="41" ht="75" customHeight="1" s="26">
+    <row r="41" ht="75" customHeight="1" s="41">
       <c r="A41" s="8" t="inlineStr">
         <is>
           <t>4.9</t>
@@ -3090,12 +3145,12 @@
           <t>01.04.2026</t>
         </is>
       </c>
-      <c r="I41" s="38" t="inlineStr">
+      <c r="I41" s="48" t="inlineStr">
         <is>
           <t>апрель 2026</t>
         </is>
       </c>
-      <c r="J41" s="39" t="inlineStr">
+      <c r="J41" s="49" t="inlineStr">
         <is>
           <t>✅ Актуально</t>
         </is>
@@ -3150,12 +3205,12 @@
           <t>01.01.2026</t>
         </is>
       </c>
-      <c r="I42" s="38" t="inlineStr">
+      <c r="I42" s="48" t="inlineStr">
         <is>
           <t>1 кв. 2026</t>
         </is>
       </c>
-      <c r="J42" s="39" t="inlineStr">
+      <c r="J42" s="49" t="inlineStr">
         <is>
           <t>✅ Актуально</t>
         </is>
@@ -3169,7 +3224,7 @@
         </is>
       </c>
     </row>
-    <row r="43" ht="75" customHeight="1" s="26">
+    <row r="43" ht="75" customHeight="1" s="41">
       <c r="A43" s="2" t="inlineStr">
         <is>
           <t>5.3</t>
@@ -3210,12 +3265,12 @@
           <t>01.01.2024</t>
         </is>
       </c>
-      <c r="I43" s="40" t="inlineStr">
+      <c r="I43" s="50" t="inlineStr">
         <is>
           <t>2024</t>
         </is>
       </c>
-      <c r="J43" s="41" t="inlineStr">
+      <c r="J43" s="51" t="inlineStr">
         <is>
           <t>⚠️ Просрочено</t>
         </is>
@@ -3229,7 +3284,7 @@
         </is>
       </c>
     </row>
-    <row r="44" ht="75" customHeight="1" s="26">
+    <row r="44" ht="75" customHeight="1" s="41">
       <c r="A44" s="8" t="inlineStr">
         <is>
           <t>5.8</t>
@@ -3270,12 +3325,12 @@
           <t>01.04.2026</t>
         </is>
       </c>
-      <c r="I44" s="38" t="inlineStr">
+      <c r="I44" s="48" t="inlineStr">
         <is>
           <t>апрель 2026</t>
         </is>
       </c>
-      <c r="J44" s="39" t="inlineStr">
+      <c r="J44" s="49" t="inlineStr">
         <is>
           <t>✅ Актуально</t>
         </is>
@@ -3289,7 +3344,7 @@
         </is>
       </c>
     </row>
-    <row r="45" ht="90" customHeight="1" s="26">
+    <row r="45" ht="90" customHeight="1" s="41">
       <c r="A45" s="2" t="inlineStr">
         <is>
           <t>5.9</t>
@@ -3330,12 +3385,12 @@
           <t>01.04.2026</t>
         </is>
       </c>
-      <c r="I45" s="38" t="inlineStr">
+      <c r="I45" s="48" t="inlineStr">
         <is>
           <t>апрель 2026</t>
         </is>
       </c>
-      <c r="J45" s="39" t="inlineStr">
+      <c r="J45" s="49" t="inlineStr">
         <is>
           <t>✅ Актуально</t>
         </is>
@@ -3349,7 +3404,7 @@
         </is>
       </c>
     </row>
-    <row r="46" ht="90" customHeight="1" s="26">
+    <row r="46" ht="90" customHeight="1" s="41">
       <c r="A46" s="2" t="inlineStr">
         <is>
           <t>5.9.ma12</t>
@@ -3390,12 +3445,12 @@
           <t>01.04.2026</t>
         </is>
       </c>
-      <c r="I46" s="38" t="inlineStr">
+      <c r="I46" s="48" t="inlineStr">
         <is>
           <t>апрель 2026</t>
         </is>
       </c>
-      <c r="J46" s="39" t="inlineStr">
+      <c r="J46" s="49" t="inlineStr">
         <is>
           <t>✅ Актуально</t>
         </is>
@@ -3409,7 +3464,7 @@
         </is>
       </c>
     </row>
-    <row r="47" ht="90" customHeight="1" s="26">
+    <row r="47" ht="90" customHeight="1" s="41">
       <c r="A47" s="2" t="inlineStr">
         <is>
           <t>5.10</t>
@@ -3450,12 +3505,12 @@
           <t>01.10.2025</t>
         </is>
       </c>
-      <c r="I47" s="40" t="inlineStr">
+      <c r="I47" s="50" t="inlineStr">
         <is>
           <t>4 кв. 2025</t>
         </is>
       </c>
-      <c r="J47" s="41" t="inlineStr">
+      <c r="J47" s="51" t="inlineStr">
         <is>
           <t>⚠️ Просрочено</t>
         </is>
@@ -3469,7 +3524,7 @@
         </is>
       </c>
     </row>
-    <row r="48" ht="90" customHeight="1" s="26">
+    <row r="48" ht="90" customHeight="1" s="41">
       <c r="A48" s="2" t="inlineStr">
         <is>
           <t>5.11</t>
@@ -3510,12 +3565,12 @@
           <t>01.10.2025</t>
         </is>
       </c>
-      <c r="I48" s="40" t="inlineStr">
+      <c r="I48" s="50" t="inlineStr">
         <is>
           <t>4 кв. 2025</t>
         </is>
       </c>
-      <c r="J48" s="41" t="inlineStr">
+      <c r="J48" s="51" t="inlineStr">
         <is>
           <t>⚠️ Просрочено</t>
         </is>
@@ -3529,7 +3584,7 @@
         </is>
       </c>
     </row>
-    <row r="49" ht="75" customHeight="1" s="26">
+    <row r="49" ht="75" customHeight="1" s="41">
       <c r="A49" s="2" t="inlineStr">
         <is>
           <t>5.12.33</t>
@@ -3570,12 +3625,12 @@
           <t>01.01.2024</t>
         </is>
       </c>
-      <c r="I49" s="38" t="inlineStr">
+      <c r="I49" s="48" t="inlineStr">
         <is>
           <t>2024</t>
         </is>
       </c>
-      <c r="J49" s="39" t="inlineStr">
+      <c r="J49" s="49" t="inlineStr">
         <is>
           <t>✅ Актуально</t>
         </is>
@@ -3589,7 +3644,7 @@
         </is>
       </c>
     </row>
-    <row r="50" ht="75" customHeight="1" s="26">
+    <row r="50" ht="75" customHeight="1" s="41">
       <c r="A50" s="2" t="inlineStr">
         <is>
           <t>5.12.38</t>
@@ -3630,12 +3685,12 @@
           <t>01.01.2024</t>
         </is>
       </c>
-      <c r="I50" s="38" t="inlineStr">
+      <c r="I50" s="48" t="inlineStr">
         <is>
           <t>2024</t>
         </is>
       </c>
-      <c r="J50" s="39" t="inlineStr">
+      <c r="J50" s="49" t="inlineStr">
         <is>
           <t>✅ Актуально</t>
         </is>
@@ -3649,7 +3704,7 @@
         </is>
       </c>
     </row>
-    <row r="51" ht="75" customHeight="1" s="26">
+    <row r="51" ht="75" customHeight="1" s="41">
       <c r="A51" s="2" t="inlineStr">
         <is>
           <t>5.13.33</t>
@@ -3690,12 +3745,12 @@
           <t>01.01.2024</t>
         </is>
       </c>
-      <c r="I51" s="38" t="inlineStr">
+      <c r="I51" s="48" t="inlineStr">
         <is>
           <t>2024</t>
         </is>
       </c>
-      <c r="J51" s="39" t="inlineStr">
+      <c r="J51" s="49" t="inlineStr">
         <is>
           <t>✅ Актуально</t>
         </is>
@@ -3709,7 +3764,7 @@
         </is>
       </c>
     </row>
-    <row r="52" ht="75" customHeight="1" s="26">
+    <row r="52" ht="75" customHeight="1" s="41">
       <c r="A52" s="2" t="inlineStr">
         <is>
           <t>5.13.38</t>
@@ -3750,12 +3805,12 @@
           <t>01.01.2024</t>
         </is>
       </c>
-      <c r="I52" s="38" t="inlineStr">
+      <c r="I52" s="48" t="inlineStr">
         <is>
           <t>2024</t>
         </is>
       </c>
-      <c r="J52" s="39" t="inlineStr">
+      <c r="J52" s="49" t="inlineStr">
         <is>
           <t>✅ Актуально</t>
         </is>
@@ -3769,7 +3824,7 @@
         </is>
       </c>
     </row>
-    <row r="53" ht="75" customHeight="1" s="26">
+    <row r="53" ht="75" customHeight="1" s="41">
       <c r="A53" s="2" t="inlineStr">
         <is>
           <t>5.14.33</t>
@@ -3810,12 +3865,12 @@
           <t>01.01.2024</t>
         </is>
       </c>
-      <c r="I53" s="38" t="inlineStr">
+      <c r="I53" s="48" t="inlineStr">
         <is>
           <t>2024</t>
         </is>
       </c>
-      <c r="J53" s="39" t="inlineStr">
+      <c r="J53" s="49" t="inlineStr">
         <is>
           <t>✅ Актуально</t>
         </is>
@@ -3829,7 +3884,7 @@
         </is>
       </c>
     </row>
-    <row r="54" ht="75" customHeight="1" s="26">
+    <row r="54" ht="75" customHeight="1" s="41">
       <c r="A54" s="2" t="inlineStr">
         <is>
           <t>5.14.38</t>
@@ -3870,12 +3925,12 @@
           <t>01.01.2024</t>
         </is>
       </c>
-      <c r="I54" s="38" t="inlineStr">
+      <c r="I54" s="48" t="inlineStr">
         <is>
           <t>2024</t>
         </is>
       </c>
-      <c r="J54" s="39" t="inlineStr">
+      <c r="J54" s="49" t="inlineStr">
         <is>
           <t>✅ Актуально</t>
         </is>
@@ -3889,7 +3944,7 @@
         </is>
       </c>
     </row>
-    <row r="55" ht="75" customHeight="1" s="26">
+    <row r="55" ht="75" customHeight="1" s="41">
       <c r="A55" s="2" t="inlineStr">
         <is>
           <t>5.15.33</t>
@@ -3930,12 +3985,12 @@
           <t>01.01.2024</t>
         </is>
       </c>
-      <c r="I55" s="38" t="inlineStr">
+      <c r="I55" s="48" t="inlineStr">
         <is>
           <t>2024</t>
         </is>
       </c>
-      <c r="J55" s="39" t="inlineStr">
+      <c r="J55" s="49" t="inlineStr">
         <is>
           <t>✅ Актуально</t>
         </is>
@@ -3949,7 +4004,7 @@
         </is>
       </c>
     </row>
-    <row r="56" ht="75" customHeight="1" s="26">
+    <row r="56" ht="75" customHeight="1" s="41">
       <c r="A56" s="2" t="inlineStr">
         <is>
           <t>5.15.38</t>
@@ -3990,12 +4045,12 @@
           <t>01.01.2024</t>
         </is>
       </c>
-      <c r="I56" s="38" t="inlineStr">
+      <c r="I56" s="48" t="inlineStr">
         <is>
           <t>2024</t>
         </is>
       </c>
-      <c r="J56" s="39" t="inlineStr">
+      <c r="J56" s="49" t="inlineStr">
         <is>
           <t>✅ Актуально</t>
         </is>
@@ -4009,7 +4064,7 @@
         </is>
       </c>
     </row>
-    <row r="57" ht="75" customHeight="1" s="26">
+    <row r="57" ht="75" customHeight="1" s="41">
       <c r="A57" s="8" t="inlineStr">
         <is>
           <t>5.20</t>
@@ -4050,12 +4105,12 @@
           <t>01.04.2026</t>
         </is>
       </c>
-      <c r="I57" s="38" t="inlineStr">
+      <c r="I57" s="48" t="inlineStr">
         <is>
           <t>апрель 2026</t>
         </is>
       </c>
-      <c r="J57" s="39" t="inlineStr">
+      <c r="J57" s="49" t="inlineStr">
         <is>
           <t>✅ Актуально</t>
         </is>
@@ -4069,7 +4124,7 @@
         </is>
       </c>
     </row>
-    <row r="58" ht="75" customHeight="1" s="26">
+    <row r="58" ht="75" customHeight="1" s="41">
       <c r="A58" s="8" t="inlineStr">
         <is>
           <t>5.21</t>
@@ -4110,12 +4165,12 @@
           <t>01.04.2026</t>
         </is>
       </c>
-      <c r="I58" s="38" t="inlineStr">
+      <c r="I58" s="48" t="inlineStr">
         <is>
           <t>апрель 2026</t>
         </is>
       </c>
-      <c r="J58" s="39" t="inlineStr">
+      <c r="J58" s="49" t="inlineStr">
         <is>
           <t>✅ Актуально</t>
         </is>
@@ -4129,7 +4184,7 @@
         </is>
       </c>
     </row>
-    <row r="59" ht="90" customHeight="1" s="26">
+    <row r="59" ht="90" customHeight="1" s="41">
       <c r="A59" s="2" t="inlineStr">
         <is>
           <t>5.22</t>
@@ -4170,12 +4225,12 @@
           <t>01.04.2026</t>
         </is>
       </c>
-      <c r="I59" s="38" t="inlineStr">
+      <c r="I59" s="48" t="inlineStr">
         <is>
           <t>апрель 2026</t>
         </is>
       </c>
-      <c r="J59" s="39" t="inlineStr">
+      <c r="J59" s="49" t="inlineStr">
         <is>
           <t>✅ Актуально</t>
         </is>
@@ -4189,7 +4244,7 @@
         </is>
       </c>
     </row>
-    <row r="60" ht="90" customHeight="1" s="26">
+    <row r="60" ht="90" customHeight="1" s="41">
       <c r="A60" s="2" t="inlineStr">
         <is>
           <t>5.22.ma12</t>
@@ -4230,12 +4285,12 @@
           <t>01.04.2026</t>
         </is>
       </c>
-      <c r="I60" s="38" t="inlineStr">
+      <c r="I60" s="48" t="inlineStr">
         <is>
           <t>апрель 2026</t>
         </is>
       </c>
-      <c r="J60" s="39" t="inlineStr">
+      <c r="J60" s="49" t="inlineStr">
         <is>
           <t>✅ Актуально</t>
         </is>
@@ -4249,7 +4304,7 @@
         </is>
       </c>
     </row>
-    <row r="61" ht="30" customHeight="1" s="26">
+    <row r="61" ht="30" customHeight="1" s="41">
       <c r="A61" s="5" t="inlineStr">
         <is>
           <t>6.1</t>
@@ -4290,14 +4345,14 @@
           <t>01.03.2026</t>
         </is>
       </c>
-      <c r="I61" s="40" t="inlineStr">
+      <c r="I61" s="48" t="inlineStr">
         <is>
           <t>март 2026</t>
         </is>
       </c>
-      <c r="J61" s="41" t="inlineStr">
-        <is>
-          <t>⚠️ Просрочено</t>
+      <c r="J61" s="49" t="inlineStr">
+        <is>
+          <t>✅ Актуально</t>
         </is>
       </c>
       <c r="K61" s="7" t="n">
@@ -4309,7 +4364,7 @@
         </is>
       </c>
     </row>
-    <row r="62" ht="30" customHeight="1" s="26">
+    <row r="62" ht="30" customHeight="1" s="41">
       <c r="A62" s="5" t="inlineStr">
         <is>
           <t>6.2</t>
@@ -4350,14 +4405,14 @@
           <t>01.03.2026</t>
         </is>
       </c>
-      <c r="I62" s="40" t="inlineStr">
+      <c r="I62" s="48" t="inlineStr">
         <is>
           <t>март 2026</t>
         </is>
       </c>
-      <c r="J62" s="41" t="inlineStr">
-        <is>
-          <t>⚠️ Просрочено</t>
+      <c r="J62" s="49" t="inlineStr">
+        <is>
+          <t>✅ Актуально</t>
         </is>
       </c>
       <c r="K62" s="7" t="n">
@@ -4410,14 +4465,14 @@
           <t>01.03.2026</t>
         </is>
       </c>
-      <c r="I63" s="40" t="inlineStr">
+      <c r="I63" s="48" t="inlineStr">
         <is>
           <t>март 2026</t>
         </is>
       </c>
-      <c r="J63" s="41" t="inlineStr">
-        <is>
-          <t>⚠️ Просрочено</t>
+      <c r="J63" s="49" t="inlineStr">
+        <is>
+          <t>✅ Актуально</t>
         </is>
       </c>
       <c r="K63" s="7" t="n">
@@ -4470,14 +4525,14 @@
           <t>01.03.2026</t>
         </is>
       </c>
-      <c r="I64" s="40" t="inlineStr">
+      <c r="I64" s="48" t="inlineStr">
         <is>
           <t>март 2026</t>
         </is>
       </c>
-      <c r="J64" s="41" t="inlineStr">
-        <is>
-          <t>⚠️ Просрочено</t>
+      <c r="J64" s="49" t="inlineStr">
+        <is>
+          <t>✅ Актуально</t>
         </is>
       </c>
       <c r="K64" s="7" t="n">
@@ -4530,14 +4585,14 @@
           <t>01.03.2026</t>
         </is>
       </c>
-      <c r="I65" s="40" t="inlineStr">
+      <c r="I65" s="48" t="inlineStr">
         <is>
           <t>март 2026</t>
         </is>
       </c>
-      <c r="J65" s="41" t="inlineStr">
-        <is>
-          <t>⚠️ Просрочено</t>
+      <c r="J65" s="49" t="inlineStr">
+        <is>
+          <t>✅ Актуально</t>
         </is>
       </c>
       <c r="K65" s="7" t="n">
@@ -4590,14 +4645,14 @@
           <t>01.03.2026</t>
         </is>
       </c>
-      <c r="I66" s="40" t="inlineStr">
+      <c r="I66" s="48" t="inlineStr">
         <is>
           <t>март 2026</t>
         </is>
       </c>
-      <c r="J66" s="41" t="inlineStr">
-        <is>
-          <t>⚠️ Просрочено</t>
+      <c r="J66" s="49" t="inlineStr">
+        <is>
+          <t>✅ Актуально</t>
         </is>
       </c>
       <c r="K66" s="7" t="n">
@@ -4650,14 +4705,14 @@
           <t>01.03.2026</t>
         </is>
       </c>
-      <c r="I67" s="40" t="inlineStr">
+      <c r="I67" s="48" t="inlineStr">
         <is>
           <t>март 2026</t>
         </is>
       </c>
-      <c r="J67" s="41" t="inlineStr">
-        <is>
-          <t>⚠️ Просрочено</t>
+      <c r="J67" s="49" t="inlineStr">
+        <is>
+          <t>✅ Актуально</t>
         </is>
       </c>
       <c r="K67" s="7" t="n">
@@ -4710,14 +4765,14 @@
           <t>01.03.2026</t>
         </is>
       </c>
-      <c r="I68" s="40" t="inlineStr">
+      <c r="I68" s="48" t="inlineStr">
         <is>
           <t>март 2026</t>
         </is>
       </c>
-      <c r="J68" s="41" t="inlineStr">
-        <is>
-          <t>⚠️ Просрочено</t>
+      <c r="J68" s="49" t="inlineStr">
+        <is>
+          <t>✅ Актуально</t>
         </is>
       </c>
       <c r="K68" s="7" t="n">
@@ -4729,7 +4784,7 @@
         </is>
       </c>
     </row>
-    <row r="69" ht="30" customHeight="1" s="26">
+    <row r="69" ht="30" customHeight="1" s="41">
       <c r="A69" s="5" t="inlineStr">
         <is>
           <t>6.9</t>
@@ -4770,14 +4825,14 @@
           <t>01.03.2026</t>
         </is>
       </c>
-      <c r="I69" s="40" t="inlineStr">
+      <c r="I69" s="48" t="inlineStr">
         <is>
           <t>март 2026</t>
         </is>
       </c>
-      <c r="J69" s="41" t="inlineStr">
-        <is>
-          <t>⚠️ Просрочено</t>
+      <c r="J69" s="49" t="inlineStr">
+        <is>
+          <t>✅ Актуально</t>
         </is>
       </c>
       <c r="K69" s="7" t="n">
@@ -4789,7 +4844,7 @@
         </is>
       </c>
     </row>
-    <row r="70" ht="30" customHeight="1" s="26">
+    <row r="70" ht="30" customHeight="1" s="41">
       <c r="A70" s="5" t="inlineStr">
         <is>
           <t>6.10</t>
@@ -4830,14 +4885,14 @@
           <t>01.03.2026</t>
         </is>
       </c>
-      <c r="I70" s="40" t="inlineStr">
+      <c r="I70" s="48" t="inlineStr">
         <is>
           <t>март 2026</t>
         </is>
       </c>
-      <c r="J70" s="41" t="inlineStr">
-        <is>
-          <t>⚠️ Просрочено</t>
+      <c r="J70" s="49" t="inlineStr">
+        <is>
+          <t>✅ Актуально</t>
         </is>
       </c>
       <c r="K70" s="7" t="n">
@@ -4849,7 +4904,7 @@
         </is>
       </c>
     </row>
-    <row r="71" ht="30" customHeight="1" s="26">
+    <row r="71" ht="30" customHeight="1" s="41">
       <c r="A71" s="5" t="inlineStr">
         <is>
           <t>6.11</t>
@@ -4890,14 +4945,14 @@
           <t>01.03.2026</t>
         </is>
       </c>
-      <c r="I71" s="40" t="inlineStr">
+      <c r="I71" s="48" t="inlineStr">
         <is>
           <t>март 2026</t>
         </is>
       </c>
-      <c r="J71" s="41" t="inlineStr">
-        <is>
-          <t>⚠️ Просрочено</t>
+      <c r="J71" s="49" t="inlineStr">
+        <is>
+          <t>✅ Актуально</t>
         </is>
       </c>
       <c r="K71" s="7" t="n">
@@ -4909,7 +4964,7 @@
         </is>
       </c>
     </row>
-    <row r="72" ht="30" customHeight="1" s="26">
+    <row r="72" ht="30" customHeight="1" s="41">
       <c r="A72" s="5" t="inlineStr">
         <is>
           <t>6.12</t>
@@ -4950,14 +5005,14 @@
           <t>01.03.2026</t>
         </is>
       </c>
-      <c r="I72" s="40" t="inlineStr">
+      <c r="I72" s="48" t="inlineStr">
         <is>
           <t>март 2026</t>
         </is>
       </c>
-      <c r="J72" s="41" t="inlineStr">
-        <is>
-          <t>⚠️ Просрочено</t>
+      <c r="J72" s="49" t="inlineStr">
+        <is>
+          <t>✅ Актуально</t>
         </is>
       </c>
       <c r="K72" s="7" t="n">
@@ -4969,7 +5024,7 @@
         </is>
       </c>
     </row>
-    <row r="73" ht="30" customHeight="1" s="26">
+    <row r="73" ht="30" customHeight="1" s="41">
       <c r="A73" s="5" t="inlineStr">
         <is>
           <t>6.13</t>
@@ -5010,14 +5065,14 @@
           <t>01.03.2026</t>
         </is>
       </c>
-      <c r="I73" s="40" t="inlineStr">
+      <c r="I73" s="48" t="inlineStr">
         <is>
           <t>март 2026</t>
         </is>
       </c>
-      <c r="J73" s="41" t="inlineStr">
-        <is>
-          <t>⚠️ Просрочено</t>
+      <c r="J73" s="49" t="inlineStr">
+        <is>
+          <t>✅ Актуально</t>
         </is>
       </c>
       <c r="K73" s="7" t="n">
@@ -5029,7 +5084,7 @@
         </is>
       </c>
     </row>
-    <row r="74" ht="30" customHeight="1" s="26">
+    <row r="74" ht="30" customHeight="1" s="41">
       <c r="A74" s="5" t="inlineStr">
         <is>
           <t>6.14</t>
@@ -5070,14 +5125,14 @@
           <t>01.03.2026</t>
         </is>
       </c>
-      <c r="I74" s="40" t="inlineStr">
+      <c r="I74" s="48" t="inlineStr">
         <is>
           <t>март 2026</t>
         </is>
       </c>
-      <c r="J74" s="41" t="inlineStr">
-        <is>
-          <t>⚠️ Просрочено</t>
+      <c r="J74" s="49" t="inlineStr">
+        <is>
+          <t>✅ Актуально</t>
         </is>
       </c>
       <c r="K74" s="7" t="n">
@@ -5089,7 +5144,7 @@
         </is>
       </c>
     </row>
-    <row r="75" ht="30" customHeight="1" s="26">
+    <row r="75" ht="30" customHeight="1" s="41">
       <c r="A75" s="5" t="inlineStr">
         <is>
           <t>6.15</t>
@@ -5130,14 +5185,14 @@
           <t>01.03.2026</t>
         </is>
       </c>
-      <c r="I75" s="40" t="inlineStr">
+      <c r="I75" s="48" t="inlineStr">
         <is>
           <t>март 2026</t>
         </is>
       </c>
-      <c r="J75" s="41" t="inlineStr">
-        <is>
-          <t>⚠️ Просрочено</t>
+      <c r="J75" s="49" t="inlineStr">
+        <is>
+          <t>✅ Актуально</t>
         </is>
       </c>
       <c r="K75" s="7" t="n">
@@ -5149,7 +5204,7 @@
         </is>
       </c>
     </row>
-    <row r="76" ht="30" customHeight="1" s="26">
+    <row r="76" ht="30" customHeight="1" s="41">
       <c r="A76" s="5" t="inlineStr">
         <is>
           <t>6.16</t>
@@ -5190,14 +5245,14 @@
           <t>01.03.2026</t>
         </is>
       </c>
-      <c r="I76" s="40" t="inlineStr">
+      <c r="I76" s="48" t="inlineStr">
         <is>
           <t>март 2026</t>
         </is>
       </c>
-      <c r="J76" s="41" t="inlineStr">
-        <is>
-          <t>⚠️ Просрочено</t>
+      <c r="J76" s="49" t="inlineStr">
+        <is>
+          <t>✅ Актуально</t>
         </is>
       </c>
       <c r="K76" s="7" t="n">
@@ -5209,7 +5264,7 @@
         </is>
       </c>
     </row>
-    <row r="77" ht="30" customHeight="1" s="26">
+    <row r="77" ht="30" customHeight="1" s="41">
       <c r="A77" s="5" t="inlineStr">
         <is>
           <t>6.17</t>
@@ -5250,14 +5305,14 @@
           <t>01.03.2026</t>
         </is>
       </c>
-      <c r="I77" s="40" t="inlineStr">
+      <c r="I77" s="48" t="inlineStr">
         <is>
           <t>март 2026</t>
         </is>
       </c>
-      <c r="J77" s="41" t="inlineStr">
-        <is>
-          <t>⚠️ Просрочено</t>
+      <c r="J77" s="49" t="inlineStr">
+        <is>
+          <t>✅ Актуально</t>
         </is>
       </c>
       <c r="K77" s="7" t="n">
@@ -5269,7 +5324,7 @@
         </is>
       </c>
     </row>
-    <row r="78" ht="30" customHeight="1" s="26">
+    <row r="78" ht="30" customHeight="1" s="41">
       <c r="A78" s="5" t="inlineStr">
         <is>
           <t>6.18</t>
@@ -5310,14 +5365,14 @@
           <t>01.03.2026</t>
         </is>
       </c>
-      <c r="I78" s="40" t="inlineStr">
+      <c r="I78" s="48" t="inlineStr">
         <is>
           <t>март 2026</t>
         </is>
       </c>
-      <c r="J78" s="41" t="inlineStr">
-        <is>
-          <t>⚠️ Просрочено</t>
+      <c r="J78" s="49" t="inlineStr">
+        <is>
+          <t>✅ Актуально</t>
         </is>
       </c>
       <c r="K78" s="7" t="n">
@@ -5370,14 +5425,14 @@
           <t>01.03.2026</t>
         </is>
       </c>
-      <c r="I79" s="40" t="inlineStr">
+      <c r="I79" s="48" t="inlineStr">
         <is>
           <t>март 2026</t>
         </is>
       </c>
-      <c r="J79" s="41" t="inlineStr">
-        <is>
-          <t>⚠️ Просрочено</t>
+      <c r="J79" s="49" t="inlineStr">
+        <is>
+          <t>✅ Актуально</t>
         </is>
       </c>
       <c r="K79" s="7" t="n">
@@ -5430,14 +5485,14 @@
           <t>01.03.2026</t>
         </is>
       </c>
-      <c r="I80" s="40" t="inlineStr">
+      <c r="I80" s="48" t="inlineStr">
         <is>
           <t>март 2026</t>
         </is>
       </c>
-      <c r="J80" s="41" t="inlineStr">
-        <is>
-          <t>⚠️ Просрочено</t>
+      <c r="J80" s="49" t="inlineStr">
+        <is>
+          <t>✅ Актуально</t>
         </is>
       </c>
       <c r="K80" s="7" t="n">
@@ -5490,14 +5545,14 @@
           <t>01.03.2026</t>
         </is>
       </c>
-      <c r="I81" s="40" t="inlineStr">
+      <c r="I81" s="48" t="inlineStr">
         <is>
           <t>март 2026</t>
         </is>
       </c>
-      <c r="J81" s="41" t="inlineStr">
-        <is>
-          <t>⚠️ Просрочено</t>
+      <c r="J81" s="49" t="inlineStr">
+        <is>
+          <t>✅ Актуально</t>
         </is>
       </c>
       <c r="K81" s="7" t="n">
@@ -5509,7 +5564,7 @@
         </is>
       </c>
     </row>
-    <row r="82" ht="30" customHeight="1" s="26">
+    <row r="82" ht="30" customHeight="1" s="41">
       <c r="A82" s="5" t="inlineStr">
         <is>
           <t>6.22</t>
@@ -5550,14 +5605,14 @@
           <t>01.03.2026</t>
         </is>
       </c>
-      <c r="I82" s="40" t="inlineStr">
+      <c r="I82" s="48" t="inlineStr">
         <is>
           <t>март 2026</t>
         </is>
       </c>
-      <c r="J82" s="41" t="inlineStr">
-        <is>
-          <t>⚠️ Просрочено</t>
+      <c r="J82" s="49" t="inlineStr">
+        <is>
+          <t>✅ Актуально</t>
         </is>
       </c>
       <c r="K82" s="7" t="n">
@@ -5569,7 +5624,7 @@
         </is>
       </c>
     </row>
-    <row r="83" ht="30" customHeight="1" s="26">
+    <row r="83" ht="30" customHeight="1" s="41">
       <c r="A83" s="5" t="inlineStr">
         <is>
           <t>6.23</t>
@@ -5610,14 +5665,14 @@
           <t>01.03.2026</t>
         </is>
       </c>
-      <c r="I83" s="40" t="inlineStr">
+      <c r="I83" s="48" t="inlineStr">
         <is>
           <t>март 2026</t>
         </is>
       </c>
-      <c r="J83" s="41" t="inlineStr">
-        <is>
-          <t>⚠️ Просрочено</t>
+      <c r="J83" s="49" t="inlineStr">
+        <is>
+          <t>✅ Актуально</t>
         </is>
       </c>
       <c r="K83" s="7" t="n">
@@ -5629,7 +5684,7 @@
         </is>
       </c>
     </row>
-    <row r="84" ht="30" customHeight="1" s="26">
+    <row r="84" ht="30" customHeight="1" s="41">
       <c r="A84" s="5" t="inlineStr">
         <is>
           <t>6.24</t>
@@ -5670,14 +5725,14 @@
           <t>01.03.2026</t>
         </is>
       </c>
-      <c r="I84" s="40" t="inlineStr">
+      <c r="I84" s="48" t="inlineStr">
         <is>
           <t>март 2026</t>
         </is>
       </c>
-      <c r="J84" s="41" t="inlineStr">
-        <is>
-          <t>⚠️ Просрочено</t>
+      <c r="J84" s="49" t="inlineStr">
+        <is>
+          <t>✅ Актуально</t>
         </is>
       </c>
       <c r="K84" s="7" t="n">
@@ -5689,7 +5744,7 @@
         </is>
       </c>
     </row>
-    <row r="85" ht="30" customHeight="1" s="26">
+    <row r="85" ht="30" customHeight="1" s="41">
       <c r="A85" s="5" t="inlineStr">
         <is>
           <t>6.25</t>
@@ -5730,14 +5785,14 @@
           <t>01.03.2026</t>
         </is>
       </c>
-      <c r="I85" s="40" t="inlineStr">
+      <c r="I85" s="48" t="inlineStr">
         <is>
           <t>март 2026</t>
         </is>
       </c>
-      <c r="J85" s="41" t="inlineStr">
-        <is>
-          <t>⚠️ Просрочено</t>
+      <c r="J85" s="49" t="inlineStr">
+        <is>
+          <t>✅ Актуально</t>
         </is>
       </c>
       <c r="K85" s="7" t="n">
@@ -5749,7 +5804,7 @@
         </is>
       </c>
     </row>
-    <row r="86" ht="30" customHeight="1" s="26">
+    <row r="86" ht="30" customHeight="1" s="41">
       <c r="A86" s="5" t="inlineStr">
         <is>
           <t>6.26</t>
@@ -5790,14 +5845,14 @@
           <t>01.03.2026</t>
         </is>
       </c>
-      <c r="I86" s="40" t="inlineStr">
+      <c r="I86" s="48" t="inlineStr">
         <is>
           <t>март 2026</t>
         </is>
       </c>
-      <c r="J86" s="41" t="inlineStr">
-        <is>
-          <t>⚠️ Просрочено</t>
+      <c r="J86" s="49" t="inlineStr">
+        <is>
+          <t>✅ Актуально</t>
         </is>
       </c>
       <c r="K86" s="7" t="n">
@@ -5809,7 +5864,7 @@
         </is>
       </c>
     </row>
-    <row r="87" ht="30" customHeight="1" s="26">
+    <row r="87" ht="30" customHeight="1" s="41">
       <c r="A87" s="5" t="inlineStr">
         <is>
           <t>6.27</t>
@@ -5850,14 +5905,14 @@
           <t>01.03.2026</t>
         </is>
       </c>
-      <c r="I87" s="40" t="inlineStr">
+      <c r="I87" s="48" t="inlineStr">
         <is>
           <t>март 2026</t>
         </is>
       </c>
-      <c r="J87" s="41" t="inlineStr">
-        <is>
-          <t>⚠️ Просрочено</t>
+      <c r="J87" s="49" t="inlineStr">
+        <is>
+          <t>✅ Актуально</t>
         </is>
       </c>
       <c r="K87" s="7" t="n">
@@ -5869,7 +5924,7 @@
         </is>
       </c>
     </row>
-    <row r="88" ht="30" customHeight="1" s="26">
+    <row r="88" ht="30" customHeight="1" s="41">
       <c r="A88" s="5" t="inlineStr">
         <is>
           <t>6.36</t>
@@ -5910,12 +5965,12 @@
           <t>01.04.2026</t>
         </is>
       </c>
-      <c r="I88" s="38" t="inlineStr">
+      <c r="I88" s="48" t="inlineStr">
         <is>
           <t>апрель 2026</t>
         </is>
       </c>
-      <c r="J88" s="39" t="inlineStr">
+      <c r="J88" s="49" t="inlineStr">
         <is>
           <t>✅ Актуально</t>
         </is>
@@ -5929,7 +5984,7 @@
         </is>
       </c>
     </row>
-    <row r="89" ht="30" customHeight="1" s="26">
+    <row r="89" ht="30" customHeight="1" s="41">
       <c r="A89" s="5" t="inlineStr">
         <is>
           <t>6.37</t>
@@ -5970,12 +6025,12 @@
           <t>01.04.2026</t>
         </is>
       </c>
-      <c r="I89" s="38" t="inlineStr">
+      <c r="I89" s="48" t="inlineStr">
         <is>
           <t>апрель 2026</t>
         </is>
       </c>
-      <c r="J89" s="39" t="inlineStr">
+      <c r="J89" s="49" t="inlineStr">
         <is>
           <t>✅ Актуально</t>
         </is>
@@ -5989,7 +6044,7 @@
         </is>
       </c>
     </row>
-    <row r="90" ht="30" customHeight="1" s="26">
+    <row r="90" ht="30" customHeight="1" s="41">
       <c r="A90" s="5" t="inlineStr">
         <is>
           <t>6.38</t>
@@ -6030,14 +6085,14 @@
           <t>01.03.2026</t>
         </is>
       </c>
-      <c r="I90" s="40" t="inlineStr">
+      <c r="I90" s="48" t="inlineStr">
         <is>
           <t>март 2026</t>
         </is>
       </c>
-      <c r="J90" s="41" t="inlineStr">
-        <is>
-          <t>⚠️ Просрочено</t>
+      <c r="J90" s="49" t="inlineStr">
+        <is>
+          <t>✅ Актуально</t>
         </is>
       </c>
       <c r="K90" s="7" t="n">
@@ -6049,7 +6104,7 @@
         </is>
       </c>
     </row>
-    <row r="91" ht="30" customHeight="1" s="26">
+    <row r="91" ht="30" customHeight="1" s="41">
       <c r="A91" s="5" t="inlineStr">
         <is>
           <t>6.39</t>
@@ -6090,14 +6145,14 @@
           <t>01.03.2026</t>
         </is>
       </c>
-      <c r="I91" s="40" t="inlineStr">
+      <c r="I91" s="48" t="inlineStr">
         <is>
           <t>март 2026</t>
         </is>
       </c>
-      <c r="J91" s="41" t="inlineStr">
-        <is>
-          <t>⚠️ Просрочено</t>
+      <c r="J91" s="49" t="inlineStr">
+        <is>
+          <t>✅ Актуально</t>
         </is>
       </c>
       <c r="K91" s="7" t="n">
@@ -6109,7 +6164,7 @@
         </is>
       </c>
     </row>
-    <row r="92" ht="30" customHeight="1" s="26">
+    <row r="92" ht="30" customHeight="1" s="41">
       <c r="A92" s="5" t="inlineStr">
         <is>
           <t>6.40</t>
@@ -6150,12 +6205,12 @@
           <t>01.04.2026</t>
         </is>
       </c>
-      <c r="I92" s="38" t="inlineStr">
+      <c r="I92" s="48" t="inlineStr">
         <is>
           <t>апрель 2026</t>
         </is>
       </c>
-      <c r="J92" s="39" t="inlineStr">
+      <c r="J92" s="49" t="inlineStr">
         <is>
           <t>✅ Актуально</t>
         </is>
@@ -6169,7 +6224,7 @@
         </is>
       </c>
     </row>
-    <row r="93" ht="30" customHeight="1" s="26">
+    <row r="93" ht="30" customHeight="1" s="41">
       <c r="A93" s="5" t="inlineStr">
         <is>
           <t>6.41</t>
@@ -6210,12 +6265,12 @@
           <t>01.04.2026</t>
         </is>
       </c>
-      <c r="I93" s="38" t="inlineStr">
+      <c r="I93" s="48" t="inlineStr">
         <is>
           <t>апрель 2026</t>
         </is>
       </c>
-      <c r="J93" s="39" t="inlineStr">
+      <c r="J93" s="49" t="inlineStr">
         <is>
           <t>✅ Актуально</t>
         </is>
@@ -6270,12 +6325,12 @@
           <t>01.04.2026</t>
         </is>
       </c>
-      <c r="I94" s="38" t="inlineStr">
+      <c r="I94" s="48" t="inlineStr">
         <is>
           <t>апрель 2026</t>
         </is>
       </c>
-      <c r="J94" s="39" t="inlineStr">
+      <c r="J94" s="49" t="inlineStr">
         <is>
           <t>✅ Актуально</t>
         </is>
@@ -6330,12 +6385,12 @@
           <t>01.04.2026</t>
         </is>
       </c>
-      <c r="I95" s="38" t="inlineStr">
+      <c r="I95" s="48" t="inlineStr">
         <is>
           <t>апрель 2026</t>
         </is>
       </c>
-      <c r="J95" s="39" t="inlineStr">
+      <c r="J95" s="49" t="inlineStr">
         <is>
           <t>✅ Актуально</t>
         </is>
@@ -6390,12 +6445,12 @@
           <t>01.04.2026</t>
         </is>
       </c>
-      <c r="I96" s="38" t="inlineStr">
+      <c r="I96" s="48" t="inlineStr">
         <is>
           <t>апрель 2026</t>
         </is>
       </c>
-      <c r="J96" s="39" t="inlineStr">
+      <c r="J96" s="49" t="inlineStr">
         <is>
           <t>✅ Актуально</t>
         </is>
@@ -6450,12 +6505,12 @@
           <t>01.04.2026</t>
         </is>
       </c>
-      <c r="I97" s="38" t="inlineStr">
+      <c r="I97" s="48" t="inlineStr">
         <is>
           <t>апрель 2026</t>
         </is>
       </c>
-      <c r="J97" s="39" t="inlineStr">
+      <c r="J97" s="49" t="inlineStr">
         <is>
           <t>✅ Актуально</t>
         </is>
@@ -6469,7 +6524,7 @@
         </is>
       </c>
     </row>
-    <row r="98" ht="30" customHeight="1" s="26">
+    <row r="98" ht="30" customHeight="1" s="41">
       <c r="A98" s="5" t="inlineStr">
         <is>
           <t>6.70</t>
@@ -6510,14 +6565,14 @@
           <t>01.03.2026</t>
         </is>
       </c>
-      <c r="I98" s="40" t="inlineStr">
+      <c r="I98" s="48" t="inlineStr">
         <is>
           <t>март 2026</t>
         </is>
       </c>
-      <c r="J98" s="41" t="inlineStr">
-        <is>
-          <t>⚠️ Просрочено</t>
+      <c r="J98" s="49" t="inlineStr">
+        <is>
+          <t>✅ Актуально</t>
         </is>
       </c>
       <c r="K98" s="7" t="n">
@@ -6570,14 +6625,14 @@
           <t>01.03.2026</t>
         </is>
       </c>
-      <c r="I99" s="40" t="inlineStr">
+      <c r="I99" s="48" t="inlineStr">
         <is>
           <t>март 2026</t>
         </is>
       </c>
-      <c r="J99" s="41" t="inlineStr">
-        <is>
-          <t>⚠️ Просрочено</t>
+      <c r="J99" s="49" t="inlineStr">
+        <is>
+          <t>✅ Актуально</t>
         </is>
       </c>
       <c r="K99" s="7" t="n">
@@ -6589,7 +6644,7 @@
         </is>
       </c>
     </row>
-    <row r="100" ht="30" customHeight="1" s="26">
+    <row r="100" ht="30" customHeight="1" s="41">
       <c r="A100" s="5" t="inlineStr">
         <is>
           <t>6.72</t>
@@ -6630,14 +6685,14 @@
           <t>01.03.2026</t>
         </is>
       </c>
-      <c r="I100" s="40" t="inlineStr">
+      <c r="I100" s="48" t="inlineStr">
         <is>
           <t>март 2026</t>
         </is>
       </c>
-      <c r="J100" s="41" t="inlineStr">
-        <is>
-          <t>⚠️ Просрочено</t>
+      <c r="J100" s="49" t="inlineStr">
+        <is>
+          <t>✅ Актуально</t>
         </is>
       </c>
       <c r="K100" s="7" t="n">
@@ -6649,7 +6704,7 @@
         </is>
       </c>
     </row>
-    <row r="101" ht="30" customHeight="1" s="26">
+    <row r="101" ht="30" customHeight="1" s="41">
       <c r="A101" s="5" t="inlineStr">
         <is>
           <t>6.73</t>
@@ -6690,14 +6745,14 @@
           <t>01.03.2026</t>
         </is>
       </c>
-      <c r="I101" s="40" t="inlineStr">
+      <c r="I101" s="48" t="inlineStr">
         <is>
           <t>март 2026</t>
         </is>
       </c>
-      <c r="J101" s="41" t="inlineStr">
-        <is>
-          <t>⚠️ Просрочено</t>
+      <c r="J101" s="49" t="inlineStr">
+        <is>
+          <t>✅ Актуально</t>
         </is>
       </c>
       <c r="K101" s="7" t="n">
@@ -6709,7 +6764,7 @@
         </is>
       </c>
     </row>
-    <row r="102" ht="30" customHeight="1" s="26">
+    <row r="102" ht="30" customHeight="1" s="41">
       <c r="A102" s="5" t="inlineStr">
         <is>
           <t>6.74</t>
@@ -6750,14 +6805,14 @@
           <t>01.03.2026</t>
         </is>
       </c>
-      <c r="I102" s="40" t="inlineStr">
+      <c r="I102" s="48" t="inlineStr">
         <is>
           <t>март 2026</t>
         </is>
       </c>
-      <c r="J102" s="41" t="inlineStr">
-        <is>
-          <t>⚠️ Просрочено</t>
+      <c r="J102" s="49" t="inlineStr">
+        <is>
+          <t>✅ Актуально</t>
         </is>
       </c>
       <c r="K102" s="7" t="n">
@@ -6769,7 +6824,7 @@
         </is>
       </c>
     </row>
-    <row r="103" ht="30" customHeight="1" s="26">
+    <row r="103" ht="30" customHeight="1" s="41">
       <c r="A103" s="5" t="inlineStr">
         <is>
           <t>6.75</t>
@@ -6810,14 +6865,14 @@
           <t>01.03.2026</t>
         </is>
       </c>
-      <c r="I103" s="40" t="inlineStr">
+      <c r="I103" s="48" t="inlineStr">
         <is>
           <t>март 2026</t>
         </is>
       </c>
-      <c r="J103" s="41" t="inlineStr">
-        <is>
-          <t>⚠️ Просрочено</t>
+      <c r="J103" s="49" t="inlineStr">
+        <is>
+          <t>✅ Актуально</t>
         </is>
       </c>
       <c r="K103" s="7" t="n">
@@ -6829,7 +6884,7 @@
         </is>
       </c>
     </row>
-    <row r="104" ht="30" customHeight="1" s="26">
+    <row r="104" ht="30" customHeight="1" s="41">
       <c r="A104" s="5" t="inlineStr">
         <is>
           <t>6.76</t>
@@ -6870,14 +6925,14 @@
           <t>01.03.2026</t>
         </is>
       </c>
-      <c r="I104" s="40" t="inlineStr">
+      <c r="I104" s="48" t="inlineStr">
         <is>
           <t>март 2026</t>
         </is>
       </c>
-      <c r="J104" s="41" t="inlineStr">
-        <is>
-          <t>⚠️ Просрочено</t>
+      <c r="J104" s="49" t="inlineStr">
+        <is>
+          <t>✅ Актуально</t>
         </is>
       </c>
       <c r="K104" s="7" t="n">
@@ -6889,7 +6944,7 @@
         </is>
       </c>
     </row>
-    <row r="105" ht="30" customHeight="1" s="26">
+    <row r="105" ht="30" customHeight="1" s="41">
       <c r="A105" s="5" t="inlineStr">
         <is>
           <t>6.77</t>
@@ -6930,14 +6985,14 @@
           <t>01.03.2026</t>
         </is>
       </c>
-      <c r="I105" s="40" t="inlineStr">
+      <c r="I105" s="48" t="inlineStr">
         <is>
           <t>март 2026</t>
         </is>
       </c>
-      <c r="J105" s="41" t="inlineStr">
-        <is>
-          <t>⚠️ Просрочено</t>
+      <c r="J105" s="49" t="inlineStr">
+        <is>
+          <t>✅ Актуально</t>
         </is>
       </c>
       <c r="K105" s="7" t="n">
@@ -6949,7 +7004,7 @@
         </is>
       </c>
     </row>
-    <row r="106" ht="30" customHeight="1" s="26">
+    <row r="106" ht="30" customHeight="1" s="41">
       <c r="A106" s="5" t="inlineStr">
         <is>
           <t>6.78</t>
@@ -6990,14 +7045,14 @@
           <t>01.03.2026</t>
         </is>
       </c>
-      <c r="I106" s="40" t="inlineStr">
+      <c r="I106" s="48" t="inlineStr">
         <is>
           <t>март 2026</t>
         </is>
       </c>
-      <c r="J106" s="41" t="inlineStr">
-        <is>
-          <t>⚠️ Просрочено</t>
+      <c r="J106" s="49" t="inlineStr">
+        <is>
+          <t>✅ Актуально</t>
         </is>
       </c>
       <c r="K106" s="7" t="n">
@@ -7009,7 +7064,7 @@
         </is>
       </c>
     </row>
-    <row r="107" ht="30" customHeight="1" s="26">
+    <row r="107" ht="30" customHeight="1" s="41">
       <c r="A107" s="5" t="inlineStr">
         <is>
           <t>6.79</t>
@@ -7050,14 +7105,14 @@
           <t>01.03.2026</t>
         </is>
       </c>
-      <c r="I107" s="40" t="inlineStr">
+      <c r="I107" s="48" t="inlineStr">
         <is>
           <t>март 2026</t>
         </is>
       </c>
-      <c r="J107" s="41" t="inlineStr">
-        <is>
-          <t>⚠️ Просрочено</t>
+      <c r="J107" s="49" t="inlineStr">
+        <is>
+          <t>✅ Актуально</t>
         </is>
       </c>
       <c r="K107" s="7" t="n">
@@ -7069,7 +7124,7 @@
         </is>
       </c>
     </row>
-    <row r="108" ht="30" customHeight="1" s="26">
+    <row r="108" ht="30" customHeight="1" s="41">
       <c r="A108" s="5" t="inlineStr">
         <is>
           <t>6.80</t>
@@ -7110,14 +7165,14 @@
           <t>01.03.2026</t>
         </is>
       </c>
-      <c r="I108" s="40" t="inlineStr">
+      <c r="I108" s="48" t="inlineStr">
         <is>
           <t>март 2026</t>
         </is>
       </c>
-      <c r="J108" s="41" t="inlineStr">
-        <is>
-          <t>⚠️ Просрочено</t>
+      <c r="J108" s="49" t="inlineStr">
+        <is>
+          <t>✅ Актуально</t>
         </is>
       </c>
       <c r="K108" s="7" t="n">
@@ -7129,7 +7184,7 @@
         </is>
       </c>
     </row>
-    <row r="109" ht="30" customHeight="1" s="26">
+    <row r="109" ht="30" customHeight="1" s="41">
       <c r="A109" s="5" t="inlineStr">
         <is>
           <t>6.81</t>
@@ -7170,14 +7225,14 @@
           <t>01.03.2026</t>
         </is>
       </c>
-      <c r="I109" s="40" t="inlineStr">
+      <c r="I109" s="48" t="inlineStr">
         <is>
           <t>март 2026</t>
         </is>
       </c>
-      <c r="J109" s="41" t="inlineStr">
-        <is>
-          <t>⚠️ Просрочено</t>
+      <c r="J109" s="49" t="inlineStr">
+        <is>
+          <t>✅ Актуально</t>
         </is>
       </c>
       <c r="K109" s="7" t="n">
@@ -7189,7 +7244,7 @@
         </is>
       </c>
     </row>
-    <row r="110" ht="30" customHeight="1" s="26">
+    <row r="110" ht="30" customHeight="1" s="41">
       <c r="A110" s="5" t="inlineStr">
         <is>
           <t>6.82</t>
@@ -7230,14 +7285,14 @@
           <t>01.03.2026</t>
         </is>
       </c>
-      <c r="I110" s="40" t="inlineStr">
+      <c r="I110" s="48" t="inlineStr">
         <is>
           <t>март 2026</t>
         </is>
       </c>
-      <c r="J110" s="41" t="inlineStr">
-        <is>
-          <t>⚠️ Просрочено</t>
+      <c r="J110" s="49" t="inlineStr">
+        <is>
+          <t>✅ Актуально</t>
         </is>
       </c>
       <c r="K110" s="7" t="n">
@@ -7249,7 +7304,7 @@
         </is>
       </c>
     </row>
-    <row r="111" ht="30" customHeight="1" s="26">
+    <row r="111" ht="30" customHeight="1" s="41">
       <c r="A111" s="5" t="inlineStr">
         <is>
           <t>6.83</t>
@@ -7290,14 +7345,14 @@
           <t>01.03.2026</t>
         </is>
       </c>
-      <c r="I111" s="40" t="inlineStr">
+      <c r="I111" s="48" t="inlineStr">
         <is>
           <t>март 2026</t>
         </is>
       </c>
-      <c r="J111" s="41" t="inlineStr">
-        <is>
-          <t>⚠️ Просрочено</t>
+      <c r="J111" s="49" t="inlineStr">
+        <is>
+          <t>✅ Актуально</t>
         </is>
       </c>
       <c r="K111" s="7" t="n">
@@ -7309,7 +7364,7 @@
         </is>
       </c>
     </row>
-    <row r="112" ht="30" customHeight="1" s="26">
+    <row r="112" ht="30" customHeight="1" s="41">
       <c r="A112" s="5" t="inlineStr">
         <is>
           <t>6.84</t>
@@ -7350,14 +7405,14 @@
           <t>01.03.2026</t>
         </is>
       </c>
-      <c r="I112" s="40" t="inlineStr">
+      <c r="I112" s="48" t="inlineStr">
         <is>
           <t>март 2026</t>
         </is>
       </c>
-      <c r="J112" s="41" t="inlineStr">
-        <is>
-          <t>⚠️ Просрочено</t>
+      <c r="J112" s="49" t="inlineStr">
+        <is>
+          <t>✅ Актуально</t>
         </is>
       </c>
       <c r="K112" s="7" t="n">
@@ -7369,7 +7424,7 @@
         </is>
       </c>
     </row>
-    <row r="113" ht="30" customHeight="1" s="26">
+    <row r="113" ht="30" customHeight="1" s="41">
       <c r="A113" s="5" t="inlineStr">
         <is>
           <t>6.85</t>
@@ -7410,14 +7465,14 @@
           <t>01.03.2026</t>
         </is>
       </c>
-      <c r="I113" s="40" t="inlineStr">
+      <c r="I113" s="48" t="inlineStr">
         <is>
           <t>март 2026</t>
         </is>
       </c>
-      <c r="J113" s="41" t="inlineStr">
-        <is>
-          <t>⚠️ Просрочено</t>
+      <c r="J113" s="49" t="inlineStr">
+        <is>
+          <t>✅ Актуально</t>
         </is>
       </c>
       <c r="K113" s="7" t="n">
@@ -7429,7 +7484,7 @@
         </is>
       </c>
     </row>
-    <row r="114" ht="30" customHeight="1" s="26">
+    <row r="114" ht="30" customHeight="1" s="41">
       <c r="A114" s="5" t="inlineStr">
         <is>
           <t>6.86</t>
@@ -7470,14 +7525,14 @@
           <t>01.03.2026</t>
         </is>
       </c>
-      <c r="I114" s="40" t="inlineStr">
+      <c r="I114" s="48" t="inlineStr">
         <is>
           <t>март 2026</t>
         </is>
       </c>
-      <c r="J114" s="41" t="inlineStr">
-        <is>
-          <t>⚠️ Просрочено</t>
+      <c r="J114" s="49" t="inlineStr">
+        <is>
+          <t>✅ Актуально</t>
         </is>
       </c>
       <c r="K114" s="7" t="n">
@@ -7489,7 +7544,7 @@
         </is>
       </c>
     </row>
-    <row r="115" ht="30" customHeight="1" s="26">
+    <row r="115" ht="30" customHeight="1" s="41">
       <c r="A115" s="5" t="inlineStr">
         <is>
           <t>6.87</t>
@@ -7530,14 +7585,14 @@
           <t>01.03.2026</t>
         </is>
       </c>
-      <c r="I115" s="40" t="inlineStr">
+      <c r="I115" s="48" t="inlineStr">
         <is>
           <t>март 2026</t>
         </is>
       </c>
-      <c r="J115" s="41" t="inlineStr">
-        <is>
-          <t>⚠️ Просрочено</t>
+      <c r="J115" s="49" t="inlineStr">
+        <is>
+          <t>✅ Актуально</t>
         </is>
       </c>
       <c r="K115" s="7" t="n">
@@ -7549,7 +7604,7 @@
         </is>
       </c>
     </row>
-    <row r="116" ht="75" customHeight="1" s="26">
+    <row r="116" ht="75" customHeight="1" s="41">
       <c r="A116" s="8" t="inlineStr">
         <is>
           <t>apartments_area_1k</t>
@@ -7590,12 +7645,12 @@
           <t>01.05.2026</t>
         </is>
       </c>
-      <c r="I116" s="38" t="inlineStr">
+      <c r="I116" s="48" t="inlineStr">
         <is>
           <t>май 2026</t>
         </is>
       </c>
-      <c r="J116" s="39" t="inlineStr">
+      <c r="J116" s="49" t="inlineStr">
         <is>
           <t>✅ Актуально</t>
         </is>
@@ -7609,7 +7664,7 @@
         </is>
       </c>
     </row>
-    <row r="117" ht="75" customHeight="1" s="26">
+    <row r="117" ht="75" customHeight="1" s="41">
       <c r="A117" s="8" t="inlineStr">
         <is>
           <t>apartments_area_2k</t>
@@ -7650,12 +7705,12 @@
           <t>01.05.2026</t>
         </is>
       </c>
-      <c r="I117" s="38" t="inlineStr">
+      <c r="I117" s="48" t="inlineStr">
         <is>
           <t>май 2026</t>
         </is>
       </c>
-      <c r="J117" s="39" t="inlineStr">
+      <c r="J117" s="49" t="inlineStr">
         <is>
           <t>✅ Актуально</t>
         </is>
@@ -7669,7 +7724,7 @@
         </is>
       </c>
     </row>
-    <row r="118" ht="75" customHeight="1" s="26">
+    <row r="118" ht="75" customHeight="1" s="41">
       <c r="A118" s="8" t="inlineStr">
         <is>
           <t>apartments_area_3k</t>
@@ -7710,12 +7765,12 @@
           <t>01.05.2026</t>
         </is>
       </c>
-      <c r="I118" s="38" t="inlineStr">
+      <c r="I118" s="48" t="inlineStr">
         <is>
           <t>май 2026</t>
         </is>
       </c>
-      <c r="J118" s="39" t="inlineStr">
+      <c r="J118" s="49" t="inlineStr">
         <is>
           <t>✅ Актуально</t>
         </is>
@@ -7729,7 +7784,7 @@
         </is>
       </c>
     </row>
-    <row r="119" ht="75" customHeight="1" s="26">
+    <row r="119" ht="75" customHeight="1" s="41">
       <c r="A119" s="8" t="inlineStr">
         <is>
           <t>apartments_area_4k</t>
@@ -7770,12 +7825,12 @@
           <t>01.05.2026</t>
         </is>
       </c>
-      <c r="I119" s="38" t="inlineStr">
+      <c r="I119" s="48" t="inlineStr">
         <is>
           <t>май 2026</t>
         </is>
       </c>
-      <c r="J119" s="39" t="inlineStr">
+      <c r="J119" s="49" t="inlineStr">
         <is>
           <t>✅ Актуально</t>
         </is>
@@ -7789,7 +7844,7 @@
         </is>
       </c>
     </row>
-    <row r="120" ht="75" customHeight="1" s="26">
+    <row r="120" ht="75" customHeight="1" s="41">
       <c r="A120" s="8" t="inlineStr">
         <is>
           <t>apartments_area_total</t>
@@ -7830,12 +7885,12 @@
           <t>01.05.2026</t>
         </is>
       </c>
-      <c r="I120" s="38" t="inlineStr">
+      <c r="I120" s="48" t="inlineStr">
         <is>
           <t>май 2026</t>
         </is>
       </c>
-      <c r="J120" s="39" t="inlineStr">
+      <c r="J120" s="49" t="inlineStr">
         <is>
           <t>✅ Актуально</t>
         </is>
@@ -7849,7 +7904,7 @@
         </is>
       </c>
     </row>
-    <row r="121" ht="75" customHeight="1" s="26">
+    <row r="121" ht="75" customHeight="1" s="41">
       <c r="A121" s="8" t="inlineStr">
         <is>
           <t>apartments_count_1k</t>
@@ -7890,12 +7945,12 @@
           <t>01.05.2026</t>
         </is>
       </c>
-      <c r="I121" s="38" t="inlineStr">
+      <c r="I121" s="48" t="inlineStr">
         <is>
           <t>май 2026</t>
         </is>
       </c>
-      <c r="J121" s="39" t="inlineStr">
+      <c r="J121" s="49" t="inlineStr">
         <is>
           <t>✅ Актуально</t>
         </is>
@@ -7909,7 +7964,7 @@
         </is>
       </c>
     </row>
-    <row r="122" ht="75" customHeight="1" s="26">
+    <row r="122" ht="75" customHeight="1" s="41">
       <c r="A122" s="8" t="inlineStr">
         <is>
           <t>apartments_count_2k</t>
@@ -7950,12 +8005,12 @@
           <t>01.05.2026</t>
         </is>
       </c>
-      <c r="I122" s="38" t="inlineStr">
+      <c r="I122" s="48" t="inlineStr">
         <is>
           <t>май 2026</t>
         </is>
       </c>
-      <c r="J122" s="39" t="inlineStr">
+      <c r="J122" s="49" t="inlineStr">
         <is>
           <t>✅ Актуально</t>
         </is>
@@ -7969,7 +8024,7 @@
         </is>
       </c>
     </row>
-    <row r="123" ht="75" customHeight="1" s="26">
+    <row r="123" ht="75" customHeight="1" s="41">
       <c r="A123" s="8" t="inlineStr">
         <is>
           <t>apartments_count_3k</t>
@@ -8010,12 +8065,12 @@
           <t>01.05.2026</t>
         </is>
       </c>
-      <c r="I123" s="38" t="inlineStr">
+      <c r="I123" s="48" t="inlineStr">
         <is>
           <t>май 2026</t>
         </is>
       </c>
-      <c r="J123" s="39" t="inlineStr">
+      <c r="J123" s="49" t="inlineStr">
         <is>
           <t>✅ Актуально</t>
         </is>
@@ -8029,7 +8084,7 @@
         </is>
       </c>
     </row>
-    <row r="124" ht="75" customHeight="1" s="26">
+    <row r="124" ht="75" customHeight="1" s="41">
       <c r="A124" s="8" t="inlineStr">
         <is>
           <t>apartments_count_4k</t>
@@ -8070,12 +8125,12 @@
           <t>01.05.2026</t>
         </is>
       </c>
-      <c r="I124" s="38" t="inlineStr">
+      <c r="I124" s="48" t="inlineStr">
         <is>
           <t>май 2026</t>
         </is>
       </c>
-      <c r="J124" s="39" t="inlineStr">
+      <c r="J124" s="49" t="inlineStr">
         <is>
           <t>✅ Актуально</t>
         </is>
@@ -8089,7 +8144,7 @@
         </is>
       </c>
     </row>
-    <row r="125" ht="75" customHeight="1" s="26">
+    <row r="125" ht="75" customHeight="1" s="41">
       <c r="A125" s="8" t="inlineStr">
         <is>
           <t>apartments_count_total</t>
@@ -8130,12 +8185,12 @@
           <t>01.05.2026</t>
         </is>
       </c>
-      <c r="I125" s="38" t="inlineStr">
+      <c r="I125" s="48" t="inlineStr">
         <is>
           <t>май 2026</t>
         </is>
       </c>
-      <c r="J125" s="39" t="inlineStr">
+      <c r="J125" s="49" t="inlineStr">
         <is>
           <t>✅ Актуально</t>
         </is>
@@ -8149,7 +8204,7 @@
         </is>
       </c>
     </row>
-    <row r="126" ht="75" customHeight="1" s="26">
+    <row r="126" ht="75" customHeight="1" s="41">
       <c r="A126" s="8" t="inlineStr">
         <is>
           <t>apartments_share_1k</t>
@@ -8190,12 +8245,12 @@
           <t>01.05.2026</t>
         </is>
       </c>
-      <c r="I126" s="38" t="inlineStr">
+      <c r="I126" s="48" t="inlineStr">
         <is>
           <t>май 2026</t>
         </is>
       </c>
-      <c r="J126" s="39" t="inlineStr">
+      <c r="J126" s="49" t="inlineStr">
         <is>
           <t>✅ Актуально</t>
         </is>
@@ -8209,7 +8264,7 @@
         </is>
       </c>
     </row>
-    <row r="127" ht="75" customHeight="1" s="26">
+    <row r="127" ht="75" customHeight="1" s="41">
       <c r="A127" s="8" t="inlineStr">
         <is>
           <t>apartments_share_2k</t>
@@ -8250,12 +8305,12 @@
           <t>01.05.2026</t>
         </is>
       </c>
-      <c r="I127" s="38" t="inlineStr">
+      <c r="I127" s="48" t="inlineStr">
         <is>
           <t>май 2026</t>
         </is>
       </c>
-      <c r="J127" s="39" t="inlineStr">
+      <c r="J127" s="49" t="inlineStr">
         <is>
           <t>✅ Актуально</t>
         </is>
@@ -8269,7 +8324,7 @@
         </is>
       </c>
     </row>
-    <row r="128" ht="75" customHeight="1" s="26">
+    <row r="128" ht="75" customHeight="1" s="41">
       <c r="A128" s="8" t="inlineStr">
         <is>
           <t>apartments_share_3k</t>
@@ -8310,12 +8365,12 @@
           <t>01.05.2026</t>
         </is>
       </c>
-      <c r="I128" s="38" t="inlineStr">
+      <c r="I128" s="48" t="inlineStr">
         <is>
           <t>май 2026</t>
         </is>
       </c>
-      <c r="J128" s="39" t="inlineStr">
+      <c r="J128" s="49" t="inlineStr">
         <is>
           <t>✅ Актуально</t>
         </is>
@@ -8329,7 +8384,7 @@
         </is>
       </c>
     </row>
-    <row r="129" ht="75" customHeight="1" s="26">
+    <row r="129" ht="75" customHeight="1" s="41">
       <c r="A129" s="8" t="inlineStr">
         <is>
           <t>apartments_share_4k</t>
@@ -8370,12 +8425,12 @@
           <t>01.05.2026</t>
         </is>
       </c>
-      <c r="I129" s="38" t="inlineStr">
+      <c r="I129" s="48" t="inlineStr">
         <is>
           <t>май 2026</t>
         </is>
       </c>
-      <c r="J129" s="39" t="inlineStr">
+      <c r="J129" s="49" t="inlineStr">
         <is>
           <t>✅ Актуально</t>
         </is>
@@ -8389,7 +8444,7 @@
         </is>
       </c>
     </row>
-    <row r="130" ht="75" customHeight="1" s="26">
+    <row r="130" ht="75" customHeight="1" s="41">
       <c r="A130" s="8" t="inlineStr">
         <is>
           <t>apt_area</t>
@@ -8430,12 +8485,12 @@
           <t>01.04.2026</t>
         </is>
       </c>
-      <c r="I130" s="38" t="inlineStr">
+      <c r="I130" s="48" t="inlineStr">
         <is>
           <t>апрель 2026</t>
         </is>
       </c>
-      <c r="J130" s="39" t="inlineStr">
+      <c r="J130" s="49" t="inlineStr">
         <is>
           <t>✅ Актуально</t>
         </is>
@@ -8449,7 +8504,7 @@
         </is>
       </c>
     </row>
-    <row r="131" ht="75" customHeight="1" s="26">
+    <row r="131" ht="75" customHeight="1" s="41">
       <c r="A131" s="8" t="inlineStr">
         <is>
           <t>apt_budget</t>
@@ -8490,12 +8545,12 @@
           <t>01.04.2026</t>
         </is>
       </c>
-      <c r="I131" s="38" t="inlineStr">
+      <c r="I131" s="48" t="inlineStr">
         <is>
           <t>апрель 2026</t>
         </is>
       </c>
-      <c r="J131" s="39" t="inlineStr">
+      <c r="J131" s="49" t="inlineStr">
         <is>
           <t>✅ Актуально</t>
         </is>
@@ -8509,7 +8564,7 @@
         </is>
       </c>
     </row>
-    <row r="132" ht="75" customHeight="1" s="26">
+    <row r="132" ht="75" customHeight="1" s="41">
       <c r="A132" s="8" t="inlineStr">
         <is>
           <t>mm_budget</t>
@@ -8550,12 +8605,12 @@
           <t>01.04.2026</t>
         </is>
       </c>
-      <c r="I132" s="38" t="inlineStr">
+      <c r="I132" s="48" t="inlineStr">
         <is>
           <t>апрель 2026</t>
         </is>
       </c>
-      <c r="J132" s="39" t="inlineStr">
+      <c r="J132" s="49" t="inlineStr">
         <is>
           <t>✅ Актуально</t>
         </is>
@@ -8569,7 +8624,7 @@
         </is>
       </c>
     </row>
-    <row r="133" ht="75" customHeight="1" s="26">
+    <row r="133" ht="75" customHeight="1" s="41">
       <c r="A133" s="8" t="inlineStr">
         <is>
           <t>mm_price</t>
@@ -8610,12 +8665,12 @@
           <t>01.04.2026</t>
         </is>
       </c>
-      <c r="I133" s="38" t="inlineStr">
+      <c r="I133" s="48" t="inlineStr">
         <is>
           <t>апрель 2026</t>
         </is>
       </c>
-      <c r="J133" s="39" t="inlineStr">
+      <c r="J133" s="49" t="inlineStr">
         <is>
           <t>✅ Актуально</t>
         </is>
@@ -8629,7 +8684,7 @@
         </is>
       </c>
     </row>
-    <row r="134" ht="75" customHeight="1" s="26">
+    <row r="134" ht="75" customHeight="1" s="41">
       <c r="A134" s="8" t="inlineStr">
         <is>
           <t>sales_apt_sqm</t>
@@ -8670,12 +8725,12 @@
           <t>01.04.2026</t>
         </is>
       </c>
-      <c r="I134" s="38" t="inlineStr">
+      <c r="I134" s="48" t="inlineStr">
         <is>
           <t>апрель 2026</t>
         </is>
       </c>
-      <c r="J134" s="39" t="inlineStr">
+      <c r="J134" s="49" t="inlineStr">
         <is>
           <t>✅ Актуально</t>
         </is>
@@ -8689,7 +8744,7 @@
         </is>
       </c>
     </row>
-    <row r="135" ht="75" customHeight="1" s="26">
+    <row r="135" ht="75" customHeight="1" s="41">
       <c r="A135" s="8" t="inlineStr">
         <is>
           <t>uc_absorption_active</t>
@@ -8730,12 +8785,12 @@
           <t>01.04.2026</t>
         </is>
       </c>
-      <c r="I135" s="38" t="inlineStr">
+      <c r="I135" s="48" t="inlineStr">
         <is>
           <t>апрель 2026</t>
         </is>
       </c>
-      <c r="J135" s="39" t="inlineStr">
+      <c r="J135" s="49" t="inlineStr">
         <is>
           <t>✅ Актуально</t>
         </is>
@@ -8749,7 +8804,7 @@
         </is>
       </c>
     </row>
-    <row r="136" ht="75" customHeight="1" s="26">
+    <row r="136" ht="75" customHeight="1" s="41">
       <c r="A136" s="8" t="inlineStr">
         <is>
           <t>uc_absorption_total</t>
@@ -8790,12 +8845,12 @@
           <t>01.04.2026</t>
         </is>
       </c>
-      <c r="I136" s="38" t="inlineStr">
+      <c r="I136" s="48" t="inlineStr">
         <is>
           <t>апрель 2026</t>
         </is>
       </c>
-      <c r="J136" s="39" t="inlineStr">
+      <c r="J136" s="49" t="inlineStr">
         <is>
           <t>✅ Актуально</t>
         </is>
@@ -8809,7 +8864,7 @@
         </is>
       </c>
     </row>
-    <row r="137" ht="75" customHeight="1" s="26">
+    <row r="137" ht="75" customHeight="1" s="41">
       <c r="A137" s="8" t="inlineStr">
         <is>
           <t>uc_area_active</t>
@@ -8850,12 +8905,12 @@
           <t>01.05.2026</t>
         </is>
       </c>
-      <c r="I137" s="38" t="inlineStr">
+      <c r="I137" s="48" t="inlineStr">
         <is>
           <t>май 2026</t>
         </is>
       </c>
-      <c r="J137" s="39" t="inlineStr">
+      <c r="J137" s="49" t="inlineStr">
         <is>
           <t>✅ Актуально</t>
         </is>
@@ -8869,7 +8924,7 @@
         </is>
       </c>
     </row>
-    <row r="138" ht="75" customHeight="1" s="26">
+    <row r="138" ht="75" customHeight="1" s="41">
       <c r="A138" s="8" t="inlineStr">
         <is>
           <t>uc_area_total</t>
@@ -8910,12 +8965,12 @@
           <t>01.05.2026</t>
         </is>
       </c>
-      <c r="I138" s="38" t="inlineStr">
+      <c r="I138" s="48" t="inlineStr">
         <is>
           <t>май 2026</t>
         </is>
       </c>
-      <c r="J138" s="39" t="inlineStr">
+      <c r="J138" s="49" t="inlineStr">
         <is>
           <t>✅ Актуально</t>
         </is>
@@ -8929,7 +8984,7 @@
         </is>
       </c>
     </row>
-    <row r="139" ht="75" customHeight="1" s="26">
+    <row r="139" ht="75" customHeight="1" s="41">
       <c r="A139" s="8" t="inlineStr">
         <is>
           <t>uc_dev_activity</t>
@@ -8970,12 +9025,12 @@
           <t>01.01.2024</t>
         </is>
       </c>
-      <c r="I139" s="40" t="inlineStr">
+      <c r="I139" s="50" t="inlineStr">
         <is>
           <t>2024</t>
         </is>
       </c>
-      <c r="J139" s="41" t="inlineStr">
+      <c r="J139" s="51" t="inlineStr">
         <is>
           <t>⚠️ Просрочено</t>
         </is>
@@ -8989,7 +9044,7 @@
         </is>
       </c>
     </row>
-    <row r="140" ht="75" customHeight="1" s="26">
+    <row r="140" ht="75" customHeight="1" s="41">
       <c r="A140" s="8" t="inlineStr">
         <is>
           <t>uc_new_active</t>
@@ -9030,12 +9085,12 @@
           <t>01.04.2026</t>
         </is>
       </c>
-      <c r="I140" s="38" t="inlineStr">
+      <c r="I140" s="48" t="inlineStr">
         <is>
           <t>апрель 2026</t>
         </is>
       </c>
-      <c r="J140" s="39" t="inlineStr">
+      <c r="J140" s="49" t="inlineStr">
         <is>
           <t>✅ Актуально</t>
         </is>
@@ -9049,7 +9104,7 @@
         </is>
       </c>
     </row>
-    <row r="141" ht="75" customHeight="1" s="26">
+    <row r="141" ht="75" customHeight="1" s="41">
       <c r="A141" s="8" t="inlineStr">
         <is>
           <t>uc_new_total</t>
@@ -9090,12 +9145,12 @@
           <t>01.04.2026</t>
         </is>
       </c>
-      <c r="I141" s="38" t="inlineStr">
+      <c r="I141" s="48" t="inlineStr">
         <is>
           <t>апрель 2026</t>
         </is>
       </c>
-      <c r="J141" s="39" t="inlineStr">
+      <c r="J141" s="49" t="inlineStr">
         <is>
           <t>✅ Актуально</t>
         </is>
@@ -9109,7 +9164,7 @@
         </is>
       </c>
     </row>
-    <row r="142" ht="75" customHeight="1" s="26">
+    <row r="142" ht="75" customHeight="1" s="41">
       <c r="A142" s="8" t="inlineStr">
         <is>
           <t>uc_new_vs_input_active</t>
@@ -9150,12 +9205,12 @@
           <t>01.04.2026</t>
         </is>
       </c>
-      <c r="I142" s="38" t="inlineStr">
+      <c r="I142" s="48" t="inlineStr">
         <is>
           <t>апрель 2026</t>
         </is>
       </c>
-      <c r="J142" s="39" t="inlineStr">
+      <c r="J142" s="49" t="inlineStr">
         <is>
           <t>✅ Актуально</t>
         </is>
@@ -9169,7 +9224,7 @@
         </is>
       </c>
     </row>
-    <row r="143" ht="75" customHeight="1" s="26">
+    <row r="143" ht="75" customHeight="1" s="41">
       <c r="A143" s="8" t="inlineStr">
         <is>
           <t>uc_new_vs_input_total</t>
@@ -9210,12 +9265,12 @@
           <t>01.04.2026</t>
         </is>
       </c>
-      <c r="I143" s="38" t="inlineStr">
+      <c r="I143" s="48" t="inlineStr">
         <is>
           <t>апрель 2026</t>
         </is>
       </c>
-      <c r="J143" s="39" t="inlineStr">
+      <c r="J143" s="49" t="inlineStr">
         <is>
           <t>✅ Актуально</t>
         </is>
@@ -9229,7 +9284,7 @@
         </is>
       </c>
     </row>
-    <row r="144" ht="75" customHeight="1" s="26">
+    <row r="144" ht="75" customHeight="1" s="41">
       <c r="A144" s="8" t="inlineStr">
         <is>
           <t>uc_new_vs_sales_active</t>
@@ -9270,12 +9325,12 @@
           <t>01.04.2026</t>
         </is>
       </c>
-      <c r="I144" s="38" t="inlineStr">
+      <c r="I144" s="48" t="inlineStr">
         <is>
           <t>апрель 2026</t>
         </is>
       </c>
-      <c r="J144" s="39" t="inlineStr">
+      <c r="J144" s="49" t="inlineStr">
         <is>
           <t>✅ Актуально</t>
         </is>
@@ -9289,7 +9344,7 @@
         </is>
       </c>
     </row>
-    <row r="145" ht="75" customHeight="1" s="26">
+    <row r="145" ht="75" customHeight="1" s="41">
       <c r="A145" s="8" t="inlineStr">
         <is>
           <t>uc_new_vs_sales_total</t>
@@ -9330,12 +9385,12 @@
           <t>01.04.2026</t>
         </is>
       </c>
-      <c r="I145" s="38" t="inlineStr">
+      <c r="I145" s="48" t="inlineStr">
         <is>
           <t>апрель 2026</t>
         </is>
       </c>
-      <c r="J145" s="39" t="inlineStr">
+      <c r="J145" s="49" t="inlineStr">
         <is>
           <t>✅ Актуально</t>
         </is>
@@ -9349,7 +9404,7 @@
         </is>
       </c>
     </row>
-    <row r="146" ht="75" customHeight="1" s="26">
+    <row r="146" ht="75" customHeight="1" s="41">
       <c r="A146" s="8" t="inlineStr">
         <is>
           <t>uc_sold_vs_ready</t>
@@ -9390,12 +9445,12 @@
           <t>01.05.2026</t>
         </is>
       </c>
-      <c r="I146" s="38" t="inlineStr">
+      <c r="I146" s="48" t="inlineStr">
         <is>
           <t>май 2026</t>
         </is>
       </c>
-      <c r="J146" s="39" t="inlineStr">
+      <c r="J146" s="49" t="inlineStr">
         <is>
           <t>✅ Актуально</t>
         </is>
@@ -9409,7 +9464,7 @@
         </is>
       </c>
     </row>
-    <row r="147" ht="75" customHeight="1" s="26">
+    <row r="147" ht="75" customHeight="1" s="41">
       <c r="A147" s="8" t="inlineStr">
         <is>
           <t>uc_stock_years_active</t>
@@ -9450,12 +9505,12 @@
           <t>01.04.2026</t>
         </is>
       </c>
-      <c r="I147" s="38" t="inlineStr">
+      <c r="I147" s="48" t="inlineStr">
         <is>
           <t>апрель 2026</t>
         </is>
       </c>
-      <c r="J147" s="39" t="inlineStr">
+      <c r="J147" s="49" t="inlineStr">
         <is>
           <t>✅ Актуально</t>
         </is>
@@ -9469,7 +9524,7 @@
         </is>
       </c>
     </row>
-    <row r="148" ht="75" customHeight="1" s="26">
+    <row r="148" ht="75" customHeight="1" s="41">
       <c r="A148" s="8" t="inlineStr">
         <is>
           <t>uc_stock_years_total</t>
@@ -9510,12 +9565,12 @@
           <t>01.04.2026</t>
         </is>
       </c>
-      <c r="I148" s="38" t="inlineStr">
+      <c r="I148" s="48" t="inlineStr">
         <is>
           <t>апрель 2026</t>
         </is>
       </c>
-      <c r="J148" s="39" t="inlineStr">
+      <c r="J148" s="49" t="inlineStr">
         <is>
           <t>✅ Актуально</t>
         </is>
@@ -9532,156 +9587,106 @@
     <row r="149"/>
     <row r="150"/>
     <row r="151">
-      <c r="A151" s="32" t="inlineStr">
+      <c r="A151" s="36" t="inlineStr">
         <is>
           <t>ЛЕГЕНДА:</t>
         </is>
       </c>
-      <c r="I151" s="42" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J151" s="43" t="inlineStr">
-        <is>
-          <t>❓ Неизвестно</t>
-        </is>
-      </c>
     </row>
     <row r="152">
-      <c r="A152" s="33" t="inlineStr">
+      <c r="A152" s="34" t="inlineStr">
         <is>
           <t>✅ Авто-парсер (работает) — запускается по расписанию, данные скачиваются автоматически</t>
         </is>
       </c>
-      <c r="B152" s="35" t="n"/>
-      <c r="C152" s="35" t="n"/>
-      <c r="D152" s="35" t="n"/>
-      <c r="E152" s="35" t="n"/>
-      <c r="F152" s="35" t="n"/>
-      <c r="G152" s="35" t="n"/>
-      <c r="H152" s="35" t="n"/>
-      <c r="I152" s="42" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J152" s="43" t="inlineStr">
-        <is>
-          <t>❓ Неизвестно</t>
-        </is>
-      </c>
-      <c r="K152" s="35" t="n"/>
-      <c r="L152" s="35" t="n"/>
-      <c r="M152" s="36" t="n"/>
+      <c r="B152" s="28" t="n"/>
+      <c r="C152" s="28" t="n"/>
+      <c r="D152" s="28" t="n"/>
+      <c r="E152" s="28" t="n"/>
+      <c r="F152" s="28" t="n"/>
+      <c r="G152" s="28" t="n"/>
+      <c r="H152" s="28" t="n"/>
+      <c r="I152" s="28" t="n"/>
+      <c r="J152" s="28" t="n"/>
+      <c r="K152" s="26" t="n"/>
+      <c r="L152" s="28" t="n"/>
+      <c r="M152" s="26" t="n"/>
     </row>
     <row r="153">
-      <c r="A153" s="28" t="inlineStr">
+      <c r="A153" s="27" t="inlineStr">
         <is>
           <t>🔄 Авто-парсер (ручная загрузка) — оркестрация работает, но Excel-файлы ДОМ.РФ нужно загрузить вручную в domrf_data/ перед запуском</t>
         </is>
       </c>
-      <c r="B153" s="35" t="n"/>
-      <c r="C153" s="35" t="n"/>
-      <c r="D153" s="35" t="n"/>
-      <c r="E153" s="35" t="n"/>
-      <c r="F153" s="35" t="n"/>
-      <c r="G153" s="35" t="n"/>
-      <c r="H153" s="35" t="n"/>
-      <c r="I153" s="42" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J153" s="43" t="inlineStr">
-        <is>
-          <t>❓ Неизвестно</t>
-        </is>
-      </c>
-      <c r="K153" s="35" t="n"/>
-      <c r="L153" s="35" t="n"/>
-      <c r="M153" s="36" t="n"/>
+      <c r="B153" s="28" t="n"/>
+      <c r="C153" s="28" t="n"/>
+      <c r="D153" s="28" t="n"/>
+      <c r="E153" s="28" t="n"/>
+      <c r="F153" s="28" t="n"/>
+      <c r="G153" s="28" t="n"/>
+      <c r="H153" s="28" t="n"/>
+      <c r="I153" s="28" t="n"/>
+      <c r="J153" s="28" t="n"/>
+      <c r="K153" s="26" t="n"/>
+      <c r="L153" s="28" t="n"/>
+      <c r="M153" s="26" t="n"/>
     </row>
     <row r="154">
-      <c r="A154" s="29" t="inlineStr">
+      <c r="A154" s="32" t="inlineStr">
         <is>
           <t>⚠️ Авто-парсер (нужна доработка) — парсер ещё не доработан</t>
         </is>
       </c>
-      <c r="B154" s="35" t="n"/>
-      <c r="C154" s="35" t="n"/>
-      <c r="D154" s="35" t="n"/>
-      <c r="E154" s="35" t="n"/>
-      <c r="F154" s="35" t="n"/>
-      <c r="G154" s="35" t="n"/>
-      <c r="H154" s="35" t="n"/>
-      <c r="I154" s="42" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J154" s="43" t="inlineStr">
-        <is>
-          <t>❓ Неизвестно</t>
-        </is>
-      </c>
-      <c r="K154" s="35" t="n"/>
-      <c r="L154" s="35" t="n"/>
-      <c r="M154" s="36" t="n"/>
+      <c r="B154" s="28" t="n"/>
+      <c r="C154" s="28" t="n"/>
+      <c r="D154" s="28" t="n"/>
+      <c r="E154" s="28" t="n"/>
+      <c r="F154" s="28" t="n"/>
+      <c r="G154" s="28" t="n"/>
+      <c r="H154" s="28" t="n"/>
+      <c r="I154" s="28" t="n"/>
+      <c r="J154" s="28" t="n"/>
+      <c r="K154" s="26" t="n"/>
+      <c r="L154" s="28" t="n"/>
+      <c r="M154" s="26" t="n"/>
     </row>
     <row r="155">
-      <c r="A155" s="27" t="inlineStr">
+      <c r="A155" s="35" t="inlineStr">
         <is>
           <t>🔧 Авто-расчёт (в scheduler) — calc_*.py / migration-скрипт запускается автоматически в составе job</t>
         </is>
       </c>
-      <c r="B155" s="35" t="n"/>
-      <c r="C155" s="35" t="n"/>
-      <c r="D155" s="35" t="n"/>
-      <c r="E155" s="35" t="n"/>
-      <c r="F155" s="35" t="n"/>
-      <c r="G155" s="35" t="n"/>
-      <c r="H155" s="35" t="n"/>
-      <c r="I155" s="42" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J155" s="43" t="inlineStr">
-        <is>
-          <t>❓ Неизвестно</t>
-        </is>
-      </c>
-      <c r="K155" s="35" t="n"/>
-      <c r="L155" s="35" t="n"/>
-      <c r="M155" s="36" t="n"/>
+      <c r="B155" s="28" t="n"/>
+      <c r="C155" s="28" t="n"/>
+      <c r="D155" s="28" t="n"/>
+      <c r="E155" s="28" t="n"/>
+      <c r="F155" s="28" t="n"/>
+      <c r="G155" s="28" t="n"/>
+      <c r="H155" s="28" t="n"/>
+      <c r="I155" s="28" t="n"/>
+      <c r="J155" s="28" t="n"/>
+      <c r="K155" s="26" t="n"/>
+      <c r="L155" s="28" t="n"/>
+      <c r="M155" s="26" t="n"/>
     </row>
     <row r="156">
-      <c r="A156" s="30" t="inlineStr">
+      <c r="A156" s="33" t="inlineStr">
         <is>
           <t>📝 Ручной расчёт — запускается вручную 1 раз в год</t>
         </is>
       </c>
-      <c r="B156" s="35" t="n"/>
-      <c r="C156" s="35" t="n"/>
-      <c r="D156" s="35" t="n"/>
-      <c r="E156" s="35" t="n"/>
-      <c r="F156" s="35" t="n"/>
-      <c r="G156" s="35" t="n"/>
-      <c r="H156" s="35" t="n"/>
-      <c r="I156" s="42" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J156" s="43" t="inlineStr">
-        <is>
-          <t>❓ Неизвестно</t>
-        </is>
-      </c>
-      <c r="K156" s="35" t="n"/>
-      <c r="L156" s="35" t="n"/>
-      <c r="M156" s="36" t="n"/>
+      <c r="B156" s="28" t="n"/>
+      <c r="C156" s="28" t="n"/>
+      <c r="D156" s="28" t="n"/>
+      <c r="E156" s="28" t="n"/>
+      <c r="F156" s="28" t="n"/>
+      <c r="G156" s="28" t="n"/>
+      <c r="H156" s="28" t="n"/>
+      <c r="I156" s="28" t="n"/>
+      <c r="J156" s="28" t="n"/>
+      <c r="K156" s="26" t="n"/>
+      <c r="L156" s="28" t="n"/>
+      <c r="M156" s="26" t="n"/>
     </row>
     <row r="157">
       <c r="A157" s="31" t="inlineStr">
@@ -9689,37 +9694,55 @@
           <t>❌ Нет автообновления — данные загружены однажды, нет парсера</t>
         </is>
       </c>
-      <c r="B157" s="35" t="n"/>
-      <c r="C157" s="35" t="n"/>
-      <c r="D157" s="35" t="n"/>
-      <c r="E157" s="35" t="n"/>
-      <c r="F157" s="35" t="n"/>
-      <c r="G157" s="35" t="n"/>
-      <c r="H157" s="35" t="n"/>
-      <c r="I157" s="42" t="inlineStr">
+      <c r="B157" s="28" t="n"/>
+      <c r="C157" s="28" t="n"/>
+      <c r="D157" s="28" t="n"/>
+      <c r="E157" s="28" t="n"/>
+      <c r="F157" s="28" t="n"/>
+      <c r="G157" s="28" t="n"/>
+      <c r="H157" s="28" t="n"/>
+      <c r="I157" s="28" t="n"/>
+      <c r="J157" s="28" t="n"/>
+      <c r="K157" s="26" t="n"/>
+      <c r="L157" s="28" t="n"/>
+      <c r="M157" s="26" t="n"/>
+    </row>
+    <row r="158"/>
+    <row r="159"/>
+    <row r="160"/>
+    <row r="161" ht="64" customHeight="1" s="41">
+      <c r="A161" s="40" t="inlineStr">
+        <is>
+          <t>команда для обновления статуса</t>
+        </is>
+      </c>
+      <c r="B161" s="40" t="inlineStr">
+        <is>
+          <t>source venv/bin/activate
+python migration/update_indicator_status.py</t>
+        </is>
+      </c>
+      <c r="I161" s="54" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J157" s="43" t="inlineStr">
+      <c r="J161" s="55" t="inlineStr">
         <is>
           <t>❓ Неизвестно</t>
         </is>
       </c>
-      <c r="K157" s="35" t="n"/>
-      <c r="L157" s="35" t="n"/>
-      <c r="M157" s="36" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="8">
     <mergeCell ref="A153:K153"/>
     <mergeCell ref="A157:K157"/>
     <mergeCell ref="A154:K154"/>
+    <mergeCell ref="A1:L1"/>
     <mergeCell ref="A156:K156"/>
     <mergeCell ref="A152:K152"/>
     <mergeCell ref="A155:K155"/>
     <mergeCell ref="A151:K151"/>
-    <mergeCell ref="A1:K1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -9734,18 +9757,18 @@
   <dimension ref="A1:H132"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
-    <col width="30" customWidth="1" style="26" min="1" max="1"/>
-    <col width="28" customWidth="1" style="26" min="2" max="2"/>
-    <col width="25" customWidth="1" style="26" min="3" max="3"/>
-    <col width="50" customWidth="1" style="26" min="4" max="4"/>
-    <col width="22" customWidth="1" style="26" min="5" max="5"/>
-    <col width="12" customWidth="1" style="26" min="6" max="6"/>
-    <col width="55" customWidth="1" style="26" min="7" max="7"/>
-    <col width="14" customWidth="1" style="26" min="8" max="8"/>
+    <col width="30" customWidth="1" style="41" min="1" max="1"/>
+    <col width="28" customWidth="1" style="41" min="2" max="2"/>
+    <col width="25" customWidth="1" style="41" min="3" max="3"/>
+    <col width="50" customWidth="1" style="41" min="4" max="4"/>
+    <col width="22" customWidth="1" style="41" min="5" max="5"/>
+    <col width="12" customWidth="1" style="41" min="6" max="6"/>
+    <col width="55" customWidth="1" style="41" min="7" max="7"/>
+    <col width="14" customWidth="1" style="41" min="8" max="8"/>
   </cols>
   <sheetData>
-    <row r="1" ht="16" customHeight="1" s="26">
-      <c r="A1" s="25" t="inlineStr">
+    <row r="1" ht="16" customHeight="1" s="41">
+      <c r="A1" s="38" t="inlineStr">
         <is>
           <t>⚙️ Автоматические парсеры — детали</t>
         </is>
@@ -9793,7 +9816,7 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="30" customHeight="1" s="26">
+    <row r="3" ht="30" customHeight="1" s="41">
       <c r="A3" s="11" t="inlineStr">
         <is>
           <t>domrf_web.py</t>
@@ -9835,7 +9858,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="30" customHeight="1" s="26">
+    <row r="4" ht="30" customHeight="1" s="41">
       <c r="A4" s="6" t="n"/>
       <c r="B4" s="6" t="n"/>
       <c r="C4" s="6" t="n"/>
@@ -9857,7 +9880,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="30" customHeight="1" s="26">
+    <row r="5" ht="30" customHeight="1" s="41">
       <c r="A5" s="6" t="n"/>
       <c r="B5" s="6" t="n"/>
       <c r="C5" s="6" t="n"/>
@@ -9879,7 +9902,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="30" customHeight="1" s="26">
+    <row r="6" ht="30" customHeight="1" s="41">
       <c r="A6" s="6" t="n"/>
       <c r="B6" s="6" t="n"/>
       <c r="C6" s="6" t="n"/>
@@ -9967,7 +9990,7 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="30" customHeight="1" s="26">
+    <row r="11" ht="30" customHeight="1" s="41">
       <c r="A11" s="11" t="inlineStr">
         <is>
           <t>fetch_rosreestr_ddu.py</t>
@@ -10009,7 +10032,7 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="30" customHeight="1" s="26">
+    <row r="13" ht="30" customHeight="1" s="41">
       <c r="A13" s="11" t="inlineStr">
         <is>
           <t>cbr.py</t>
@@ -10051,7 +10074,7 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="30" customHeight="1" s="26">
+    <row r="14" ht="30" customHeight="1" s="41">
       <c r="A14" s="6" t="n"/>
       <c r="B14" s="6" t="n"/>
       <c r="C14" s="6" t="n"/>
@@ -10161,7 +10184,7 @@
         </is>
       </c>
     </row>
-    <row r="19" ht="30" customHeight="1" s="26">
+    <row r="19" ht="30" customHeight="1" s="41">
       <c r="A19" s="6" t="n"/>
       <c r="B19" s="6" t="n"/>
       <c r="C19" s="6" t="n"/>
@@ -10183,7 +10206,7 @@
         </is>
       </c>
     </row>
-    <row r="20" ht="30" customHeight="1" s="26">
+    <row r="20" ht="30" customHeight="1" s="41">
       <c r="A20" s="6" t="n"/>
       <c r="B20" s="6" t="n"/>
       <c r="C20" s="6" t="n"/>
@@ -10249,7 +10272,7 @@
         </is>
       </c>
     </row>
-    <row r="23" ht="30" customHeight="1" s="26">
+    <row r="23" ht="30" customHeight="1" s="41">
       <c r="A23" s="6" t="n"/>
       <c r="B23" s="6" t="n"/>
       <c r="C23" s="6" t="n"/>
@@ -10271,7 +10294,7 @@
         </is>
       </c>
     </row>
-    <row r="24" ht="30" customHeight="1" s="26">
+    <row r="24" ht="30" customHeight="1" s="41">
       <c r="A24" s="6" t="n"/>
       <c r="B24" s="6" t="n"/>
       <c r="C24" s="6" t="n"/>
@@ -10293,7 +10316,7 @@
         </is>
       </c>
     </row>
-    <row r="25" ht="30" customHeight="1" s="26">
+    <row r="25" ht="30" customHeight="1" s="41">
       <c r="A25" s="6" t="n"/>
       <c r="B25" s="6" t="n"/>
       <c r="C25" s="6" t="n"/>
@@ -10337,7 +10360,7 @@
         </is>
       </c>
     </row>
-    <row r="27" ht="30" customHeight="1" s="26">
+    <row r="27" ht="30" customHeight="1" s="41">
       <c r="A27" s="6" t="n"/>
       <c r="B27" s="6" t="n"/>
       <c r="C27" s="6" t="n"/>
@@ -10359,7 +10382,7 @@
         </is>
       </c>
     </row>
-    <row r="28" ht="30" customHeight="1" s="26">
+    <row r="28" ht="30" customHeight="1" s="41">
       <c r="A28" s="6" t="n"/>
       <c r="B28" s="6" t="n"/>
       <c r="C28" s="6" t="n"/>
@@ -10381,7 +10404,7 @@
         </is>
       </c>
     </row>
-    <row r="29" ht="30" customHeight="1" s="26">
+    <row r="29" ht="30" customHeight="1" s="41">
       <c r="A29" s="6" t="n"/>
       <c r="B29" s="6" t="n"/>
       <c r="C29" s="6" t="n"/>
@@ -10403,7 +10426,7 @@
         </is>
       </c>
     </row>
-    <row r="30" ht="30" customHeight="1" s="26">
+    <row r="30" ht="30" customHeight="1" s="41">
       <c r="A30" s="6" t="n"/>
       <c r="B30" s="6" t="n"/>
       <c r="C30" s="6" t="n"/>
@@ -10425,7 +10448,7 @@
         </is>
       </c>
     </row>
-    <row r="31" ht="30" customHeight="1" s="26">
+    <row r="31" ht="30" customHeight="1" s="41">
       <c r="A31" s="6" t="n"/>
       <c r="B31" s="6" t="n"/>
       <c r="C31" s="6" t="n"/>
@@ -10447,7 +10470,7 @@
         </is>
       </c>
     </row>
-    <row r="32" ht="30" customHeight="1" s="26">
+    <row r="32" ht="30" customHeight="1" s="41">
       <c r="A32" s="6" t="n"/>
       <c r="B32" s="6" t="n"/>
       <c r="C32" s="6" t="n"/>
@@ -10469,7 +10492,7 @@
         </is>
       </c>
     </row>
-    <row r="33" ht="30" customHeight="1" s="26">
+    <row r="33" ht="30" customHeight="1" s="41">
       <c r="A33" s="6" t="n"/>
       <c r="B33" s="6" t="n"/>
       <c r="C33" s="6" t="n"/>
@@ -10491,7 +10514,7 @@
         </is>
       </c>
     </row>
-    <row r="34" ht="30" customHeight="1" s="26">
+    <row r="34" ht="30" customHeight="1" s="41">
       <c r="A34" s="6" t="n"/>
       <c r="B34" s="6" t="n"/>
       <c r="C34" s="6" t="n"/>
@@ -10513,7 +10536,7 @@
         </is>
       </c>
     </row>
-    <row r="35" ht="30" customHeight="1" s="26">
+    <row r="35" ht="30" customHeight="1" s="41">
       <c r="A35" s="6" t="n"/>
       <c r="B35" s="6" t="n"/>
       <c r="C35" s="6" t="n"/>
@@ -10535,7 +10558,7 @@
         </is>
       </c>
     </row>
-    <row r="36" ht="30" customHeight="1" s="26">
+    <row r="36" ht="30" customHeight="1" s="41">
       <c r="A36" s="6" t="n"/>
       <c r="B36" s="6" t="n"/>
       <c r="C36" s="6" t="n"/>
@@ -10601,7 +10624,7 @@
         </is>
       </c>
     </row>
-    <row r="39" ht="30" customHeight="1" s="26">
+    <row r="39" ht="30" customHeight="1" s="41">
       <c r="A39" s="6" t="n"/>
       <c r="B39" s="6" t="n"/>
       <c r="C39" s="6" t="n"/>
@@ -10623,7 +10646,7 @@
         </is>
       </c>
     </row>
-    <row r="40" ht="30" customHeight="1" s="26">
+    <row r="40" ht="30" customHeight="1" s="41">
       <c r="A40" s="6" t="n"/>
       <c r="B40" s="6" t="n"/>
       <c r="C40" s="6" t="n"/>
@@ -10645,7 +10668,7 @@
         </is>
       </c>
     </row>
-    <row r="41" ht="30" customHeight="1" s="26">
+    <row r="41" ht="30" customHeight="1" s="41">
       <c r="A41" s="6" t="n"/>
       <c r="B41" s="6" t="n"/>
       <c r="C41" s="6" t="n"/>
@@ -10667,7 +10690,7 @@
         </is>
       </c>
     </row>
-    <row r="42" ht="30" customHeight="1" s="26">
+    <row r="42" ht="30" customHeight="1" s="41">
       <c r="A42" s="6" t="n"/>
       <c r="B42" s="6" t="n"/>
       <c r="C42" s="6" t="n"/>
@@ -10689,7 +10712,7 @@
         </is>
       </c>
     </row>
-    <row r="43" ht="30" customHeight="1" s="26">
+    <row r="43" ht="30" customHeight="1" s="41">
       <c r="A43" s="6" t="n"/>
       <c r="B43" s="6" t="n"/>
       <c r="C43" s="6" t="n"/>
@@ -10711,7 +10734,7 @@
         </is>
       </c>
     </row>
-    <row r="44" ht="30" customHeight="1" s="26">
+    <row r="44" ht="30" customHeight="1" s="41">
       <c r="A44" s="6" t="n"/>
       <c r="B44" s="6" t="n"/>
       <c r="C44" s="6" t="n"/>
@@ -10733,7 +10756,7 @@
         </is>
       </c>
     </row>
-    <row r="45" ht="30" customHeight="1" s="26">
+    <row r="45" ht="30" customHeight="1" s="41">
       <c r="A45" s="6" t="n"/>
       <c r="B45" s="6" t="n"/>
       <c r="C45" s="6" t="n"/>
@@ -10755,7 +10778,7 @@
         </is>
       </c>
     </row>
-    <row r="46" ht="30" customHeight="1" s="26">
+    <row r="46" ht="30" customHeight="1" s="41">
       <c r="A46" s="6" t="n"/>
       <c r="B46" s="6" t="n"/>
       <c r="C46" s="6" t="n"/>
@@ -10799,7 +10822,7 @@
         </is>
       </c>
     </row>
-    <row r="48" ht="30" customHeight="1" s="26">
+    <row r="48" ht="30" customHeight="1" s="41">
       <c r="A48" s="6" t="n"/>
       <c r="B48" s="6" t="n"/>
       <c r="C48" s="6" t="n"/>
@@ -10821,7 +10844,7 @@
         </is>
       </c>
     </row>
-    <row r="49" ht="30" customHeight="1" s="26">
+    <row r="49" ht="30" customHeight="1" s="41">
       <c r="A49" s="6" t="n"/>
       <c r="B49" s="6" t="n"/>
       <c r="C49" s="6" t="n"/>
@@ -10843,7 +10866,7 @@
         </is>
       </c>
     </row>
-    <row r="50" ht="30" customHeight="1" s="26">
+    <row r="50" ht="30" customHeight="1" s="41">
       <c r="A50" s="6" t="n"/>
       <c r="B50" s="6" t="n"/>
       <c r="C50" s="6" t="n"/>
@@ -10865,7 +10888,7 @@
         </is>
       </c>
     </row>
-    <row r="51" ht="30" customHeight="1" s="26">
+    <row r="51" ht="30" customHeight="1" s="41">
       <c r="A51" s="6" t="n"/>
       <c r="B51" s="6" t="n"/>
       <c r="C51" s="6" t="n"/>
@@ -10887,7 +10910,7 @@
         </is>
       </c>
     </row>
-    <row r="52" ht="30" customHeight="1" s="26">
+    <row r="52" ht="30" customHeight="1" s="41">
       <c r="A52" s="6" t="n"/>
       <c r="B52" s="6" t="n"/>
       <c r="C52" s="6" t="n"/>
@@ -10909,7 +10932,7 @@
         </is>
       </c>
     </row>
-    <row r="53" ht="30" customHeight="1" s="26">
+    <row r="53" ht="30" customHeight="1" s="41">
       <c r="A53" s="6" t="n"/>
       <c r="B53" s="6" t="n"/>
       <c r="C53" s="6" t="n"/>
@@ -10931,7 +10954,7 @@
         </is>
       </c>
     </row>
-    <row r="54" ht="30" customHeight="1" s="26">
+    <row r="54" ht="30" customHeight="1" s="41">
       <c r="A54" s="6" t="n"/>
       <c r="B54" s="6" t="n"/>
       <c r="C54" s="6" t="n"/>
@@ -10953,7 +10976,7 @@
         </is>
       </c>
     </row>
-    <row r="55" ht="30" customHeight="1" s="26">
+    <row r="55" ht="30" customHeight="1" s="41">
       <c r="A55" s="6" t="n"/>
       <c r="B55" s="6" t="n"/>
       <c r="C55" s="6" t="n"/>
@@ -10975,7 +10998,7 @@
         </is>
       </c>
     </row>
-    <row r="56" ht="30" customHeight="1" s="26">
+    <row r="56" ht="30" customHeight="1" s="41">
       <c r="A56" s="6" t="n"/>
       <c r="B56" s="6" t="n"/>
       <c r="C56" s="6" t="n"/>
@@ -10997,7 +11020,7 @@
         </is>
       </c>
     </row>
-    <row r="57" ht="30" customHeight="1" s="26">
+    <row r="57" ht="30" customHeight="1" s="41">
       <c r="A57" s="6" t="n"/>
       <c r="B57" s="6" t="n"/>
       <c r="C57" s="6" t="n"/>
@@ -11019,7 +11042,7 @@
         </is>
       </c>
     </row>
-    <row r="58" ht="30" customHeight="1" s="26">
+    <row r="58" ht="30" customHeight="1" s="41">
       <c r="A58" s="6" t="n"/>
       <c r="B58" s="6" t="n"/>
       <c r="C58" s="6" t="n"/>
@@ -11041,7 +11064,7 @@
         </is>
       </c>
     </row>
-    <row r="59" ht="30" customHeight="1" s="26">
+    <row r="59" ht="30" customHeight="1" s="41">
       <c r="A59" s="6" t="n"/>
       <c r="B59" s="6" t="n"/>
       <c r="C59" s="6" t="n"/>
@@ -11063,7 +11086,7 @@
         </is>
       </c>
     </row>
-    <row r="60" ht="30" customHeight="1" s="26">
+    <row r="60" ht="30" customHeight="1" s="41">
       <c r="A60" s="6" t="n"/>
       <c r="B60" s="6" t="n"/>
       <c r="C60" s="6" t="n"/>
@@ -11085,7 +11108,7 @@
         </is>
       </c>
     </row>
-    <row r="61" ht="30" customHeight="1" s="26">
+    <row r="61" ht="30" customHeight="1" s="41">
       <c r="A61" s="6" t="n"/>
       <c r="B61" s="6" t="n"/>
       <c r="C61" s="6" t="n"/>
@@ -11107,7 +11130,7 @@
         </is>
       </c>
     </row>
-    <row r="62" ht="30" customHeight="1" s="26">
+    <row r="62" ht="30" customHeight="1" s="41">
       <c r="A62" s="6" t="n"/>
       <c r="B62" s="6" t="n"/>
       <c r="C62" s="6" t="n"/>
@@ -11129,7 +11152,7 @@
         </is>
       </c>
     </row>
-    <row r="63" ht="30" customHeight="1" s="26">
+    <row r="63" ht="30" customHeight="1" s="41">
       <c r="A63" s="6" t="n"/>
       <c r="B63" s="6" t="n"/>
       <c r="C63" s="6" t="n"/>
@@ -11239,7 +11262,7 @@
         </is>
       </c>
     </row>
-    <row r="69" ht="30" customHeight="1" s="26">
+    <row r="69" ht="30" customHeight="1" s="41">
       <c r="A69" s="11" t="inlineStr">
         <is>
           <t>rosstat.py + fetch_fedstat.py</t>
@@ -11479,7 +11502,7 @@
         </is>
       </c>
     </row>
-    <row r="79" ht="30" customHeight="1" s="26">
+    <row r="79" ht="30" customHeight="1" s="41">
       <c r="A79" s="6" t="n"/>
       <c r="B79" s="6" t="n"/>
       <c r="C79" s="6" t="n"/>
@@ -11501,7 +11524,7 @@
         </is>
       </c>
     </row>
-    <row r="80" ht="30" customHeight="1" s="26">
+    <row r="80" ht="30" customHeight="1" s="41">
       <c r="A80" s="6" t="n"/>
       <c r="B80" s="6" t="n"/>
       <c r="C80" s="6" t="n"/>
@@ -11567,7 +11590,7 @@
         </is>
       </c>
     </row>
-    <row r="83" ht="30" customHeight="1" s="26">
+    <row r="83" ht="30" customHeight="1" s="41">
       <c r="A83" s="6" t="n"/>
       <c r="B83" s="6" t="n"/>
       <c r="C83" s="6" t="n"/>
@@ -11589,7 +11612,7 @@
         </is>
       </c>
     </row>
-    <row r="84" ht="30" customHeight="1" s="26">
+    <row r="84" ht="30" customHeight="1" s="41">
       <c r="A84" s="6" t="n"/>
       <c r="B84" s="6" t="n"/>
       <c r="C84" s="6" t="n"/>
@@ -11611,7 +11634,7 @@
         </is>
       </c>
     </row>
-    <row r="85" ht="30" customHeight="1" s="26">
+    <row r="85" ht="30" customHeight="1" s="41">
       <c r="A85" s="6" t="n"/>
       <c r="B85" s="6" t="n"/>
       <c r="C85" s="6" t="n"/>
@@ -11655,7 +11678,7 @@
         </is>
       </c>
     </row>
-    <row r="88" ht="30" customHeight="1" s="26">
+    <row r="88" ht="30" customHeight="1" s="41">
       <c r="A88" s="11" t="inlineStr">
         <is>
           <t>fetch_income_rosstat.py</t>
@@ -11719,7 +11742,7 @@
         </is>
       </c>
     </row>
-    <row r="91" ht="30" customHeight="1" s="26">
+    <row r="91" ht="30" customHeight="1" s="41">
       <c r="A91" s="12" t="inlineStr">
         <is>
           <t>domrf.py (оркестратор)</t>
@@ -11761,7 +11784,7 @@
         </is>
       </c>
     </row>
-    <row r="92" ht="30" customHeight="1" s="26">
+    <row r="92" ht="30" customHeight="1" s="41">
       <c r="A92" s="9" t="n"/>
       <c r="B92" s="9" t="n"/>
       <c r="C92" s="9" t="n"/>
@@ -11783,7 +11806,7 @@
         </is>
       </c>
     </row>
-    <row r="93" ht="30" customHeight="1" s="26">
+    <row r="93" ht="30" customHeight="1" s="41">
       <c r="A93" s="9" t="n"/>
       <c r="B93" s="9" t="n"/>
       <c r="C93" s="9" t="n"/>
@@ -11805,7 +11828,7 @@
         </is>
       </c>
     </row>
-    <row r="94" ht="30" customHeight="1" s="26">
+    <row r="94" ht="30" customHeight="1" s="41">
       <c r="A94" s="9" t="n"/>
       <c r="B94" s="9" t="n"/>
       <c r="C94" s="9" t="n"/>
@@ -11827,7 +11850,7 @@
         </is>
       </c>
     </row>
-    <row r="95" ht="30" customHeight="1" s="26">
+    <row r="95" ht="30" customHeight="1" s="41">
       <c r="A95" s="9" t="n"/>
       <c r="B95" s="9" t="n"/>
       <c r="C95" s="9" t="n"/>
@@ -11849,7 +11872,7 @@
         </is>
       </c>
     </row>
-    <row r="96" ht="30" customHeight="1" s="26">
+    <row r="96" ht="30" customHeight="1" s="41">
       <c r="A96" s="9" t="n"/>
       <c r="B96" s="9" t="n"/>
       <c r="C96" s="9" t="n"/>
@@ -11871,7 +11894,7 @@
         </is>
       </c>
     </row>
-    <row r="97" ht="30" customHeight="1" s="26">
+    <row r="97" ht="30" customHeight="1" s="41">
       <c r="A97" s="9" t="n"/>
       <c r="B97" s="9" t="n"/>
       <c r="C97" s="9" t="n"/>
@@ -11893,7 +11916,7 @@
         </is>
       </c>
     </row>
-    <row r="98" ht="30" customHeight="1" s="26">
+    <row r="98" ht="30" customHeight="1" s="41">
       <c r="A98" s="9" t="n"/>
       <c r="B98" s="9" t="n"/>
       <c r="C98" s="9" t="n"/>
@@ -11915,7 +11938,7 @@
         </is>
       </c>
     </row>
-    <row r="99" ht="30" customHeight="1" s="26">
+    <row r="99" ht="30" customHeight="1" s="41">
       <c r="A99" s="9" t="n"/>
       <c r="B99" s="9" t="n"/>
       <c r="C99" s="9" t="n"/>
@@ -11937,7 +11960,7 @@
         </is>
       </c>
     </row>
-    <row r="100" ht="30" customHeight="1" s="26">
+    <row r="100" ht="30" customHeight="1" s="41">
       <c r="A100" s="9" t="n"/>
       <c r="B100" s="9" t="n"/>
       <c r="C100" s="9" t="n"/>
@@ -11959,7 +11982,7 @@
         </is>
       </c>
     </row>
-    <row r="101" ht="30" customHeight="1" s="26">
+    <row r="101" ht="30" customHeight="1" s="41">
       <c r="A101" s="9" t="n"/>
       <c r="B101" s="9" t="n"/>
       <c r="C101" s="9" t="n"/>
@@ -11981,7 +12004,7 @@
         </is>
       </c>
     </row>
-    <row r="102" ht="30" customHeight="1" s="26">
+    <row r="102" ht="30" customHeight="1" s="41">
       <c r="A102" s="9" t="n"/>
       <c r="B102" s="9" t="n"/>
       <c r="C102" s="9" t="n"/>
@@ -12003,7 +12026,7 @@
         </is>
       </c>
     </row>
-    <row r="103" ht="30" customHeight="1" s="26">
+    <row r="103" ht="30" customHeight="1" s="41">
       <c r="A103" s="9" t="n"/>
       <c r="B103" s="9" t="n"/>
       <c r="C103" s="9" t="n"/>
@@ -12025,7 +12048,7 @@
         </is>
       </c>
     </row>
-    <row r="104" ht="30" customHeight="1" s="26">
+    <row r="104" ht="30" customHeight="1" s="41">
       <c r="A104" s="9" t="n"/>
       <c r="B104" s="9" t="n"/>
       <c r="C104" s="9" t="n"/>
@@ -12259,7 +12282,7 @@
         </is>
       </c>
     </row>
-    <row r="115" ht="30" customHeight="1" s="26">
+    <row r="115" ht="30" customHeight="1" s="41">
       <c r="A115" s="9" t="n"/>
       <c r="B115" s="9" t="n"/>
       <c r="C115" s="9" t="n"/>
@@ -12281,7 +12304,7 @@
         </is>
       </c>
     </row>
-    <row r="116" ht="30" customHeight="1" s="26">
+    <row r="116" ht="30" customHeight="1" s="41">
       <c r="A116" s="9" t="n"/>
       <c r="B116" s="9" t="n"/>
       <c r="C116" s="9" t="n"/>
@@ -12347,7 +12370,7 @@
         </is>
       </c>
     </row>
-    <row r="119" ht="30" customHeight="1" s="26">
+    <row r="119" ht="30" customHeight="1" s="41">
       <c r="A119" s="9" t="n"/>
       <c r="B119" s="9" t="n"/>
       <c r="C119" s="9" t="n"/>
@@ -12369,7 +12392,7 @@
         </is>
       </c>
     </row>
-    <row r="120" ht="30" customHeight="1" s="26">
+    <row r="120" ht="30" customHeight="1" s="41">
       <c r="A120" s="9" t="n"/>
       <c r="B120" s="9" t="n"/>
       <c r="C120" s="9" t="n"/>
@@ -12413,7 +12436,7 @@
         </is>
       </c>
     </row>
-    <row r="122" ht="30" customHeight="1" s="26">
+    <row r="122" ht="30" customHeight="1" s="41">
       <c r="A122" s="9" t="n"/>
       <c r="B122" s="9" t="n"/>
       <c r="C122" s="9" t="n"/>
@@ -12435,7 +12458,7 @@
         </is>
       </c>
     </row>
-    <row r="123" ht="30" customHeight="1" s="26">
+    <row r="123" ht="30" customHeight="1" s="41">
       <c r="A123" s="9" t="n"/>
       <c r="B123" s="9" t="n"/>
       <c r="C123" s="9" t="n"/>
@@ -12501,7 +12524,7 @@
         </is>
       </c>
     </row>
-    <row r="126" ht="30" customHeight="1" s="26">
+    <row r="126" ht="30" customHeight="1" s="41">
       <c r="A126" s="9" t="n"/>
       <c r="B126" s="9" t="n"/>
       <c r="C126" s="9" t="n"/>
@@ -12523,7 +12546,7 @@
         </is>
       </c>
     </row>
-    <row r="127" ht="30" customHeight="1" s="26">
+    <row r="127" ht="30" customHeight="1" s="41">
       <c r="A127" s="9" t="n"/>
       <c r="B127" s="9" t="n"/>
       <c r="C127" s="9" t="n"/>
@@ -12545,7 +12568,7 @@
         </is>
       </c>
     </row>
-    <row r="128" ht="30" customHeight="1" s="26">
+    <row r="128" ht="30" customHeight="1" s="41">
       <c r="A128" s="9" t="n"/>
       <c r="B128" s="9" t="n"/>
       <c r="C128" s="9" t="n"/>
@@ -12567,7 +12590,7 @@
         </is>
       </c>
     </row>
-    <row r="129" ht="30" customHeight="1" s="26">
+    <row r="129" ht="30" customHeight="1" s="41">
       <c r="A129" s="9" t="n"/>
       <c r="B129" s="9" t="n"/>
       <c r="C129" s="9" t="n"/>
@@ -12589,7 +12612,7 @@
         </is>
       </c>
     </row>
-    <row r="130" ht="30" customHeight="1" s="26">
+    <row r="130" ht="30" customHeight="1" s="41">
       <c r="A130" s="9" t="n"/>
       <c r="B130" s="9" t="n"/>
       <c r="C130" s="9" t="n"/>
@@ -12611,7 +12634,7 @@
         </is>
       </c>
     </row>
-    <row r="131" ht="30" customHeight="1" s="26">
+    <row r="131" ht="30" customHeight="1" s="41">
       <c r="A131" s="9" t="n"/>
       <c r="B131" s="9" t="n"/>
       <c r="C131" s="9" t="n"/>
@@ -12633,7 +12656,7 @@
         </is>
       </c>
     </row>
-    <row r="132" ht="30" customHeight="1" s="26">
+    <row r="132" ht="30" customHeight="1" s="41">
       <c r="A132" s="9" t="n"/>
       <c r="B132" s="9" t="n"/>
       <c r="C132" s="9" t="n"/>
@@ -12672,17 +12695,17 @@
   <dimension ref="A1:H36"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
-    <col width="28" customWidth="1" style="26" min="1" max="2"/>
-    <col width="12" customWidth="1" style="26" min="3" max="3"/>
-    <col width="55" customWidth="1" style="26" min="4" max="4"/>
-    <col width="45" customWidth="1" style="26" min="5" max="5"/>
-    <col width="50" customWidth="1" style="26" min="6" max="6"/>
-    <col width="14" customWidth="1" style="26" min="7" max="7"/>
-    <col width="12" customWidth="1" style="26" min="8" max="8"/>
+    <col width="28" customWidth="1" style="41" min="1" max="2"/>
+    <col width="12" customWidth="1" style="41" min="3" max="3"/>
+    <col width="55" customWidth="1" style="41" min="4" max="4"/>
+    <col width="45" customWidth="1" style="41" min="5" max="5"/>
+    <col width="50" customWidth="1" style="41" min="6" max="6"/>
+    <col width="14" customWidth="1" style="41" min="7" max="7"/>
+    <col width="12" customWidth="1" style="41" min="8" max="8"/>
   </cols>
   <sheetData>
-    <row r="1" ht="16" customHeight="1" s="26">
-      <c r="A1" s="25" t="inlineStr">
+    <row r="1" ht="16" customHeight="1" s="41">
+      <c r="A1" s="38" t="inlineStr">
         <is>
           <t>🔧 Расчётные скрипты, запускаемые автоматически в scheduler</t>
         </is>
@@ -12730,7 +12753,7 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="30" customHeight="1" s="26">
+    <row r="3" ht="30" customHeight="1" s="41">
       <c r="A3" s="13" t="inlineStr">
         <is>
           <t>migrate_population_1990_2010.py --all-years</t>
@@ -12770,7 +12793,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="5" ht="30" customHeight="1" s="26">
+    <row r="5" ht="30" customHeight="1" s="41">
       <c r="A5" s="13" t="inlineStr">
         <is>
           <t>calc_housing_per_capita.py</t>
@@ -12810,7 +12833,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="6" ht="30" customHeight="1" s="26">
+    <row r="6" ht="30" customHeight="1" s="41">
       <c r="A6" s="3" t="n"/>
       <c r="B6" s="3" t="n"/>
       <c r="C6" s="2" t="inlineStr">
@@ -12858,7 +12881,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="9" ht="30" customHeight="1" s="26">
+    <row r="9" ht="30" customHeight="1" s="41">
       <c r="A9" s="13" t="inlineStr">
         <is>
           <t>calc_avg_apt_area.py</t>
@@ -12898,7 +12921,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="11" ht="30" customHeight="1" s="26">
+    <row r="11" ht="30" customHeight="1" s="41">
       <c r="A11" s="13" t="inlineStr">
         <is>
           <t>calc_sales_pace.py</t>
@@ -12962,7 +12985,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="14" ht="30" customHeight="1" s="26">
+    <row r="14" ht="30" customHeight="1" s="41">
       <c r="A14" s="13" t="inlineStr">
         <is>
           <t>calc_sales_pace_mm.py</t>
@@ -13002,7 +13025,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="15" ht="30" customHeight="1" s="26">
+    <row r="15" ht="30" customHeight="1" s="41">
       <c r="A15" s="3" t="n"/>
       <c r="B15" s="3" t="n"/>
       <c r="C15" s="2" t="inlineStr">
@@ -13026,7 +13049,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="17" ht="30" customHeight="1" s="26">
+    <row r="17" ht="30" customHeight="1" s="41">
       <c r="A17" s="13" t="inlineStr">
         <is>
           <t>calc_developer_activity.py</t>
@@ -13066,7 +13089,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="19" ht="30" customHeight="1" s="26">
+    <row r="19" ht="30" customHeight="1" s="41">
       <c r="A19" s="13" t="inlineStr">
         <is>
           <t>calc_demand_activity.py</t>
@@ -13106,7 +13129,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="21" ht="30" customHeight="1" s="26">
+    <row r="21" ht="30" customHeight="1" s="41">
       <c r="A21" s="13" t="inlineStr">
         <is>
           <t>calc_affordability.py</t>
@@ -13146,7 +13169,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="23" ht="30" customHeight="1" s="26">
+    <row r="23" ht="30" customHeight="1" s="41">
       <c r="A23" s="13" t="inlineStr">
         <is>
           <t>calc_affordability_fcp.py</t>
@@ -13186,7 +13209,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="25" ht="30" customHeight="1" s="26">
+    <row r="25" ht="30" customHeight="1" s="41">
       <c r="A25" s="13" t="inlineStr">
         <is>
           <t>calc_annual_companion.py</t>
@@ -13226,7 +13249,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="27" ht="30" customHeight="1" s="26">
+    <row r="27" ht="30" customHeight="1" s="41">
       <c r="A27" s="13" t="inlineStr">
         <is>
           <t>calc_housing_provision.py</t>
@@ -13266,7 +13289,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="29" ht="30" customHeight="1" s="26">
+    <row r="29" ht="30" customHeight="1" s="41">
       <c r="A29" s="13" t="inlineStr">
         <is>
           <t>calc_housing_need.py</t>
@@ -13306,7 +13329,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="30" ht="30" customHeight="1" s="26">
+    <row r="30" ht="30" customHeight="1" s="41">
       <c r="A30" s="3" t="n"/>
       <c r="B30" s="3" t="n"/>
       <c r="C30" s="2" t="inlineStr">
@@ -13330,7 +13353,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="31" ht="30" customHeight="1" s="26">
+    <row r="31" ht="30" customHeight="1" s="41">
       <c r="A31" s="3" t="n"/>
       <c r="B31" s="3" t="n"/>
       <c r="C31" s="2" t="inlineStr">
@@ -13354,7 +13377,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="32" ht="30" customHeight="1" s="26">
+    <row r="32" ht="30" customHeight="1" s="41">
       <c r="A32" s="3" t="n"/>
       <c r="B32" s="3" t="n"/>
       <c r="C32" s="2" t="inlineStr">
@@ -13378,7 +13401,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="33" ht="30" customHeight="1" s="26">
+    <row r="33" ht="30" customHeight="1" s="41">
       <c r="A33" s="3" t="n"/>
       <c r="B33" s="3" t="n"/>
       <c r="C33" s="2" t="inlineStr">
@@ -13402,7 +13425,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="34" ht="30" customHeight="1" s="26">
+    <row r="34" ht="30" customHeight="1" s="41">
       <c r="A34" s="3" t="n"/>
       <c r="B34" s="3" t="n"/>
       <c r="C34" s="2" t="inlineStr">
@@ -13426,7 +13449,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="35" ht="30" customHeight="1" s="26">
+    <row r="35" ht="30" customHeight="1" s="41">
       <c r="A35" s="3" t="n"/>
       <c r="B35" s="3" t="n"/>
       <c r="C35" s="2" t="inlineStr">
@@ -13450,7 +13473,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="36" ht="30" customHeight="1" s="26">
+    <row r="36" ht="30" customHeight="1" s="41">
       <c r="A36" s="3" t="n"/>
       <c r="B36" s="3" t="n"/>
       <c r="C36" s="2" t="inlineStr">
@@ -13491,16 +13514,16 @@
   <dimension ref="A1:H2"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
-    <col width="28" customWidth="1" style="26" min="1" max="1"/>
-    <col width="12" customWidth="1" style="26" min="2" max="2"/>
-    <col width="55" customWidth="1" style="26" min="3" max="5"/>
-    <col width="45" customWidth="1" style="26" min="6" max="6"/>
-    <col width="14" customWidth="1" style="26" min="7" max="7"/>
-    <col width="12" customWidth="1" style="26" min="8" max="8"/>
+    <col width="28" customWidth="1" style="41" min="1" max="1"/>
+    <col width="12" customWidth="1" style="41" min="2" max="2"/>
+    <col width="55" customWidth="1" style="41" min="3" max="5"/>
+    <col width="45" customWidth="1" style="41" min="6" max="6"/>
+    <col width="14" customWidth="1" style="41" min="7" max="7"/>
+    <col width="12" customWidth="1" style="41" min="8" max="8"/>
   </cols>
   <sheetData>
-    <row r="1" ht="16" customHeight="1" s="26">
-      <c r="A1" s="25" t="inlineStr">
+    <row r="1" ht="16" customHeight="1" s="41">
+      <c r="A1" s="38" t="inlineStr">
         <is>
           <t>📝 Расчётные скрипты — только ручной запуск (не в scheduler)</t>
         </is>
@@ -13565,16 +13588,16 @@
   <dimension ref="A1:G13"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
-    <col width="10" customWidth="1" style="26" min="1" max="1"/>
-    <col width="55" customWidth="1" style="26" min="2" max="2"/>
-    <col width="15" customWidth="1" style="26" min="3" max="3"/>
-    <col width="14" customWidth="1" style="26" min="4" max="5"/>
-    <col width="12" customWidth="1" style="26" min="6" max="6"/>
-    <col width="70" customWidth="1" style="26" min="7" max="7"/>
+    <col width="10" customWidth="1" style="41" min="1" max="1"/>
+    <col width="55" customWidth="1" style="41" min="2" max="2"/>
+    <col width="15" customWidth="1" style="41" min="3" max="3"/>
+    <col width="14" customWidth="1" style="41" min="4" max="5"/>
+    <col width="12" customWidth="1" style="41" min="6" max="6"/>
+    <col width="70" customWidth="1" style="41" min="7" max="7"/>
   </cols>
   <sheetData>
-    <row r="1" ht="16" customHeight="1" s="26">
-      <c r="A1" s="25" t="inlineStr">
+    <row r="1" ht="16" customHeight="1" s="41">
+      <c r="A1" s="38" t="inlineStr">
         <is>
           <t>❌ Индикаторы без автоматического обновления</t>
         </is>
@@ -13887,13 +13910,13 @@
   <dimension ref="A1:C9"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
-    <col width="35" customWidth="1" style="26" min="1" max="1"/>
-    <col width="22" customWidth="1" style="26" min="2" max="2"/>
-    <col width="12" customWidth="1" style="26" min="3" max="3"/>
+    <col width="35" customWidth="1" style="41" min="1" max="1"/>
+    <col width="22" customWidth="1" style="41" min="2" max="2"/>
+    <col width="12" customWidth="1" style="41" min="3" max="3"/>
   </cols>
   <sheetData>
-    <row r="1" ht="16" customHeight="1" s="26">
-      <c r="A1" s="34" t="inlineStr">
+    <row r="1" ht="16" customHeight="1" s="41">
+      <c r="A1" s="39" t="inlineStr">
         <is>
           <t>📊 Статистика покрытия индикаторов</t>
         </is>

--- a/indicator_update_map.xlsx
+++ b/indicator_update_map.xlsx
@@ -21,7 +21,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="9">
+  <fonts count="10">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -76,8 +76,13 @@
     <font>
       <sz val="10"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="17">
+  <fills count="18">
     <fill>
       <patternFill/>
     </fill>
@@ -159,6 +164,11 @@
         <fgColor rgb="00F2F2F2"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="004472C4"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="6">
     <border>
@@ -231,7 +241,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="56">
+  <cellXfs count="58">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -373,6 +383,12 @@
     </xf>
     <xf numFmtId="0" fontId="8" fillId="16" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="17" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -739,7 +755,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M161"/>
+  <dimension ref="A1:O161"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="13.83203125" customWidth="1" style="41" min="1" max="1"/>
@@ -750,9 +766,9 @@
     <col width="30" customWidth="1" style="41" min="6" max="6"/>
     <col width="28" customWidth="1" style="41" min="7" max="8"/>
     <col width="18" customWidth="1" style="41" min="9" max="9"/>
-    <col width="20" customWidth="1" style="41" min="10" max="10"/>
-    <col width="55" customWidth="1" style="41" min="11" max="11"/>
-    <col width="39.33203125" customWidth="1" style="41" min="12" max="12"/>
+    <col width="22" customWidth="1" style="41" min="10" max="10"/>
+    <col width="18" customWidth="1" style="41" min="11" max="11"/>
+    <col width="18" customWidth="1" style="41" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1" s="41">
@@ -813,12 +829,22 @@
           <t>Статус</t>
         </is>
       </c>
-      <c r="K2" s="1" t="inlineStr">
+      <c r="K2" s="56" t="inlineStr">
+        <is>
+          <t>Дата парсера</t>
+        </is>
+      </c>
+      <c r="L2" s="56" t="inlineStr">
+        <is>
+          <t>Дата расчёта</t>
+        </is>
+      </c>
+      <c r="M2" s="1" t="inlineStr">
         <is>
           <t>Кол-во точек</t>
         </is>
       </c>
-      <c r="L2" s="1" t="inlineStr">
+      <c r="N2" s="1" t="inlineStr">
         <is>
           <t>Примечания</t>
         </is>
@@ -875,10 +901,16 @@
           <t>✅ Актуально</t>
         </is>
       </c>
-      <c r="K3" s="4" t="n">
+      <c r="K3" s="57" t="inlineStr"/>
+      <c r="L3" s="57" t="inlineStr">
+        <is>
+          <t>25.05.2026 09:18</t>
+        </is>
+      </c>
+      <c r="M3" s="4" t="n">
         <v>36</v>
       </c>
-      <c r="L3" s="3" t="inlineStr">
+      <c r="N3" s="3" t="inlineStr">
         <is>
           <t>Нет внешних источников — данные из Росстата захардкожены в скрипте</t>
         </is>
@@ -925,20 +957,22 @@
           <t>01.10.2025</t>
         </is>
       </c>
-      <c r="I4" s="50" t="inlineStr">
-        <is>
-          <t>4 кв. 2025</t>
-        </is>
-      </c>
-      <c r="J4" s="51" t="inlineStr">
-        <is>
-          <t>⚠️ Просрочено</t>
-        </is>
-      </c>
-      <c r="K4" s="7" t="n">
+      <c r="I4" s="48" t="inlineStr">
+        <is>
+          <t>1 кв. 2026</t>
+        </is>
+      </c>
+      <c r="J4" s="49" t="inlineStr">
+        <is>
+          <t>✅ Актуально</t>
+        </is>
+      </c>
+      <c r="K4" s="57" t="inlineStr"/>
+      <c r="L4" s="57" t="inlineStr"/>
+      <c r="M4" s="7" t="n">
         <v>56</v>
       </c>
-      <c r="L4" s="6" t="inlineStr">
+      <c r="N4" s="6" t="inlineStr">
         <is>
           <t>rosstat.gov.ru / folder/13397</t>
         </is>
@@ -985,20 +1019,22 @@
           <t>01.01.2024</t>
         </is>
       </c>
-      <c r="I5" s="50" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
-      </c>
-      <c r="J5" s="51" t="inlineStr">
-        <is>
-          <t>⚠️ Просрочено</t>
-        </is>
-      </c>
-      <c r="K5" s="7" t="n">
+      <c r="I5" s="48" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="J5" s="49" t="inlineStr">
+        <is>
+          <t>✅ Актуально</t>
+        </is>
+      </c>
+      <c r="K5" s="57" t="inlineStr"/>
+      <c r="L5" s="57" t="inlineStr"/>
+      <c r="M5" s="7" t="n">
         <v>12</v>
       </c>
-      <c r="L5" s="6" t="inlineStr">
+      <c r="N5" s="6" t="inlineStr">
         <is>
           <t>rosstat.gov.ru / folder/13397</t>
         </is>
@@ -1055,10 +1091,12 @@
           <t>⚠️ Просрочено</t>
         </is>
       </c>
-      <c r="K6" s="7" t="n">
+      <c r="K6" s="57" t="inlineStr"/>
+      <c r="L6" s="57" t="inlineStr"/>
+      <c r="M6" s="7" t="n">
         <v>36</v>
       </c>
-      <c r="L6" s="6" t="inlineStr">
+      <c r="N6" s="6" t="inlineStr">
         <is>
           <t>fedstat.ru (ЕМИСС / Росстат)</t>
         </is>
@@ -1115,10 +1153,16 @@
           <t>✅ Актуально</t>
         </is>
       </c>
-      <c r="K7" s="4" t="n">
+      <c r="K7" s="57" t="inlineStr"/>
+      <c r="L7" s="57" t="inlineStr">
+        <is>
+          <t>21.05.2026 22:25</t>
+        </is>
+      </c>
+      <c r="M7" s="4" t="n">
         <v>14</v>
       </c>
-      <c r="L7" s="3" t="inlineStr">
+      <c r="N7" s="3" t="inlineStr">
         <is>
           <t>1.3 (квартальная зарплата, обновляется rosstat.py)</t>
         </is>
@@ -1175,10 +1219,12 @@
           <t>✅ Актуально</t>
         </is>
       </c>
-      <c r="K8" s="7" t="n">
+      <c r="K8" s="57" t="inlineStr"/>
+      <c r="L8" s="57" t="inlineStr"/>
+      <c r="M8" s="7" t="n">
         <v>112</v>
       </c>
-      <c r="L8" s="6" t="inlineStr">
+      <c r="N8" s="6" t="inlineStr">
         <is>
           <t>fedstat.ru (ЕМИСС / Росстат)</t>
         </is>
@@ -1235,10 +1281,12 @@
           <t>✅ Актуально</t>
         </is>
       </c>
-      <c r="K9" s="7" t="n">
+      <c r="K9" s="57" t="inlineStr"/>
+      <c r="L9" s="57" t="inlineStr"/>
+      <c r="M9" s="7" t="n">
         <v>112</v>
       </c>
-      <c r="L9" s="6" t="inlineStr">
+      <c r="N9" s="6" t="inlineStr">
         <is>
           <t>fedstat.ru (ЕМИСС / Росстат)</t>
         </is>
@@ -1295,10 +1343,12 @@
           <t>✅ Актуально</t>
         </is>
       </c>
-      <c r="K10" s="7" t="n">
+      <c r="K10" s="57" t="inlineStr"/>
+      <c r="L10" s="57" t="inlineStr"/>
+      <c r="M10" s="7" t="n">
         <v>112</v>
       </c>
-      <c r="L10" s="6" t="inlineStr">
+      <c r="N10" s="6" t="inlineStr">
         <is>
           <t>fedstat.ru (ЕМИСС / Росстат)</t>
         </is>
@@ -1355,10 +1405,16 @@
           <t>⚠️ Просрочено</t>
         </is>
       </c>
-      <c r="K11" s="4" t="n">
+      <c r="K11" s="57" t="inlineStr"/>
+      <c r="L11" s="57" t="inlineStr">
+        <is>
+          <t>15.04.2026 22:02</t>
+        </is>
+      </c>
+      <c r="M11" s="4" t="n">
         <v>108</v>
       </c>
-      <c r="L11" s="3" t="inlineStr">
+      <c r="N11" s="3" t="inlineStr">
         <is>
           <t>2.1 (ввод всего, тыс. кв. м), 2.2 (ввод ИЖС), 1.1 (население, тыс. чел.)</t>
         </is>
@@ -1415,10 +1471,16 @@
           <t>⚠️ Просрочено</t>
         </is>
       </c>
-      <c r="K12" s="4" t="n">
+      <c r="K12" s="57" t="inlineStr"/>
+      <c r="L12" s="57" t="inlineStr">
+        <is>
+          <t>15.04.2026 22:02</t>
+        </is>
+      </c>
+      <c r="M12" s="4" t="n">
         <v>108</v>
       </c>
-      <c r="L12" s="3" t="inlineStr">
+      <c r="N12" s="3" t="inlineStr">
         <is>
           <t>2.1 (ввод всего, тыс. кв. м), 2.2 (ввод ИЖС), 1.1 (население, тыс. чел.)</t>
         </is>
@@ -1475,10 +1537,16 @@
           <t>⚠️ Просрочено</t>
         </is>
       </c>
-      <c r="K13" s="4" t="n">
+      <c r="K13" s="57" t="inlineStr"/>
+      <c r="L13" s="57" t="inlineStr">
+        <is>
+          <t>15.04.2026 22:02</t>
+        </is>
+      </c>
+      <c r="M13" s="4" t="n">
         <v>108</v>
       </c>
-      <c r="L13" s="3" t="inlineStr">
+      <c r="N13" s="3" t="inlineStr">
         <is>
           <t>2.1 (ввод всего, тыс. кв. м), 2.2 (ввод ИЖС), 1.1 (население, тыс. чел.)</t>
         </is>
@@ -1535,10 +1603,12 @@
           <t>✅ Актуально</t>
         </is>
       </c>
-      <c r="K14" s="7" t="n">
+      <c r="K14" s="57" t="inlineStr"/>
+      <c r="L14" s="57" t="inlineStr"/>
+      <c r="M14" s="7" t="n">
         <v>18</v>
       </c>
-      <c r="L14" s="6" t="inlineStr">
+      <c r="N14" s="6" t="inlineStr">
         <is>
           <t>fedstat.ru (ЕМИСС / Росстат)</t>
         </is>
@@ -1595,10 +1665,16 @@
           <t>✅ Актуально</t>
         </is>
       </c>
-      <c r="K15" s="4" t="n">
+      <c r="K15" s="57" t="inlineStr"/>
+      <c r="L15" s="57" t="inlineStr">
+        <is>
+          <t>15.04.2026 21:50</t>
+        </is>
+      </c>
+      <c r="M15" s="4" t="n">
         <v>14</v>
       </c>
-      <c r="L15" s="3" t="inlineStr">
+      <c r="N15" s="3" t="inlineStr">
         <is>
           <t>2.9 (жилфонд млн кв.м, конец года N), 1.1 (население тыс.чел, нач. N+1)</t>
         </is>
@@ -1655,10 +1731,12 @@
           <t>✅ Актуально</t>
         </is>
       </c>
-      <c r="K16" s="7" t="n">
+      <c r="K16" s="57" t="inlineStr"/>
+      <c r="L16" s="57" t="inlineStr"/>
+      <c r="M16" s="7" t="n">
         <v>17</v>
       </c>
-      <c r="L16" s="6" t="inlineStr">
+      <c r="N16" s="6" t="inlineStr">
         <is>
           <t>fedstat.ru (ЕМИСС / Росстат)</t>
         </is>
@@ -1715,10 +1793,12 @@
           <t>✅ Актуально</t>
         </is>
       </c>
-      <c r="K17" s="7" t="n">
+      <c r="K17" s="57" t="inlineStr"/>
+      <c r="L17" s="57" t="inlineStr"/>
+      <c r="M17" s="7" t="n">
         <v>18</v>
       </c>
-      <c r="L17" s="6" t="inlineStr">
+      <c r="N17" s="6" t="inlineStr">
         <is>
           <t>fedstat.ru (ЕМИСС / Росстат)</t>
         </is>
@@ -1775,10 +1855,12 @@
           <t>✅ Актуально</t>
         </is>
       </c>
-      <c r="K18" s="7" t="n">
+      <c r="K18" s="57" t="inlineStr"/>
+      <c r="L18" s="57" t="inlineStr"/>
+      <c r="M18" s="7" t="n">
         <v>13</v>
       </c>
-      <c r="L18" s="6" t="inlineStr">
+      <c r="N18" s="6" t="inlineStr">
         <is>
           <t>fedstat.ru (ЕМИСС / Росстат)</t>
         </is>
@@ -1835,10 +1917,12 @@
           <t>⛔ Отключён</t>
         </is>
       </c>
-      <c r="K19" s="7" t="n">
+      <c r="K19" s="57" t="inlineStr"/>
+      <c r="L19" s="57" t="inlineStr"/>
+      <c r="M19" s="7" t="n">
         <v>10</v>
       </c>
-      <c r="L19" s="6" t="inlineStr">
+      <c r="N19" s="6" t="inlineStr">
         <is>
           <t>fedstat.ru (ЕМИСС / Росстат)</t>
         </is>
@@ -1895,10 +1979,16 @@
           <t>✅ Актуально</t>
         </is>
       </c>
-      <c r="K20" s="7" t="n">
+      <c r="K20" s="57" t="inlineStr">
+        <is>
+          <t>25.05.2026 09:11</t>
+        </is>
+      </c>
+      <c r="L20" s="57" t="inlineStr"/>
+      <c r="M20" s="7" t="n">
         <v>77</v>
       </c>
-      <c r="L20" s="6" t="inlineStr">
+      <c r="N20" s="6" t="inlineStr">
         <is>
           <t>ЕИСЖС / наш.дом.рф</t>
         </is>
@@ -1955,10 +2045,16 @@
           <t>✅ Актуально</t>
         </is>
       </c>
-      <c r="K21" s="7" t="n">
+      <c r="K21" s="57" t="inlineStr">
+        <is>
+          <t>25.05.2026 09:11</t>
+        </is>
+      </c>
+      <c r="L21" s="57" t="inlineStr"/>
+      <c r="M21" s="7" t="n">
         <v>77</v>
       </c>
-      <c r="L21" s="6" t="inlineStr">
+      <c r="N21" s="6" t="inlineStr">
         <is>
           <t>ЕИСЖС / наш.дом.рф</t>
         </is>
@@ -2015,10 +2111,16 @@
           <t>✅ Актуально</t>
         </is>
       </c>
-      <c r="K22" s="7" t="n">
+      <c r="K22" s="57" t="inlineStr">
+        <is>
+          <t>25.05.2026 09:11</t>
+        </is>
+      </c>
+      <c r="L22" s="57" t="inlineStr"/>
+      <c r="M22" s="7" t="n">
         <v>77</v>
       </c>
-      <c r="L22" s="6" t="inlineStr">
+      <c r="N22" s="6" t="inlineStr">
         <is>
           <t>ЕИСЖС / наш.дом.рф</t>
         </is>
@@ -2075,10 +2177,16 @@
           <t>✅ Актуально</t>
         </is>
       </c>
-      <c r="K23" s="7" t="n">
+      <c r="K23" s="57" t="inlineStr">
+        <is>
+          <t>25.05.2026 09:11</t>
+        </is>
+      </c>
+      <c r="L23" s="57" t="inlineStr"/>
+      <c r="M23" s="7" t="n">
         <v>77</v>
       </c>
-      <c r="L23" s="6" t="inlineStr">
+      <c r="N23" s="6" t="inlineStr">
         <is>
           <t>ЕИСЖС / наш.дом.рф</t>
         </is>
@@ -2135,10 +2243,16 @@
           <t>✅ Актуально</t>
         </is>
       </c>
-      <c r="K24" s="4" t="n">
+      <c r="K24" s="57" t="inlineStr"/>
+      <c r="L24" s="57" t="inlineStr">
+        <is>
+          <t>25.05.2026 09:11</t>
+        </is>
+      </c>
+      <c r="M24" s="4" t="n">
         <v>77</v>
       </c>
-      <c r="L24" s="3" t="inlineStr">
+      <c r="N24" s="3" t="inlineStr">
         <is>
           <t>3.3 (жилая площадь), 3.4 (кол-во квартир)</t>
         </is>
@@ -2195,10 +2309,16 @@
           <t>✅ Актуально</t>
         </is>
       </c>
-      <c r="K25" s="10" t="n">
+      <c r="K25" s="57" t="inlineStr">
+        <is>
+          <t>25.05.2026 09:11</t>
+        </is>
+      </c>
+      <c r="L25" s="57" t="inlineStr"/>
+      <c r="M25" s="10" t="n">
         <v>45</v>
       </c>
-      <c r="L25" s="9" t="inlineStr">
+      <c r="N25" s="9" t="inlineStr">
         <is>
           <t>Локальные Excel-файлы ДОМ.РФ (migration/domrf_data/)</t>
         </is>
@@ -2255,10 +2375,16 @@
           <t>⚠️ Просрочено</t>
         </is>
       </c>
-      <c r="K26" s="4" t="n">
+      <c r="K26" s="57" t="inlineStr"/>
+      <c r="L26" s="57" t="inlineStr">
+        <is>
+          <t>25.05.2026 09:10</t>
+        </is>
+      </c>
+      <c r="M26" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="L26" s="3" t="inlineStr">
+      <c r="N26" s="3" t="inlineStr">
         <is>
           <t>3.3 (жилая площадь МЖД), 1.1 (население)</t>
         </is>
@@ -2315,10 +2441,16 @@
           <t>✅ Актуально</t>
         </is>
       </c>
-      <c r="K27" s="7" t="n">
+      <c r="K27" s="57" t="inlineStr">
+        <is>
+          <t>25.05.2026 09:11</t>
+        </is>
+      </c>
+      <c r="L27" s="57" t="inlineStr"/>
+      <c r="M27" s="7" t="n">
         <v>65</v>
       </c>
-      <c r="L27" s="6" t="inlineStr">
+      <c r="N27" s="6" t="inlineStr">
         <is>
           <t>ЕИСЖС / наш.дом.рф</t>
         </is>
@@ -2375,10 +2507,16 @@
           <t>✅ Актуально</t>
         </is>
       </c>
-      <c r="K28" s="7" t="n">
+      <c r="K28" s="57" t="inlineStr">
+        <is>
+          <t>25.05.2026 09:11</t>
+        </is>
+      </c>
+      <c r="L28" s="57" t="inlineStr"/>
+      <c r="M28" s="7" t="n">
         <v>77</v>
       </c>
-      <c r="L28" s="6" t="inlineStr">
+      <c r="N28" s="6" t="inlineStr">
         <is>
           <t>ЕИСЖС / наш.дом.рф</t>
         </is>
@@ -2435,10 +2573,16 @@
           <t>✅ Актуально</t>
         </is>
       </c>
-      <c r="K29" s="7" t="n">
+      <c r="K29" s="57" t="inlineStr">
+        <is>
+          <t>25.05.2026 09:11</t>
+        </is>
+      </c>
+      <c r="L29" s="57" t="inlineStr"/>
+      <c r="M29" s="7" t="n">
         <v>77</v>
       </c>
-      <c r="L29" s="6" t="inlineStr">
+      <c r="N29" s="6" t="inlineStr">
         <is>
           <t>ЕИСЖС / наш.дом.рф</t>
         </is>
@@ -2495,10 +2639,16 @@
           <t>✅ Актуально</t>
         </is>
       </c>
-      <c r="K30" s="10" t="n">
+      <c r="K30" s="57" t="inlineStr">
+        <is>
+          <t>25.05.2026 09:11</t>
+        </is>
+      </c>
+      <c r="L30" s="57" t="inlineStr"/>
+      <c r="M30" s="10" t="n">
         <v>64</v>
       </c>
-      <c r="L30" s="9" t="inlineStr">
+      <c r="N30" s="9" t="inlineStr">
         <is>
           <t>Локальные Excel-файлы ДОМ.РФ (migration/domrf_data/)</t>
         </is>
@@ -2555,10 +2705,12 @@
           <t>✅ Актуально</t>
         </is>
       </c>
-      <c r="K31" s="7" t="n">
+      <c r="K31" s="57" t="inlineStr"/>
+      <c r="L31" s="57" t="inlineStr"/>
+      <c r="M31" s="7" t="n">
         <v>37</v>
       </c>
-      <c r="L31" s="6" t="inlineStr">
+      <c r="N31" s="6" t="inlineStr">
         <is>
           <t>fedstat.ru (ЕМИСС / Росстат)</t>
         </is>
@@ -2615,10 +2767,12 @@
           <t>✅ Актуально</t>
         </is>
       </c>
-      <c r="K32" s="7" t="n">
+      <c r="K32" s="57" t="inlineStr"/>
+      <c r="L32" s="57" t="inlineStr"/>
+      <c r="M32" s="7" t="n">
         <v>37</v>
       </c>
-      <c r="L32" s="6" t="inlineStr">
+      <c r="N32" s="6" t="inlineStr">
         <is>
           <t>fedstat.ru (ЕМИСС / Росстат)</t>
         </is>
@@ -2675,10 +2829,12 @@
           <t>✅ Актуально</t>
         </is>
       </c>
-      <c r="K33" s="7" t="n">
+      <c r="K33" s="57" t="inlineStr"/>
+      <c r="L33" s="57" t="inlineStr"/>
+      <c r="M33" s="7" t="n">
         <v>37</v>
       </c>
-      <c r="L33" s="6" t="inlineStr">
+      <c r="N33" s="6" t="inlineStr">
         <is>
           <t>fedstat.ru (ЕМИСС / Росстат)</t>
         </is>
@@ -2735,10 +2891,12 @@
           <t>✅ Актуально</t>
         </is>
       </c>
-      <c r="K34" s="7" t="n">
+      <c r="K34" s="57" t="inlineStr"/>
+      <c r="L34" s="57" t="inlineStr"/>
+      <c r="M34" s="7" t="n">
         <v>37</v>
       </c>
-      <c r="L34" s="6" t="inlineStr">
+      <c r="N34" s="6" t="inlineStr">
         <is>
           <t>fedstat.ru (ЕМИСС / Росстат)</t>
         </is>
@@ -2795,10 +2953,12 @@
           <t>✅ Актуально</t>
         </is>
       </c>
-      <c r="K35" s="7" t="n">
+      <c r="K35" s="57" t="inlineStr"/>
+      <c r="L35" s="57" t="inlineStr"/>
+      <c r="M35" s="7" t="n">
         <v>37</v>
       </c>
-      <c r="L35" s="6" t="inlineStr">
+      <c r="N35" s="6" t="inlineStr">
         <is>
           <t>fedstat.ru (ЕМИСС / Росстат)</t>
         </is>
@@ -2855,10 +3015,12 @@
           <t>✅ Актуально</t>
         </is>
       </c>
-      <c r="K36" s="7" t="n">
+      <c r="K36" s="57" t="inlineStr"/>
+      <c r="L36" s="57" t="inlineStr"/>
+      <c r="M36" s="7" t="n">
         <v>37</v>
       </c>
-      <c r="L36" s="6" t="inlineStr">
+      <c r="N36" s="6" t="inlineStr">
         <is>
           <t>fedstat.ru (ЕМИСС / Росстат)</t>
         </is>
@@ -2915,10 +3077,12 @@
           <t>✅ Актуально</t>
         </is>
       </c>
-      <c r="K37" s="7" t="n">
+      <c r="K37" s="57" t="inlineStr"/>
+      <c r="L37" s="57" t="inlineStr"/>
+      <c r="M37" s="7" t="n">
         <v>37</v>
       </c>
-      <c r="L37" s="6" t="inlineStr">
+      <c r="N37" s="6" t="inlineStr">
         <is>
           <t>fedstat.ru (ЕМИСС / Росстат)</t>
         </is>
@@ -2975,10 +3139,12 @@
           <t>✅ Актуально</t>
         </is>
       </c>
-      <c r="K38" s="7" t="n">
+      <c r="K38" s="57" t="inlineStr"/>
+      <c r="L38" s="57" t="inlineStr"/>
+      <c r="M38" s="7" t="n">
         <v>37</v>
       </c>
-      <c r="L38" s="6" t="inlineStr">
+      <c r="N38" s="6" t="inlineStr">
         <is>
           <t>fedstat.ru (ЕМИСС / Росстат)</t>
         </is>
@@ -3035,10 +3201,12 @@
           <t>✅ Актуально</t>
         </is>
       </c>
-      <c r="K39" s="7" t="n">
+      <c r="K39" s="57" t="inlineStr"/>
+      <c r="L39" s="57" t="inlineStr"/>
+      <c r="M39" s="7" t="n">
         <v>37</v>
       </c>
-      <c r="L39" s="6" t="inlineStr">
+      <c r="N39" s="6" t="inlineStr">
         <is>
           <t>fedstat.ru (ЕМИСС / Росстат)</t>
         </is>
@@ -3095,10 +3263,16 @@
           <t>✅ Актуально</t>
         </is>
       </c>
-      <c r="K40" s="10" t="n">
+      <c r="K40" s="57" t="inlineStr">
+        <is>
+          <t>25.05.2026 09:11</t>
+        </is>
+      </c>
+      <c r="L40" s="57" t="inlineStr"/>
+      <c r="M40" s="10" t="n">
         <v>64</v>
       </c>
-      <c r="L40" s="9" t="inlineStr">
+      <c r="N40" s="9" t="inlineStr">
         <is>
           <t>Локальные Excel-файлы ДОМ.РФ (migration/domrf_data/)</t>
         </is>
@@ -3155,10 +3329,16 @@
           <t>✅ Актуально</t>
         </is>
       </c>
-      <c r="K41" s="10" t="n">
+      <c r="K41" s="57" t="inlineStr">
+        <is>
+          <t>25.05.2026 09:11</t>
+        </is>
+      </c>
+      <c r="L41" s="57" t="inlineStr"/>
+      <c r="M41" s="10" t="n">
         <v>64</v>
       </c>
-      <c r="L41" s="9" t="inlineStr">
+      <c r="N41" s="9" t="inlineStr">
         <is>
           <t>Локальные Excel-файлы ДОМ.РФ (migration/domrf_data/)</t>
         </is>
@@ -3215,10 +3395,12 @@
           <t>✅ Актуально</t>
         </is>
       </c>
-      <c r="K42" s="7" t="n">
+      <c r="K42" s="57" t="inlineStr"/>
+      <c r="L42" s="57" t="inlineStr"/>
+      <c r="M42" s="7" t="n">
         <v>65</v>
       </c>
-      <c r="L42" s="6" t="inlineStr">
+      <c r="N42" s="6" t="inlineStr">
         <is>
           <t>Росреестр (rosreestr.gov.ru)</t>
         </is>
@@ -3275,10 +3457,16 @@
           <t>⚠️ Просрочено</t>
         </is>
       </c>
-      <c r="K43" s="4" t="n">
+      <c r="K43" s="57" t="inlineStr"/>
+      <c r="L43" s="57" t="inlineStr">
+        <is>
+          <t>14.05.2026 21:18</t>
+        </is>
+      </c>
+      <c r="M43" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="L43" s="3" t="inlineStr">
+      <c r="N43" s="3" t="inlineStr">
         <is>
           <t>5.1 (ДДУ квартальные), 1.1 (население)</t>
         </is>
@@ -3335,10 +3523,16 @@
           <t>✅ Актуально</t>
         </is>
       </c>
-      <c r="K44" s="10" t="n">
+      <c r="K44" s="57" t="inlineStr">
+        <is>
+          <t>25.05.2026 09:11</t>
+        </is>
+      </c>
+      <c r="L44" s="57" t="inlineStr"/>
+      <c r="M44" s="10" t="n">
         <v>64</v>
       </c>
-      <c r="L44" s="9" t="inlineStr">
+      <c r="N44" s="9" t="inlineStr">
         <is>
           <t>Локальные Excel-файлы ДОМ.РФ (migration/domrf_data/)</t>
         </is>
@@ -3395,10 +3589,16 @@
           <t>✅ Актуально</t>
         </is>
       </c>
-      <c r="K45" s="4" t="n">
+      <c r="K45" s="57" t="inlineStr"/>
+      <c r="L45" s="57" t="inlineStr">
+        <is>
+          <t>25.05.2026 09:10</t>
+        </is>
+      </c>
+      <c r="M45" s="4" t="n">
         <v>76</v>
       </c>
-      <c r="L45" s="3" t="inlineStr">
+      <c r="N45" s="3" t="inlineStr">
         <is>
           <t>5.8 (кол-во сделок ДДУ квартиры)</t>
         </is>
@@ -3455,10 +3655,16 @@
           <t>✅ Актуально</t>
         </is>
       </c>
-      <c r="K46" s="4" t="n">
+      <c r="K46" s="57" t="inlineStr"/>
+      <c r="L46" s="57" t="inlineStr">
+        <is>
+          <t>25.05.2026 09:10</t>
+        </is>
+      </c>
+      <c r="M46" s="4" t="n">
         <v>65</v>
       </c>
-      <c r="L46" s="3" t="inlineStr">
+      <c r="N46" s="3" t="inlineStr">
         <is>
           <t>5.8 (кол-во сделок ДДУ квартиры)</t>
         </is>
@@ -3515,10 +3721,16 @@
           <t>⚠️ Просрочено</t>
         </is>
       </c>
-      <c r="K47" s="4" t="n">
+      <c r="K47" s="57" t="inlineStr"/>
+      <c r="L47" s="57" t="inlineStr">
+        <is>
+          <t>25.05.2026 09:11</t>
+        </is>
+      </c>
+      <c r="M47" s="4" t="n">
         <v>20</v>
       </c>
-      <c r="L47" s="3" t="inlineStr">
+      <c r="N47" s="3" t="inlineStr">
         <is>
           <t>1.3 (зарплата), матрица продаж DomRF (apt_budget/apt_area)</t>
         </is>
@@ -3575,10 +3787,16 @@
           <t>⚠️ Просрочено</t>
         </is>
       </c>
-      <c r="K48" s="4" t="n">
+      <c r="K48" s="57" t="inlineStr"/>
+      <c r="L48" s="57" t="inlineStr">
+        <is>
+          <t>25.05.2026 09:12</t>
+        </is>
+      </c>
+      <c r="M48" s="4" t="n">
         <v>24</v>
       </c>
-      <c r="L48" s="3" t="inlineStr">
+      <c r="N48" s="3" t="inlineStr">
         <is>
           <t>1.3 (зарплата), apartments_area_2k, матрица продаж</t>
         </is>
@@ -3635,10 +3853,16 @@
           <t>✅ Актуально</t>
         </is>
       </c>
-      <c r="K49" s="4" t="n">
+      <c r="K49" s="57" t="inlineStr"/>
+      <c r="L49" s="57" t="inlineStr">
+        <is>
+          <t>13.05.2026 14:29</t>
+        </is>
+      </c>
+      <c r="M49" s="4" t="n">
         <v>14</v>
       </c>
-      <c r="L49" s="3" t="inlineStr">
+      <c r="N49" s="3" t="inlineStr">
         <is>
           <t>2.10 (обеспеченность), 1.1 (население), 2.1 (ввод жилья), 2.13 (благоустройство %)</t>
         </is>
@@ -3695,10 +3919,16 @@
           <t>✅ Актуально</t>
         </is>
       </c>
-      <c r="K50" s="4" t="n">
+      <c r="K50" s="57" t="inlineStr"/>
+      <c r="L50" s="57" t="inlineStr">
+        <is>
+          <t>13.05.2026 14:29</t>
+        </is>
+      </c>
+      <c r="M50" s="4" t="n">
         <v>14</v>
       </c>
-      <c r="L50" s="3" t="inlineStr">
+      <c r="N50" s="3" t="inlineStr">
         <is>
           <t>2.10 (обеспеченность), 1.1 (население), 2.1 (ввод жилья), 2.13 (благоустройство %)</t>
         </is>
@@ -3755,10 +3985,16 @@
           <t>✅ Актуально</t>
         </is>
       </c>
-      <c r="K51" s="4" t="n">
+      <c r="K51" s="57" t="inlineStr"/>
+      <c r="L51" s="57" t="inlineStr">
+        <is>
+          <t>13.05.2026 14:29</t>
+        </is>
+      </c>
+      <c r="M51" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="L51" s="3" t="inlineStr">
+      <c r="N51" s="3" t="inlineStr">
         <is>
           <t>2.10 (обеспеченность), 1.1 (население), 2.1 (ввод жилья), 2.13 (благоустройство %)</t>
         </is>
@@ -3815,10 +4051,16 @@
           <t>✅ Актуально</t>
         </is>
       </c>
-      <c r="K52" s="4" t="n">
+      <c r="K52" s="57" t="inlineStr"/>
+      <c r="L52" s="57" t="inlineStr">
+        <is>
+          <t>13.05.2026 14:29</t>
+        </is>
+      </c>
+      <c r="M52" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="L52" s="3" t="inlineStr">
+      <c r="N52" s="3" t="inlineStr">
         <is>
           <t>2.10 (обеспеченность), 1.1 (население), 2.1 (ввод жилья), 2.13 (благоустройство %)</t>
         </is>
@@ -3875,10 +4117,16 @@
           <t>✅ Актуально</t>
         </is>
       </c>
-      <c r="K53" s="4" t="n">
+      <c r="K53" s="57" t="inlineStr"/>
+      <c r="L53" s="57" t="inlineStr">
+        <is>
+          <t>13.05.2026 14:29</t>
+        </is>
+      </c>
+      <c r="M53" s="4" t="n">
         <v>12</v>
       </c>
-      <c r="L53" s="3" t="inlineStr">
+      <c r="N53" s="3" t="inlineStr">
         <is>
           <t>2.10 (обеспеченность), 1.1 (население), 2.1 (ввод жилья), 2.13 (благоустройство %)</t>
         </is>
@@ -3935,10 +4183,16 @@
           <t>✅ Актуально</t>
         </is>
       </c>
-      <c r="K54" s="4" t="n">
+      <c r="K54" s="57" t="inlineStr"/>
+      <c r="L54" s="57" t="inlineStr">
+        <is>
+          <t>13.05.2026 14:29</t>
+        </is>
+      </c>
+      <c r="M54" s="4" t="n">
         <v>12</v>
       </c>
-      <c r="L54" s="3" t="inlineStr">
+      <c r="N54" s="3" t="inlineStr">
         <is>
           <t>2.10 (обеспеченность), 1.1 (население), 2.1 (ввод жилья), 2.13 (благоустройство %)</t>
         </is>
@@ -3995,10 +4249,16 @@
           <t>✅ Актуально</t>
         </is>
       </c>
-      <c r="K55" s="4" t="n">
+      <c r="K55" s="57" t="inlineStr"/>
+      <c r="L55" s="57" t="inlineStr">
+        <is>
+          <t>13.05.2026 14:29</t>
+        </is>
+      </c>
+      <c r="M55" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="L55" s="3" t="inlineStr">
+      <c r="N55" s="3" t="inlineStr">
         <is>
           <t>2.10 (обеспеченность), 1.1 (население), 2.1 (ввод жилья), 2.13 (благоустройство %)</t>
         </is>
@@ -4055,10 +4315,16 @@
           <t>✅ Актуально</t>
         </is>
       </c>
-      <c r="K56" s="4" t="n">
+      <c r="K56" s="57" t="inlineStr"/>
+      <c r="L56" s="57" t="inlineStr">
+        <is>
+          <t>13.05.2026 14:29</t>
+        </is>
+      </c>
+      <c r="M56" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="L56" s="3" t="inlineStr">
+      <c r="N56" s="3" t="inlineStr">
         <is>
           <t>2.10 (обеспеченность), 1.1 (население), 2.1 (ввод жилья), 2.13 (благоустройство %)</t>
         </is>
@@ -4115,10 +4381,16 @@
           <t>✅ Актуально</t>
         </is>
       </c>
-      <c r="K57" s="10" t="n">
+      <c r="K57" s="57" t="inlineStr">
+        <is>
+          <t>25.05.2026 09:11</t>
+        </is>
+      </c>
+      <c r="L57" s="57" t="inlineStr"/>
+      <c r="M57" s="10" t="n">
         <v>64</v>
       </c>
-      <c r="L57" s="9" t="inlineStr">
+      <c r="N57" s="9" t="inlineStr">
         <is>
           <t>Локальные Excel-файлы ДОМ.РФ (migration/domrf_data/)</t>
         </is>
@@ -4175,10 +4447,16 @@
           <t>✅ Актуально</t>
         </is>
       </c>
-      <c r="K58" s="10" t="n">
+      <c r="K58" s="57" t="inlineStr">
+        <is>
+          <t>25.05.2026 09:11</t>
+        </is>
+      </c>
+      <c r="L58" s="57" t="inlineStr"/>
+      <c r="M58" s="10" t="n">
         <v>64</v>
       </c>
-      <c r="L58" s="9" t="inlineStr">
+      <c r="N58" s="9" t="inlineStr">
         <is>
           <t>Локальные Excel-файлы ДОМ.РФ (migration/domrf_data/)</t>
         </is>
@@ -4235,10 +4513,16 @@
           <t>✅ Актуально</t>
         </is>
       </c>
-      <c r="K59" s="4" t="n">
+      <c r="K59" s="57" t="inlineStr"/>
+      <c r="L59" s="57" t="inlineStr">
+        <is>
+          <t>25.05.2026 09:10</t>
+        </is>
+      </c>
+      <c r="M59" s="4" t="n">
         <v>64</v>
       </c>
-      <c r="L59" s="3" t="inlineStr">
+      <c r="N59" s="3" t="inlineStr">
         <is>
           <t>5.20 (кол-во сделок машиноместа)</t>
         </is>
@@ -4295,10 +4579,16 @@
           <t>✅ Актуально</t>
         </is>
       </c>
-      <c r="K60" s="4" t="n">
+      <c r="K60" s="57" t="inlineStr"/>
+      <c r="L60" s="57" t="inlineStr">
+        <is>
+          <t>25.05.2026 09:10</t>
+        </is>
+      </c>
+      <c r="M60" s="4" t="n">
         <v>53</v>
       </c>
-      <c r="L60" s="3" t="inlineStr">
+      <c r="N60" s="3" t="inlineStr">
         <is>
           <t>5.20 (кол-во сделок машиноместа)</t>
         </is>
@@ -4355,10 +4645,16 @@
           <t>✅ Актуально</t>
         </is>
       </c>
-      <c r="K61" s="7" t="n">
+      <c r="K61" s="57" t="inlineStr">
+        <is>
+          <t>24.05.2026 23:45</t>
+        </is>
+      </c>
+      <c r="L61" s="57" t="inlineStr"/>
+      <c r="M61" s="7" t="n">
         <v>111</v>
       </c>
-      <c r="L61" s="6" t="inlineStr">
+      <c r="N61" s="6" t="inlineStr">
         <is>
           <t>Банк России (cbr.ru)</t>
         </is>
@@ -4415,10 +4711,16 @@
           <t>✅ Актуально</t>
         </is>
       </c>
-      <c r="K62" s="7" t="n">
+      <c r="K62" s="57" t="inlineStr">
+        <is>
+          <t>24.05.2026 23:45</t>
+        </is>
+      </c>
+      <c r="L62" s="57" t="inlineStr"/>
+      <c r="M62" s="7" t="n">
         <v>111</v>
       </c>
-      <c r="L62" s="6" t="inlineStr">
+      <c r="N62" s="6" t="inlineStr">
         <is>
           <t>Банк России (cbr.ru)</t>
         </is>
@@ -4475,10 +4777,16 @@
           <t>✅ Актуально</t>
         </is>
       </c>
-      <c r="K63" s="7" t="n">
+      <c r="K63" s="57" t="inlineStr">
+        <is>
+          <t>24.05.2026 23:45</t>
+        </is>
+      </c>
+      <c r="L63" s="57" t="inlineStr"/>
+      <c r="M63" s="7" t="n">
         <v>111</v>
       </c>
-      <c r="L63" s="6" t="inlineStr">
+      <c r="N63" s="6" t="inlineStr">
         <is>
           <t>Банк России (cbr.ru)</t>
         </is>
@@ -4535,10 +4843,16 @@
           <t>✅ Актуально</t>
         </is>
       </c>
-      <c r="K64" s="7" t="n">
+      <c r="K64" s="57" t="inlineStr">
+        <is>
+          <t>24.05.2026 23:45</t>
+        </is>
+      </c>
+      <c r="L64" s="57" t="inlineStr"/>
+      <c r="M64" s="7" t="n">
         <v>111</v>
       </c>
-      <c r="L64" s="6" t="inlineStr">
+      <c r="N64" s="6" t="inlineStr">
         <is>
           <t>Банк России (cbr.ru)</t>
         </is>
@@ -4595,10 +4909,16 @@
           <t>✅ Актуально</t>
         </is>
       </c>
-      <c r="K65" s="7" t="n">
+      <c r="K65" s="57" t="inlineStr">
+        <is>
+          <t>24.05.2026 23:45</t>
+        </is>
+      </c>
+      <c r="L65" s="57" t="inlineStr"/>
+      <c r="M65" s="7" t="n">
         <v>111</v>
       </c>
-      <c r="L65" s="6" t="inlineStr">
+      <c r="N65" s="6" t="inlineStr">
         <is>
           <t>Банк России (cbr.ru)</t>
         </is>
@@ -4655,10 +4975,16 @@
           <t>✅ Актуально</t>
         </is>
       </c>
-      <c r="K66" s="7" t="n">
+      <c r="K66" s="57" t="inlineStr">
+        <is>
+          <t>24.05.2026 23:45</t>
+        </is>
+      </c>
+      <c r="L66" s="57" t="inlineStr"/>
+      <c r="M66" s="7" t="n">
         <v>111</v>
       </c>
-      <c r="L66" s="6" t="inlineStr">
+      <c r="N66" s="6" t="inlineStr">
         <is>
           <t>Банк России (cbr.ru)</t>
         </is>
@@ -4715,10 +5041,16 @@
           <t>✅ Актуально</t>
         </is>
       </c>
-      <c r="K67" s="7" t="n">
+      <c r="K67" s="57" t="inlineStr">
+        <is>
+          <t>24.05.2026 23:45</t>
+        </is>
+      </c>
+      <c r="L67" s="57" t="inlineStr"/>
+      <c r="M67" s="7" t="n">
         <v>111</v>
       </c>
-      <c r="L67" s="6" t="inlineStr">
+      <c r="N67" s="6" t="inlineStr">
         <is>
           <t>Банк России (cbr.ru)</t>
         </is>
@@ -4775,10 +5107,16 @@
           <t>✅ Актуально</t>
         </is>
       </c>
-      <c r="K68" s="7" t="n">
+      <c r="K68" s="57" t="inlineStr">
+        <is>
+          <t>24.05.2026 23:45</t>
+        </is>
+      </c>
+      <c r="L68" s="57" t="inlineStr"/>
+      <c r="M68" s="7" t="n">
         <v>111</v>
       </c>
-      <c r="L68" s="6" t="inlineStr">
+      <c r="N68" s="6" t="inlineStr">
         <is>
           <t>Банк России (cbr.ru)</t>
         </is>
@@ -4835,10 +5173,16 @@
           <t>✅ Актуально</t>
         </is>
       </c>
-      <c r="K69" s="7" t="n">
+      <c r="K69" s="57" t="inlineStr">
+        <is>
+          <t>24.05.2026 23:45</t>
+        </is>
+      </c>
+      <c r="L69" s="57" t="inlineStr"/>
+      <c r="M69" s="7" t="n">
         <v>111</v>
       </c>
-      <c r="L69" s="6" t="inlineStr">
+      <c r="N69" s="6" t="inlineStr">
         <is>
           <t>Банк России (cbr.ru)</t>
         </is>
@@ -4895,10 +5239,16 @@
           <t>✅ Актуально</t>
         </is>
       </c>
-      <c r="K70" s="7" t="n">
+      <c r="K70" s="57" t="inlineStr">
+        <is>
+          <t>24.05.2026 23:45</t>
+        </is>
+      </c>
+      <c r="L70" s="57" t="inlineStr"/>
+      <c r="M70" s="7" t="n">
         <v>111</v>
       </c>
-      <c r="L70" s="6" t="inlineStr">
+      <c r="N70" s="6" t="inlineStr">
         <is>
           <t>Банк России (cbr.ru)</t>
         </is>
@@ -4955,10 +5305,16 @@
           <t>✅ Актуально</t>
         </is>
       </c>
-      <c r="K71" s="7" t="n">
+      <c r="K71" s="57" t="inlineStr">
+        <is>
+          <t>24.05.2026 23:45</t>
+        </is>
+      </c>
+      <c r="L71" s="57" t="inlineStr"/>
+      <c r="M71" s="7" t="n">
         <v>111</v>
       </c>
-      <c r="L71" s="6" t="inlineStr">
+      <c r="N71" s="6" t="inlineStr">
         <is>
           <t>Банк России (cbr.ru)</t>
         </is>
@@ -5015,10 +5371,16 @@
           <t>✅ Актуально</t>
         </is>
       </c>
-      <c r="K72" s="7" t="n">
+      <c r="K72" s="57" t="inlineStr">
+        <is>
+          <t>24.05.2026 23:45</t>
+        </is>
+      </c>
+      <c r="L72" s="57" t="inlineStr"/>
+      <c r="M72" s="7" t="n">
         <v>111</v>
       </c>
-      <c r="L72" s="6" t="inlineStr">
+      <c r="N72" s="6" t="inlineStr">
         <is>
           <t>Банк России (cbr.ru)</t>
         </is>
@@ -5075,10 +5437,16 @@
           <t>✅ Актуально</t>
         </is>
       </c>
-      <c r="K73" s="7" t="n">
+      <c r="K73" s="57" t="inlineStr">
+        <is>
+          <t>24.05.2026 23:45</t>
+        </is>
+      </c>
+      <c r="L73" s="57" t="inlineStr"/>
+      <c r="M73" s="7" t="n">
         <v>111</v>
       </c>
-      <c r="L73" s="6" t="inlineStr">
+      <c r="N73" s="6" t="inlineStr">
         <is>
           <t>Банк России (cbr.ru)</t>
         </is>
@@ -5135,10 +5503,16 @@
           <t>✅ Актуально</t>
         </is>
       </c>
-      <c r="K74" s="7" t="n">
+      <c r="K74" s="57" t="inlineStr">
+        <is>
+          <t>24.05.2026 23:45</t>
+        </is>
+      </c>
+      <c r="L74" s="57" t="inlineStr"/>
+      <c r="M74" s="7" t="n">
         <v>111</v>
       </c>
-      <c r="L74" s="6" t="inlineStr">
+      <c r="N74" s="6" t="inlineStr">
         <is>
           <t>Банк России (cbr.ru)</t>
         </is>
@@ -5195,10 +5569,16 @@
           <t>✅ Актуально</t>
         </is>
       </c>
-      <c r="K75" s="7" t="n">
+      <c r="K75" s="57" t="inlineStr">
+        <is>
+          <t>24.05.2026 23:45</t>
+        </is>
+      </c>
+      <c r="L75" s="57" t="inlineStr"/>
+      <c r="M75" s="7" t="n">
         <v>111</v>
       </c>
-      <c r="L75" s="6" t="inlineStr">
+      <c r="N75" s="6" t="inlineStr">
         <is>
           <t>Банк России (cbr.ru)</t>
         </is>
@@ -5255,10 +5635,16 @@
           <t>✅ Актуально</t>
         </is>
       </c>
-      <c r="K76" s="7" t="n">
+      <c r="K76" s="57" t="inlineStr">
+        <is>
+          <t>24.05.2026 23:45</t>
+        </is>
+      </c>
+      <c r="L76" s="57" t="inlineStr"/>
+      <c r="M76" s="7" t="n">
         <v>111</v>
       </c>
-      <c r="L76" s="6" t="inlineStr">
+      <c r="N76" s="6" t="inlineStr">
         <is>
           <t>Банк России (cbr.ru)</t>
         </is>
@@ -5315,10 +5701,16 @@
           <t>✅ Актуально</t>
         </is>
       </c>
-      <c r="K77" s="7" t="n">
+      <c r="K77" s="57" t="inlineStr">
+        <is>
+          <t>24.05.2026 23:45</t>
+        </is>
+      </c>
+      <c r="L77" s="57" t="inlineStr"/>
+      <c r="M77" s="7" t="n">
         <v>111</v>
       </c>
-      <c r="L77" s="6" t="inlineStr">
+      <c r="N77" s="6" t="inlineStr">
         <is>
           <t>Банк России (cbr.ru)</t>
         </is>
@@ -5375,10 +5767,16 @@
           <t>✅ Актуально</t>
         </is>
       </c>
-      <c r="K78" s="7" t="n">
+      <c r="K78" s="57" t="inlineStr">
+        <is>
+          <t>24.05.2026 23:45</t>
+        </is>
+      </c>
+      <c r="L78" s="57" t="inlineStr"/>
+      <c r="M78" s="7" t="n">
         <v>111</v>
       </c>
-      <c r="L78" s="6" t="inlineStr">
+      <c r="N78" s="6" t="inlineStr">
         <is>
           <t>Банк России (cbr.ru)</t>
         </is>
@@ -5435,10 +5833,16 @@
           <t>✅ Актуально</t>
         </is>
       </c>
-      <c r="K79" s="7" t="n">
+      <c r="K79" s="57" t="inlineStr">
+        <is>
+          <t>24.05.2026 23:45</t>
+        </is>
+      </c>
+      <c r="L79" s="57" t="inlineStr"/>
+      <c r="M79" s="7" t="n">
         <v>111</v>
       </c>
-      <c r="L79" s="6" t="inlineStr">
+      <c r="N79" s="6" t="inlineStr">
         <is>
           <t>Банк России (cbr.ru)</t>
         </is>
@@ -5495,10 +5899,16 @@
           <t>✅ Актуально</t>
         </is>
       </c>
-      <c r="K80" s="7" t="n">
+      <c r="K80" s="57" t="inlineStr">
+        <is>
+          <t>24.05.2026 23:45</t>
+        </is>
+      </c>
+      <c r="L80" s="57" t="inlineStr"/>
+      <c r="M80" s="7" t="n">
         <v>111</v>
       </c>
-      <c r="L80" s="6" t="inlineStr">
+      <c r="N80" s="6" t="inlineStr">
         <is>
           <t>Банк России (cbr.ru)</t>
         </is>
@@ -5555,10 +5965,16 @@
           <t>✅ Актуально</t>
         </is>
       </c>
-      <c r="K81" s="7" t="n">
+      <c r="K81" s="57" t="inlineStr">
+        <is>
+          <t>24.05.2026 23:45</t>
+        </is>
+      </c>
+      <c r="L81" s="57" t="inlineStr"/>
+      <c r="M81" s="7" t="n">
         <v>111</v>
       </c>
-      <c r="L81" s="6" t="inlineStr">
+      <c r="N81" s="6" t="inlineStr">
         <is>
           <t>Банк России (cbr.ru)</t>
         </is>
@@ -5615,10 +6031,16 @@
           <t>✅ Актуально</t>
         </is>
       </c>
-      <c r="K82" s="7" t="n">
+      <c r="K82" s="57" t="inlineStr">
+        <is>
+          <t>24.05.2026 23:45</t>
+        </is>
+      </c>
+      <c r="L82" s="57" t="inlineStr"/>
+      <c r="M82" s="7" t="n">
         <v>111</v>
       </c>
-      <c r="L82" s="6" t="inlineStr">
+      <c r="N82" s="6" t="inlineStr">
         <is>
           <t>Банк России (cbr.ru)</t>
         </is>
@@ -5675,10 +6097,16 @@
           <t>✅ Актуально</t>
         </is>
       </c>
-      <c r="K83" s="7" t="n">
+      <c r="K83" s="57" t="inlineStr">
+        <is>
+          <t>24.05.2026 23:45</t>
+        </is>
+      </c>
+      <c r="L83" s="57" t="inlineStr"/>
+      <c r="M83" s="7" t="n">
         <v>111</v>
       </c>
-      <c r="L83" s="6" t="inlineStr">
+      <c r="N83" s="6" t="inlineStr">
         <is>
           <t>Банк России (cbr.ru)</t>
         </is>
@@ -5735,10 +6163,16 @@
           <t>✅ Актуально</t>
         </is>
       </c>
-      <c r="K84" s="7" t="n">
+      <c r="K84" s="57" t="inlineStr">
+        <is>
+          <t>24.05.2026 23:45</t>
+        </is>
+      </c>
+      <c r="L84" s="57" t="inlineStr"/>
+      <c r="M84" s="7" t="n">
         <v>111</v>
       </c>
-      <c r="L84" s="6" t="inlineStr">
+      <c r="N84" s="6" t="inlineStr">
         <is>
           <t>Банк России (cbr.ru)</t>
         </is>
@@ -5795,10 +6229,16 @@
           <t>✅ Актуально</t>
         </is>
       </c>
-      <c r="K85" s="7" t="n">
+      <c r="K85" s="57" t="inlineStr">
+        <is>
+          <t>24.05.2026 23:45</t>
+        </is>
+      </c>
+      <c r="L85" s="57" t="inlineStr"/>
+      <c r="M85" s="7" t="n">
         <v>111</v>
       </c>
-      <c r="L85" s="6" t="inlineStr">
+      <c r="N85" s="6" t="inlineStr">
         <is>
           <t>Банк России (cbr.ru)</t>
         </is>
@@ -5855,10 +6295,16 @@
           <t>✅ Актуально</t>
         </is>
       </c>
-      <c r="K86" s="7" t="n">
+      <c r="K86" s="57" t="inlineStr">
+        <is>
+          <t>24.05.2026 23:45</t>
+        </is>
+      </c>
+      <c r="L86" s="57" t="inlineStr"/>
+      <c r="M86" s="7" t="n">
         <v>111</v>
       </c>
-      <c r="L86" s="6" t="inlineStr">
+      <c r="N86" s="6" t="inlineStr">
         <is>
           <t>Банк России (cbr.ru)</t>
         </is>
@@ -5915,10 +6361,16 @@
           <t>✅ Актуально</t>
         </is>
       </c>
-      <c r="K87" s="7" t="n">
+      <c r="K87" s="57" t="inlineStr">
+        <is>
+          <t>24.05.2026 23:45</t>
+        </is>
+      </c>
+      <c r="L87" s="57" t="inlineStr"/>
+      <c r="M87" s="7" t="n">
         <v>111</v>
       </c>
-      <c r="L87" s="6" t="inlineStr">
+      <c r="N87" s="6" t="inlineStr">
         <is>
           <t>Банк России (cbr.ru)</t>
         </is>
@@ -5975,10 +6427,16 @@
           <t>✅ Актуально</t>
         </is>
       </c>
-      <c r="K88" s="7" t="n">
+      <c r="K88" s="57" t="inlineStr">
+        <is>
+          <t>24.05.2026 23:45</t>
+        </is>
+      </c>
+      <c r="L88" s="57" t="inlineStr"/>
+      <c r="M88" s="7" t="n">
         <v>100</v>
       </c>
-      <c r="L88" s="6" t="inlineStr">
+      <c r="N88" s="6" t="inlineStr">
         <is>
           <t>Банк России (cbr.ru)</t>
         </is>
@@ -6035,10 +6493,16 @@
           <t>✅ Актуально</t>
         </is>
       </c>
-      <c r="K89" s="7" t="n">
+      <c r="K89" s="57" t="inlineStr">
+        <is>
+          <t>24.05.2026 23:45</t>
+        </is>
+      </c>
+      <c r="L89" s="57" t="inlineStr"/>
+      <c r="M89" s="7" t="n">
         <v>100</v>
       </c>
-      <c r="L89" s="6" t="inlineStr">
+      <c r="N89" s="6" t="inlineStr">
         <is>
           <t>Банк России (cbr.ru)</t>
         </is>
@@ -6095,10 +6559,16 @@
           <t>✅ Актуально</t>
         </is>
       </c>
-      <c r="K90" s="7" t="n">
+      <c r="K90" s="57" t="inlineStr">
+        <is>
+          <t>24.05.2026 23:45</t>
+        </is>
+      </c>
+      <c r="L90" s="57" t="inlineStr"/>
+      <c r="M90" s="7" t="n">
         <v>99</v>
       </c>
-      <c r="L90" s="6" t="inlineStr">
+      <c r="N90" s="6" t="inlineStr">
         <is>
           <t>Банк России (cbr.ru)</t>
         </is>
@@ -6155,10 +6625,16 @@
           <t>✅ Актуально</t>
         </is>
       </c>
-      <c r="K91" s="7" t="n">
+      <c r="K91" s="57" t="inlineStr">
+        <is>
+          <t>24.05.2026 23:45</t>
+        </is>
+      </c>
+      <c r="L91" s="57" t="inlineStr"/>
+      <c r="M91" s="7" t="n">
         <v>99</v>
       </c>
-      <c r="L91" s="6" t="inlineStr">
+      <c r="N91" s="6" t="inlineStr">
         <is>
           <t>Банк России (cbr.ru)</t>
         </is>
@@ -6215,10 +6691,16 @@
           <t>✅ Актуально</t>
         </is>
       </c>
-      <c r="K92" s="7" t="n">
+      <c r="K92" s="57" t="inlineStr">
+        <is>
+          <t>24.05.2026 23:45</t>
+        </is>
+      </c>
+      <c r="L92" s="57" t="inlineStr"/>
+      <c r="M92" s="7" t="n">
         <v>100</v>
       </c>
-      <c r="L92" s="6" t="inlineStr">
+      <c r="N92" s="6" t="inlineStr">
         <is>
           <t>Банк России (cbr.ru)</t>
         </is>
@@ -6275,10 +6757,16 @@
           <t>✅ Актуально</t>
         </is>
       </c>
-      <c r="K93" s="7" t="n">
+      <c r="K93" s="57" t="inlineStr">
+        <is>
+          <t>24.05.2026 23:45</t>
+        </is>
+      </c>
+      <c r="L93" s="57" t="inlineStr"/>
+      <c r="M93" s="7" t="n">
         <v>100</v>
       </c>
-      <c r="L93" s="6" t="inlineStr">
+      <c r="N93" s="6" t="inlineStr">
         <is>
           <t>Банк России (cbr.ru)</t>
         </is>
@@ -6335,10 +6823,16 @@
           <t>✅ Актуально</t>
         </is>
       </c>
-      <c r="K94" s="7" t="n">
+      <c r="K94" s="57" t="inlineStr">
+        <is>
+          <t>24.05.2026 23:45</t>
+        </is>
+      </c>
+      <c r="L94" s="57" t="inlineStr"/>
+      <c r="M94" s="7" t="n">
         <v>100</v>
       </c>
-      <c r="L94" s="6" t="inlineStr">
+      <c r="N94" s="6" t="inlineStr">
         <is>
           <t>Банк России (cbr.ru)</t>
         </is>
@@ -6395,10 +6889,16 @@
           <t>✅ Актуально</t>
         </is>
       </c>
-      <c r="K95" s="7" t="n">
+      <c r="K95" s="57" t="inlineStr">
+        <is>
+          <t>24.05.2026 23:45</t>
+        </is>
+      </c>
+      <c r="L95" s="57" t="inlineStr"/>
+      <c r="M95" s="7" t="n">
         <v>100</v>
       </c>
-      <c r="L95" s="6" t="inlineStr">
+      <c r="N95" s="6" t="inlineStr">
         <is>
           <t>Банк России (cbr.ru)</t>
         </is>
@@ -6455,10 +6955,16 @@
           <t>✅ Актуально</t>
         </is>
       </c>
-      <c r="K96" s="7" t="n">
+      <c r="K96" s="57" t="inlineStr">
+        <is>
+          <t>24.05.2026 23:45</t>
+        </is>
+      </c>
+      <c r="L96" s="57" t="inlineStr"/>
+      <c r="M96" s="7" t="n">
         <v>100</v>
       </c>
-      <c r="L96" s="6" t="inlineStr">
+      <c r="N96" s="6" t="inlineStr">
         <is>
           <t>Банк России (cbr.ru)</t>
         </is>
@@ -6515,10 +7021,16 @@
           <t>✅ Актуально</t>
         </is>
       </c>
-      <c r="K97" s="7" t="n">
+      <c r="K97" s="57" t="inlineStr">
+        <is>
+          <t>24.05.2026 23:45</t>
+        </is>
+      </c>
+      <c r="L97" s="57" t="inlineStr"/>
+      <c r="M97" s="7" t="n">
         <v>100</v>
       </c>
-      <c r="L97" s="6" t="inlineStr">
+      <c r="N97" s="6" t="inlineStr">
         <is>
           <t>Банк России (cbr.ru)</t>
         </is>
@@ -6575,10 +7087,16 @@
           <t>✅ Актуально</t>
         </is>
       </c>
-      <c r="K98" s="7" t="n">
+      <c r="K98" s="57" t="inlineStr">
+        <is>
+          <t>24.05.2026 23:45</t>
+        </is>
+      </c>
+      <c r="L98" s="57" t="inlineStr"/>
+      <c r="M98" s="7" t="n">
         <v>27</v>
       </c>
-      <c r="L98" s="6" t="inlineStr">
+      <c r="N98" s="6" t="inlineStr">
         <is>
           <t>Банк России (cbr.ru)</t>
         </is>
@@ -6635,10 +7153,16 @@
           <t>✅ Актуально</t>
         </is>
       </c>
-      <c r="K99" s="7" t="n">
+      <c r="K99" s="57" t="inlineStr">
+        <is>
+          <t>24.05.2026 23:45</t>
+        </is>
+      </c>
+      <c r="L99" s="57" t="inlineStr"/>
+      <c r="M99" s="7" t="n">
         <v>27</v>
       </c>
-      <c r="L99" s="6" t="inlineStr">
+      <c r="N99" s="6" t="inlineStr">
         <is>
           <t>Банк России (cbr.ru)</t>
         </is>
@@ -6695,10 +7219,16 @@
           <t>✅ Актуально</t>
         </is>
       </c>
-      <c r="K100" s="7" t="n">
+      <c r="K100" s="57" t="inlineStr">
+        <is>
+          <t>24.05.2026 23:45</t>
+        </is>
+      </c>
+      <c r="L100" s="57" t="inlineStr"/>
+      <c r="M100" s="7" t="n">
         <v>27</v>
       </c>
-      <c r="L100" s="6" t="inlineStr">
+      <c r="N100" s="6" t="inlineStr">
         <is>
           <t>Банк России (cbr.ru)</t>
         </is>
@@ -6755,10 +7285,16 @@
           <t>✅ Актуально</t>
         </is>
       </c>
-      <c r="K101" s="7" t="n">
+      <c r="K101" s="57" t="inlineStr">
+        <is>
+          <t>24.05.2026 23:45</t>
+        </is>
+      </c>
+      <c r="L101" s="57" t="inlineStr"/>
+      <c r="M101" s="7" t="n">
         <v>27</v>
       </c>
-      <c r="L101" s="6" t="inlineStr">
+      <c r="N101" s="6" t="inlineStr">
         <is>
           <t>Банк России (cbr.ru)</t>
         </is>
@@ -6815,10 +7351,16 @@
           <t>✅ Актуально</t>
         </is>
       </c>
-      <c r="K102" s="7" t="n">
+      <c r="K102" s="57" t="inlineStr">
+        <is>
+          <t>24.05.2026 23:45</t>
+        </is>
+      </c>
+      <c r="L102" s="57" t="inlineStr"/>
+      <c r="M102" s="7" t="n">
         <v>27</v>
       </c>
-      <c r="L102" s="6" t="inlineStr">
+      <c r="N102" s="6" t="inlineStr">
         <is>
           <t>Банк России (cbr.ru)</t>
         </is>
@@ -6875,10 +7417,16 @@
           <t>✅ Актуально</t>
         </is>
       </c>
-      <c r="K103" s="7" t="n">
+      <c r="K103" s="57" t="inlineStr">
+        <is>
+          <t>24.05.2026 23:45</t>
+        </is>
+      </c>
+      <c r="L103" s="57" t="inlineStr"/>
+      <c r="M103" s="7" t="n">
         <v>27</v>
       </c>
-      <c r="L103" s="6" t="inlineStr">
+      <c r="N103" s="6" t="inlineStr">
         <is>
           <t>Банк России (cbr.ru)</t>
         </is>
@@ -6935,10 +7483,16 @@
           <t>✅ Актуально</t>
         </is>
       </c>
-      <c r="K104" s="7" t="n">
+      <c r="K104" s="57" t="inlineStr">
+        <is>
+          <t>24.05.2026 23:45</t>
+        </is>
+      </c>
+      <c r="L104" s="57" t="inlineStr"/>
+      <c r="M104" s="7" t="n">
         <v>27</v>
       </c>
-      <c r="L104" s="6" t="inlineStr">
+      <c r="N104" s="6" t="inlineStr">
         <is>
           <t>Банк России (cbr.ru)</t>
         </is>
@@ -6995,10 +7549,16 @@
           <t>✅ Актуально</t>
         </is>
       </c>
-      <c r="K105" s="7" t="n">
+      <c r="K105" s="57" t="inlineStr">
+        <is>
+          <t>24.05.2026 23:45</t>
+        </is>
+      </c>
+      <c r="L105" s="57" t="inlineStr"/>
+      <c r="M105" s="7" t="n">
         <v>27</v>
       </c>
-      <c r="L105" s="6" t="inlineStr">
+      <c r="N105" s="6" t="inlineStr">
         <is>
           <t>Банк России (cbr.ru)</t>
         </is>
@@ -7055,10 +7615,16 @@
           <t>✅ Актуально</t>
         </is>
       </c>
-      <c r="K106" s="7" t="n">
+      <c r="K106" s="57" t="inlineStr">
+        <is>
+          <t>24.05.2026 23:45</t>
+        </is>
+      </c>
+      <c r="L106" s="57" t="inlineStr"/>
+      <c r="M106" s="7" t="n">
         <v>27</v>
       </c>
-      <c r="L106" s="6" t="inlineStr">
+      <c r="N106" s="6" t="inlineStr">
         <is>
           <t>Банк России (cbr.ru)</t>
         </is>
@@ -7115,10 +7681,16 @@
           <t>✅ Актуально</t>
         </is>
       </c>
-      <c r="K107" s="7" t="n">
+      <c r="K107" s="57" t="inlineStr">
+        <is>
+          <t>24.05.2026 23:45</t>
+        </is>
+      </c>
+      <c r="L107" s="57" t="inlineStr"/>
+      <c r="M107" s="7" t="n">
         <v>27</v>
       </c>
-      <c r="L107" s="6" t="inlineStr">
+      <c r="N107" s="6" t="inlineStr">
         <is>
           <t>Банк России (cbr.ru)</t>
         </is>
@@ -7175,10 +7747,16 @@
           <t>✅ Актуально</t>
         </is>
       </c>
-      <c r="K108" s="7" t="n">
+      <c r="K108" s="57" t="inlineStr">
+        <is>
+          <t>24.05.2026 23:45</t>
+        </is>
+      </c>
+      <c r="L108" s="57" t="inlineStr"/>
+      <c r="M108" s="7" t="n">
         <v>27</v>
       </c>
-      <c r="L108" s="6" t="inlineStr">
+      <c r="N108" s="6" t="inlineStr">
         <is>
           <t>Банк России (cbr.ru)</t>
         </is>
@@ -7235,10 +7813,16 @@
           <t>✅ Актуально</t>
         </is>
       </c>
-      <c r="K109" s="7" t="n">
+      <c r="K109" s="57" t="inlineStr">
+        <is>
+          <t>24.05.2026 23:45</t>
+        </is>
+      </c>
+      <c r="L109" s="57" t="inlineStr"/>
+      <c r="M109" s="7" t="n">
         <v>27</v>
       </c>
-      <c r="L109" s="6" t="inlineStr">
+      <c r="N109" s="6" t="inlineStr">
         <is>
           <t>Банк России (cbr.ru)</t>
         </is>
@@ -7295,10 +7879,16 @@
           <t>✅ Актуально</t>
         </is>
       </c>
-      <c r="K110" s="7" t="n">
+      <c r="K110" s="57" t="inlineStr">
+        <is>
+          <t>24.05.2026 23:45</t>
+        </is>
+      </c>
+      <c r="L110" s="57" t="inlineStr"/>
+      <c r="M110" s="7" t="n">
         <v>27</v>
       </c>
-      <c r="L110" s="6" t="inlineStr">
+      <c r="N110" s="6" t="inlineStr">
         <is>
           <t>Банк России (cbr.ru)</t>
         </is>
@@ -7355,10 +7945,16 @@
           <t>✅ Актуально</t>
         </is>
       </c>
-      <c r="K111" s="7" t="n">
+      <c r="K111" s="57" t="inlineStr">
+        <is>
+          <t>24.05.2026 23:45</t>
+        </is>
+      </c>
+      <c r="L111" s="57" t="inlineStr"/>
+      <c r="M111" s="7" t="n">
         <v>27</v>
       </c>
-      <c r="L111" s="6" t="inlineStr">
+      <c r="N111" s="6" t="inlineStr">
         <is>
           <t>Банк России (cbr.ru)</t>
         </is>
@@ -7415,10 +8011,16 @@
           <t>✅ Актуально</t>
         </is>
       </c>
-      <c r="K112" s="7" t="n">
+      <c r="K112" s="57" t="inlineStr">
+        <is>
+          <t>24.05.2026 23:45</t>
+        </is>
+      </c>
+      <c r="L112" s="57" t="inlineStr"/>
+      <c r="M112" s="7" t="n">
         <v>27</v>
       </c>
-      <c r="L112" s="6" t="inlineStr">
+      <c r="N112" s="6" t="inlineStr">
         <is>
           <t>Банк России (cbr.ru)</t>
         </is>
@@ -7475,10 +8077,16 @@
           <t>✅ Актуально</t>
         </is>
       </c>
-      <c r="K113" s="7" t="n">
+      <c r="K113" s="57" t="inlineStr">
+        <is>
+          <t>24.05.2026 23:45</t>
+        </is>
+      </c>
+      <c r="L113" s="57" t="inlineStr"/>
+      <c r="M113" s="7" t="n">
         <v>27</v>
       </c>
-      <c r="L113" s="6" t="inlineStr">
+      <c r="N113" s="6" t="inlineStr">
         <is>
           <t>Банк России (cbr.ru)</t>
         </is>
@@ -7535,10 +8143,16 @@
           <t>✅ Актуально</t>
         </is>
       </c>
-      <c r="K114" s="7" t="n">
+      <c r="K114" s="57" t="inlineStr">
+        <is>
+          <t>24.05.2026 23:45</t>
+        </is>
+      </c>
+      <c r="L114" s="57" t="inlineStr"/>
+      <c r="M114" s="7" t="n">
         <v>27</v>
       </c>
-      <c r="L114" s="6" t="inlineStr">
+      <c r="N114" s="6" t="inlineStr">
         <is>
           <t>Банк России (cbr.ru)</t>
         </is>
@@ -7595,10 +8209,16 @@
           <t>✅ Актуально</t>
         </is>
       </c>
-      <c r="K115" s="7" t="n">
+      <c r="K115" s="57" t="inlineStr">
+        <is>
+          <t>24.05.2026 23:45</t>
+        </is>
+      </c>
+      <c r="L115" s="57" t="inlineStr"/>
+      <c r="M115" s="7" t="n">
         <v>27</v>
       </c>
-      <c r="L115" s="6" t="inlineStr">
+      <c r="N115" s="6" t="inlineStr">
         <is>
           <t>Банк России (cbr.ru)</t>
         </is>
@@ -7655,10 +8275,16 @@
           <t>✅ Актуально</t>
         </is>
       </c>
-      <c r="K116" s="10" t="n">
+      <c r="K116" s="57" t="inlineStr">
+        <is>
+          <t>25.05.2026 09:11</t>
+        </is>
+      </c>
+      <c r="L116" s="57" t="inlineStr"/>
+      <c r="M116" s="10" t="n">
         <v>52</v>
       </c>
-      <c r="L116" s="9" t="inlineStr">
+      <c r="N116" s="9" t="inlineStr">
         <is>
           <t>Локальные Excel-файлы ДОМ.РФ (migration/domrf_data/)</t>
         </is>
@@ -7715,10 +8341,16 @@
           <t>✅ Актуально</t>
         </is>
       </c>
-      <c r="K117" s="10" t="n">
+      <c r="K117" s="57" t="inlineStr">
+        <is>
+          <t>25.05.2026 09:11</t>
+        </is>
+      </c>
+      <c r="L117" s="57" t="inlineStr"/>
+      <c r="M117" s="10" t="n">
         <v>52</v>
       </c>
-      <c r="L117" s="9" t="inlineStr">
+      <c r="N117" s="9" t="inlineStr">
         <is>
           <t>Локальные Excel-файлы ДОМ.РФ (migration/domrf_data/)</t>
         </is>
@@ -7775,10 +8407,16 @@
           <t>✅ Актуально</t>
         </is>
       </c>
-      <c r="K118" s="10" t="n">
+      <c r="K118" s="57" t="inlineStr">
+        <is>
+          <t>25.05.2026 09:11</t>
+        </is>
+      </c>
+      <c r="L118" s="57" t="inlineStr"/>
+      <c r="M118" s="10" t="n">
         <v>52</v>
       </c>
-      <c r="L118" s="9" t="inlineStr">
+      <c r="N118" s="9" t="inlineStr">
         <is>
           <t>Локальные Excel-файлы ДОМ.РФ (migration/domrf_data/)</t>
         </is>
@@ -7835,10 +8473,16 @@
           <t>✅ Актуально</t>
         </is>
       </c>
-      <c r="K119" s="10" t="n">
+      <c r="K119" s="57" t="inlineStr">
+        <is>
+          <t>25.05.2026 09:11</t>
+        </is>
+      </c>
+      <c r="L119" s="57" t="inlineStr"/>
+      <c r="M119" s="10" t="n">
         <v>52</v>
       </c>
-      <c r="L119" s="9" t="inlineStr">
+      <c r="N119" s="9" t="inlineStr">
         <is>
           <t>Локальные Excel-файлы ДОМ.РФ (migration/domrf_data/)</t>
         </is>
@@ -7895,10 +8539,16 @@
           <t>✅ Актуально</t>
         </is>
       </c>
-      <c r="K120" s="10" t="n">
+      <c r="K120" s="57" t="inlineStr">
+        <is>
+          <t>25.05.2026 09:11</t>
+        </is>
+      </c>
+      <c r="L120" s="57" t="inlineStr"/>
+      <c r="M120" s="10" t="n">
         <v>52</v>
       </c>
-      <c r="L120" s="9" t="inlineStr">
+      <c r="N120" s="9" t="inlineStr">
         <is>
           <t>Локальные Excel-файлы ДОМ.РФ (migration/domrf_data/)</t>
         </is>
@@ -7955,10 +8605,16 @@
           <t>✅ Актуально</t>
         </is>
       </c>
-      <c r="K121" s="10" t="n">
+      <c r="K121" s="57" t="inlineStr">
+        <is>
+          <t>25.05.2026 09:11</t>
+        </is>
+      </c>
+      <c r="L121" s="57" t="inlineStr"/>
+      <c r="M121" s="10" t="n">
         <v>54</v>
       </c>
-      <c r="L121" s="9" t="inlineStr">
+      <c r="N121" s="9" t="inlineStr">
         <is>
           <t>Локальные Excel-файлы ДОМ.РФ (migration/domrf_data/)</t>
         </is>
@@ -8015,10 +8671,16 @@
           <t>✅ Актуально</t>
         </is>
       </c>
-      <c r="K122" s="10" t="n">
+      <c r="K122" s="57" t="inlineStr">
+        <is>
+          <t>25.05.2026 09:11</t>
+        </is>
+      </c>
+      <c r="L122" s="57" t="inlineStr"/>
+      <c r="M122" s="10" t="n">
         <v>54</v>
       </c>
-      <c r="L122" s="9" t="inlineStr">
+      <c r="N122" s="9" t="inlineStr">
         <is>
           <t>Локальные Excel-файлы ДОМ.РФ (migration/domrf_data/)</t>
         </is>
@@ -8075,10 +8737,16 @@
           <t>✅ Актуально</t>
         </is>
       </c>
-      <c r="K123" s="10" t="n">
+      <c r="K123" s="57" t="inlineStr">
+        <is>
+          <t>25.05.2026 09:11</t>
+        </is>
+      </c>
+      <c r="L123" s="57" t="inlineStr"/>
+      <c r="M123" s="10" t="n">
         <v>54</v>
       </c>
-      <c r="L123" s="9" t="inlineStr">
+      <c r="N123" s="9" t="inlineStr">
         <is>
           <t>Локальные Excel-файлы ДОМ.РФ (migration/domrf_data/)</t>
         </is>
@@ -8135,10 +8803,16 @@
           <t>✅ Актуально</t>
         </is>
       </c>
-      <c r="K124" s="10" t="n">
+      <c r="K124" s="57" t="inlineStr">
+        <is>
+          <t>25.05.2026 09:11</t>
+        </is>
+      </c>
+      <c r="L124" s="57" t="inlineStr"/>
+      <c r="M124" s="10" t="n">
         <v>54</v>
       </c>
-      <c r="L124" s="9" t="inlineStr">
+      <c r="N124" s="9" t="inlineStr">
         <is>
           <t>Локальные Excel-файлы ДОМ.РФ (migration/domrf_data/)</t>
         </is>
@@ -8195,10 +8869,16 @@
           <t>✅ Актуально</t>
         </is>
       </c>
-      <c r="K125" s="10" t="n">
+      <c r="K125" s="57" t="inlineStr">
+        <is>
+          <t>25.05.2026 09:11</t>
+        </is>
+      </c>
+      <c r="L125" s="57" t="inlineStr"/>
+      <c r="M125" s="10" t="n">
         <v>54</v>
       </c>
-      <c r="L125" s="9" t="inlineStr">
+      <c r="N125" s="9" t="inlineStr">
         <is>
           <t>Локальные Excel-файлы ДОМ.РФ (migration/domrf_data/)</t>
         </is>
@@ -8255,10 +8935,16 @@
           <t>✅ Актуально</t>
         </is>
       </c>
-      <c r="K126" s="10" t="n">
+      <c r="K126" s="57" t="inlineStr">
+        <is>
+          <t>25.05.2026 09:11</t>
+        </is>
+      </c>
+      <c r="L126" s="57" t="inlineStr"/>
+      <c r="M126" s="10" t="n">
         <v>54</v>
       </c>
-      <c r="L126" s="9" t="inlineStr">
+      <c r="N126" s="9" t="inlineStr">
         <is>
           <t>Локальные Excel-файлы ДОМ.РФ (migration/domrf_data/)</t>
         </is>
@@ -8315,10 +9001,16 @@
           <t>✅ Актуально</t>
         </is>
       </c>
-      <c r="K127" s="10" t="n">
+      <c r="K127" s="57" t="inlineStr">
+        <is>
+          <t>25.05.2026 09:11</t>
+        </is>
+      </c>
+      <c r="L127" s="57" t="inlineStr"/>
+      <c r="M127" s="10" t="n">
         <v>54</v>
       </c>
-      <c r="L127" s="9" t="inlineStr">
+      <c r="N127" s="9" t="inlineStr">
         <is>
           <t>Локальные Excel-файлы ДОМ.РФ (migration/domrf_data/)</t>
         </is>
@@ -8375,10 +9067,16 @@
           <t>✅ Актуально</t>
         </is>
       </c>
-      <c r="K128" s="10" t="n">
+      <c r="K128" s="57" t="inlineStr">
+        <is>
+          <t>25.05.2026 09:11</t>
+        </is>
+      </c>
+      <c r="L128" s="57" t="inlineStr"/>
+      <c r="M128" s="10" t="n">
         <v>54</v>
       </c>
-      <c r="L128" s="9" t="inlineStr">
+      <c r="N128" s="9" t="inlineStr">
         <is>
           <t>Локальные Excel-файлы ДОМ.РФ (migration/domrf_data/)</t>
         </is>
@@ -8435,10 +9133,16 @@
           <t>✅ Актуально</t>
         </is>
       </c>
-      <c r="K129" s="10" t="n">
+      <c r="K129" s="57" t="inlineStr">
+        <is>
+          <t>25.05.2026 09:11</t>
+        </is>
+      </c>
+      <c r="L129" s="57" t="inlineStr"/>
+      <c r="M129" s="10" t="n">
         <v>54</v>
       </c>
-      <c r="L129" s="9" t="inlineStr">
+      <c r="N129" s="9" t="inlineStr">
         <is>
           <t>Локальные Excel-файлы ДОМ.РФ (migration/domrf_data/)</t>
         </is>
@@ -8495,10 +9199,16 @@
           <t>✅ Актуально</t>
         </is>
       </c>
-      <c r="K130" s="10" t="n">
+      <c r="K130" s="57" t="inlineStr">
+        <is>
+          <t>25.05.2026 09:11</t>
+        </is>
+      </c>
+      <c r="L130" s="57" t="inlineStr"/>
+      <c r="M130" s="10" t="n">
         <v>64</v>
       </c>
-      <c r="L130" s="9" t="inlineStr">
+      <c r="N130" s="9" t="inlineStr">
         <is>
           <t>Локальные Excel-файлы ДОМ.РФ (migration/domrf_data/)</t>
         </is>
@@ -8555,10 +9265,16 @@
           <t>✅ Актуально</t>
         </is>
       </c>
-      <c r="K131" s="10" t="n">
+      <c r="K131" s="57" t="inlineStr">
+        <is>
+          <t>25.05.2026 09:11</t>
+        </is>
+      </c>
+      <c r="L131" s="57" t="inlineStr"/>
+      <c r="M131" s="10" t="n">
         <v>64</v>
       </c>
-      <c r="L131" s="9" t="inlineStr">
+      <c r="N131" s="9" t="inlineStr">
         <is>
           <t>Локальные Excel-файлы ДОМ.РФ (migration/domrf_data/)</t>
         </is>
@@ -8615,10 +9331,16 @@
           <t>✅ Актуально</t>
         </is>
       </c>
-      <c r="K132" s="10" t="n">
+      <c r="K132" s="57" t="inlineStr">
+        <is>
+          <t>25.05.2026 09:11</t>
+        </is>
+      </c>
+      <c r="L132" s="57" t="inlineStr"/>
+      <c r="M132" s="10" t="n">
         <v>64</v>
       </c>
-      <c r="L132" s="9" t="inlineStr">
+      <c r="N132" s="9" t="inlineStr">
         <is>
           <t>Локальные Excel-файлы ДОМ.РФ (migration/domrf_data/)</t>
         </is>
@@ -8675,10 +9397,16 @@
           <t>✅ Актуально</t>
         </is>
       </c>
-      <c r="K133" s="10" t="n">
+      <c r="K133" s="57" t="inlineStr">
+        <is>
+          <t>25.05.2026 09:11</t>
+        </is>
+      </c>
+      <c r="L133" s="57" t="inlineStr"/>
+      <c r="M133" s="10" t="n">
         <v>64</v>
       </c>
-      <c r="L133" s="9" t="inlineStr">
+      <c r="N133" s="9" t="inlineStr">
         <is>
           <t>Локальные Excel-файлы ДОМ.РФ (migration/domrf_data/)</t>
         </is>
@@ -8735,10 +9463,16 @@
           <t>✅ Актуально</t>
         </is>
       </c>
-      <c r="K134" s="10" t="n">
+      <c r="K134" s="57" t="inlineStr">
+        <is>
+          <t>25.05.2026 09:11</t>
+        </is>
+      </c>
+      <c r="L134" s="57" t="inlineStr"/>
+      <c r="M134" s="10" t="n">
         <v>64</v>
       </c>
-      <c r="L134" s="9" t="inlineStr">
+      <c r="N134" s="9" t="inlineStr">
         <is>
           <t>Локальные Excel-файлы ДОМ.РФ (migration/domrf_data/)</t>
         </is>
@@ -8795,10 +9529,16 @@
           <t>✅ Актуально</t>
         </is>
       </c>
-      <c r="K135" s="10" t="n">
+      <c r="K135" s="57" t="inlineStr">
+        <is>
+          <t>25.05.2026 09:11</t>
+        </is>
+      </c>
+      <c r="L135" s="57" t="inlineStr"/>
+      <c r="M135" s="10" t="n">
         <v>53</v>
       </c>
-      <c r="L135" s="9" t="inlineStr">
+      <c r="N135" s="9" t="inlineStr">
         <is>
           <t>Локальные Excel-файлы ДОМ.РФ (migration/domrf_data/)</t>
         </is>
@@ -8855,10 +9595,16 @@
           <t>✅ Актуально</t>
         </is>
       </c>
-      <c r="K136" s="10" t="n">
+      <c r="K136" s="57" t="inlineStr">
+        <is>
+          <t>25.05.2026 09:11</t>
+        </is>
+      </c>
+      <c r="L136" s="57" t="inlineStr"/>
+      <c r="M136" s="10" t="n">
         <v>53</v>
       </c>
-      <c r="L136" s="9" t="inlineStr">
+      <c r="N136" s="9" t="inlineStr">
         <is>
           <t>Локальные Excel-файлы ДОМ.РФ (migration/domrf_data/)</t>
         </is>
@@ -8915,10 +9661,16 @@
           <t>✅ Актуально</t>
         </is>
       </c>
-      <c r="K137" s="10" t="n">
+      <c r="K137" s="57" t="inlineStr">
+        <is>
+          <t>25.05.2026 09:11</t>
+        </is>
+      </c>
+      <c r="L137" s="57" t="inlineStr"/>
+      <c r="M137" s="10" t="n">
         <v>54</v>
       </c>
-      <c r="L137" s="9" t="inlineStr">
+      <c r="N137" s="9" t="inlineStr">
         <is>
           <t>Локальные Excel-файлы ДОМ.РФ (migration/domrf_data/)</t>
         </is>
@@ -8975,10 +9727,16 @@
           <t>✅ Актуально</t>
         </is>
       </c>
-      <c r="K138" s="10" t="n">
+      <c r="K138" s="57" t="inlineStr">
+        <is>
+          <t>25.05.2026 09:11</t>
+        </is>
+      </c>
+      <c r="L138" s="57" t="inlineStr"/>
+      <c r="M138" s="10" t="n">
         <v>54</v>
       </c>
-      <c r="L138" s="9" t="inlineStr">
+      <c r="N138" s="9" t="inlineStr">
         <is>
           <t>Локальные Excel-файлы ДОМ.РФ (migration/domrf_data/)</t>
         </is>
@@ -9035,10 +9793,16 @@
           <t>⚠️ Просрочено</t>
         </is>
       </c>
-      <c r="K139" s="10" t="n">
+      <c r="K139" s="57" t="inlineStr"/>
+      <c r="L139" s="57" t="inlineStr">
+        <is>
+          <t>25.05.2026 09:03</t>
+        </is>
+      </c>
+      <c r="M139" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="L139" s="9" t="inlineStr">
+      <c r="N139" s="9" t="inlineStr">
         <is>
           <t>Локальные Excel-файлы ДОМ.РФ (migration/domrf_data/)</t>
         </is>
@@ -9095,10 +9859,16 @@
           <t>✅ Актуально</t>
         </is>
       </c>
-      <c r="K140" s="10" t="n">
+      <c r="K140" s="57" t="inlineStr">
+        <is>
+          <t>25.05.2026 09:11</t>
+        </is>
+      </c>
+      <c r="L140" s="57" t="inlineStr"/>
+      <c r="M140" s="10" t="n">
         <v>30</v>
       </c>
-      <c r="L140" s="9" t="inlineStr">
+      <c r="N140" s="9" t="inlineStr">
         <is>
           <t>Локальные Excel-файлы ДОМ.РФ (migration/domrf_data/)</t>
         </is>
@@ -9155,10 +9925,16 @@
           <t>✅ Актуально</t>
         </is>
       </c>
-      <c r="K141" s="10" t="n">
+      <c r="K141" s="57" t="inlineStr">
+        <is>
+          <t>25.05.2026 09:11</t>
+        </is>
+      </c>
+      <c r="L141" s="57" t="inlineStr"/>
+      <c r="M141" s="10" t="n">
         <v>30</v>
       </c>
-      <c r="L141" s="9" t="inlineStr">
+      <c r="N141" s="9" t="inlineStr">
         <is>
           <t>Локальные Excel-файлы ДОМ.РФ (migration/domrf_data/)</t>
         </is>
@@ -9215,10 +9991,16 @@
           <t>✅ Актуально</t>
         </is>
       </c>
-      <c r="K142" s="10" t="n">
+      <c r="K142" s="57" t="inlineStr">
+        <is>
+          <t>25.05.2026 09:11</t>
+        </is>
+      </c>
+      <c r="L142" s="57" t="inlineStr"/>
+      <c r="M142" s="10" t="n">
         <v>19</v>
       </c>
-      <c r="L142" s="9" t="inlineStr">
+      <c r="N142" s="9" t="inlineStr">
         <is>
           <t>Локальные Excel-файлы ДОМ.РФ (migration/domrf_data/)</t>
         </is>
@@ -9275,10 +10057,16 @@
           <t>✅ Актуально</t>
         </is>
       </c>
-      <c r="K143" s="10" t="n">
+      <c r="K143" s="57" t="inlineStr">
+        <is>
+          <t>25.05.2026 09:11</t>
+        </is>
+      </c>
+      <c r="L143" s="57" t="inlineStr"/>
+      <c r="M143" s="10" t="n">
         <v>19</v>
       </c>
-      <c r="L143" s="9" t="inlineStr">
+      <c r="N143" s="9" t="inlineStr">
         <is>
           <t>Локальные Excel-файлы ДОМ.РФ (migration/domrf_data/)</t>
         </is>
@@ -9335,10 +10123,16 @@
           <t>✅ Актуально</t>
         </is>
       </c>
-      <c r="K144" s="10" t="n">
+      <c r="K144" s="57" t="inlineStr">
+        <is>
+          <t>25.05.2026 09:11</t>
+        </is>
+      </c>
+      <c r="L144" s="57" t="inlineStr"/>
+      <c r="M144" s="10" t="n">
         <v>19</v>
       </c>
-      <c r="L144" s="9" t="inlineStr">
+      <c r="N144" s="9" t="inlineStr">
         <is>
           <t>Локальные Excel-файлы ДОМ.РФ (migration/domrf_data/)</t>
         </is>
@@ -9395,10 +10189,16 @@
           <t>✅ Актуально</t>
         </is>
       </c>
-      <c r="K145" s="10" t="n">
+      <c r="K145" s="57" t="inlineStr">
+        <is>
+          <t>25.05.2026 09:11</t>
+        </is>
+      </c>
+      <c r="L145" s="57" t="inlineStr"/>
+      <c r="M145" s="10" t="n">
         <v>19</v>
       </c>
-      <c r="L145" s="9" t="inlineStr">
+      <c r="N145" s="9" t="inlineStr">
         <is>
           <t>Локальные Excel-файлы ДОМ.РФ (migration/domrf_data/)</t>
         </is>
@@ -9455,10 +10255,16 @@
           <t>✅ Актуально</t>
         </is>
       </c>
-      <c r="K146" s="10" t="n">
+      <c r="K146" s="57" t="inlineStr">
+        <is>
+          <t>25.05.2026 09:11</t>
+        </is>
+      </c>
+      <c r="L146" s="57" t="inlineStr"/>
+      <c r="M146" s="10" t="n">
         <v>54</v>
       </c>
-      <c r="L146" s="9" t="inlineStr">
+      <c r="N146" s="9" t="inlineStr">
         <is>
           <t>Локальные Excel-файлы ДОМ.РФ (migration/domrf_data/)</t>
         </is>
@@ -9515,10 +10321,16 @@
           <t>✅ Актуально</t>
         </is>
       </c>
-      <c r="K147" s="10" t="n">
+      <c r="K147" s="57" t="inlineStr">
+        <is>
+          <t>25.05.2026 09:11</t>
+        </is>
+      </c>
+      <c r="L147" s="57" t="inlineStr"/>
+      <c r="M147" s="10" t="n">
         <v>53</v>
       </c>
-      <c r="L147" s="9" t="inlineStr">
+      <c r="N147" s="9" t="inlineStr">
         <is>
           <t>Локальные Excel-файлы ДОМ.РФ (migration/domrf_data/)</t>
         </is>
@@ -9575,10 +10387,16 @@
           <t>✅ Актуально</t>
         </is>
       </c>
-      <c r="K148" s="10" t="n">
+      <c r="K148" s="57" t="inlineStr">
+        <is>
+          <t>25.05.2026 09:11</t>
+        </is>
+      </c>
+      <c r="L148" s="57" t="inlineStr"/>
+      <c r="M148" s="10" t="n">
         <v>53</v>
       </c>
-      <c r="L148" s="9" t="inlineStr">
+      <c r="N148" s="9" t="inlineStr">
         <is>
           <t>Локальные Excel-файлы ДОМ.РФ (migration/domrf_data/)</t>
         </is>
@@ -9592,6 +10410,8 @@
           <t>ЛЕГЕНДА:</t>
         </is>
       </c>
+      <c r="K151" s="57" t="inlineStr"/>
+      <c r="L151" s="57" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" s="34" t="inlineStr">
@@ -9608,9 +10428,11 @@
       <c r="H152" s="28" t="n"/>
       <c r="I152" s="28" t="n"/>
       <c r="J152" s="28" t="n"/>
-      <c r="K152" s="26" t="n"/>
-      <c r="L152" s="28" t="n"/>
+      <c r="K152" s="57" t="inlineStr"/>
+      <c r="L152" s="57" t="inlineStr"/>
       <c r="M152" s="26" t="n"/>
+      <c r="N152" s="28" t="n"/>
+      <c r="O152" s="26" t="n"/>
     </row>
     <row r="153">
       <c r="A153" s="27" t="inlineStr">
@@ -9627,9 +10449,11 @@
       <c r="H153" s="28" t="n"/>
       <c r="I153" s="28" t="n"/>
       <c r="J153" s="28" t="n"/>
-      <c r="K153" s="26" t="n"/>
-      <c r="L153" s="28" t="n"/>
+      <c r="K153" s="57" t="inlineStr"/>
+      <c r="L153" s="57" t="inlineStr"/>
       <c r="M153" s="26" t="n"/>
+      <c r="N153" s="28" t="n"/>
+      <c r="O153" s="26" t="n"/>
     </row>
     <row r="154">
       <c r="A154" s="32" t="inlineStr">
@@ -9646,9 +10470,11 @@
       <c r="H154" s="28" t="n"/>
       <c r="I154" s="28" t="n"/>
       <c r="J154" s="28" t="n"/>
-      <c r="K154" s="26" t="n"/>
-      <c r="L154" s="28" t="n"/>
+      <c r="K154" s="57" t="inlineStr"/>
+      <c r="L154" s="57" t="inlineStr"/>
       <c r="M154" s="26" t="n"/>
+      <c r="N154" s="28" t="n"/>
+      <c r="O154" s="26" t="n"/>
     </row>
     <row r="155">
       <c r="A155" s="35" t="inlineStr">
@@ -9665,9 +10491,11 @@
       <c r="H155" s="28" t="n"/>
       <c r="I155" s="28" t="n"/>
       <c r="J155" s="28" t="n"/>
-      <c r="K155" s="26" t="n"/>
-      <c r="L155" s="28" t="n"/>
+      <c r="K155" s="57" t="inlineStr"/>
+      <c r="L155" s="57" t="inlineStr"/>
       <c r="M155" s="26" t="n"/>
+      <c r="N155" s="28" t="n"/>
+      <c r="O155" s="26" t="n"/>
     </row>
     <row r="156">
       <c r="A156" s="33" t="inlineStr">
@@ -9684,9 +10512,11 @@
       <c r="H156" s="28" t="n"/>
       <c r="I156" s="28" t="n"/>
       <c r="J156" s="28" t="n"/>
-      <c r="K156" s="26" t="n"/>
-      <c r="L156" s="28" t="n"/>
+      <c r="K156" s="57" t="inlineStr"/>
+      <c r="L156" s="57" t="inlineStr"/>
       <c r="M156" s="26" t="n"/>
+      <c r="N156" s="28" t="n"/>
+      <c r="O156" s="26" t="n"/>
     </row>
     <row r="157">
       <c r="A157" s="31" t="inlineStr">
@@ -9703,9 +10533,11 @@
       <c r="H157" s="28" t="n"/>
       <c r="I157" s="28" t="n"/>
       <c r="J157" s="28" t="n"/>
-      <c r="K157" s="26" t="n"/>
-      <c r="L157" s="28" t="n"/>
+      <c r="K157" s="57" t="inlineStr"/>
+      <c r="L157" s="57" t="inlineStr"/>
       <c r="M157" s="26" t="n"/>
+      <c r="N157" s="28" t="n"/>
+      <c r="O157" s="26" t="n"/>
     </row>
     <row r="158"/>
     <row r="159"/>
@@ -9732,6 +10564,8 @@
           <t>❓ Неизвестно</t>
         </is>
       </c>
+      <c r="K161" s="57" t="inlineStr"/>
+      <c r="L161" s="57" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="8">

--- a/indicator_update_map.xlsx
+++ b/indicator_update_map.xlsx
@@ -241,7 +241,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="58">
+  <cellXfs count="59">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -389,6 +389,9 @@
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -755,20 +758,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O161"/>
+  <dimension ref="A1:N161"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
-    <col width="13.83203125" customWidth="1" style="41" min="1" max="1"/>
+    <col width="10" customWidth="1" style="41" min="1" max="1"/>
     <col width="55" customWidth="1" style="41" min="2" max="2"/>
     <col width="15" customWidth="1" style="41" min="3" max="3"/>
     <col width="14" customWidth="1" style="41" min="4" max="4"/>
     <col width="28" customWidth="1" style="41" min="5" max="5"/>
     <col width="30" customWidth="1" style="41" min="6" max="6"/>
     <col width="28" customWidth="1" style="41" min="7" max="8"/>
+    <col width="14" customWidth="1" style="41" min="8" max="8"/>
     <col width="18" customWidth="1" style="41" min="9" max="9"/>
     <col width="22" customWidth="1" style="41" min="10" max="10"/>
-    <col width="18" customWidth="1" style="41" min="11" max="11"/>
-    <col width="18" customWidth="1" style="41" min="12" max="12"/>
+    <col width="19" customWidth="1" style="41" min="11" max="11"/>
+    <col width="19" customWidth="1" style="41" min="12" max="12"/>
+    <col width="13" customWidth="1" style="41" min="13" max="13"/>
+    <col width="55" customWidth="1" style="41" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1" s="41">
@@ -829,12 +835,12 @@
           <t>Статус</t>
         </is>
       </c>
-      <c r="K2" s="56" t="inlineStr">
+      <c r="K2" s="58" t="inlineStr">
         <is>
           <t>Дата парсера</t>
         </is>
       </c>
-      <c r="L2" s="56" t="inlineStr">
+      <c r="L2" s="58" t="inlineStr">
         <is>
           <t>Дата расчёта</t>
         </is>
@@ -10410,8 +10416,6 @@
           <t>ЛЕГЕНДА:</t>
         </is>
       </c>
-      <c r="K151" s="57" t="inlineStr"/>
-      <c r="L151" s="57" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" s="34" t="inlineStr">
@@ -10428,11 +10432,10 @@
       <c r="H152" s="28" t="n"/>
       <c r="I152" s="28" t="n"/>
       <c r="J152" s="28" t="n"/>
-      <c r="K152" s="57" t="inlineStr"/>
-      <c r="L152" s="57" t="inlineStr"/>
-      <c r="M152" s="26" t="n"/>
-      <c r="N152" s="28" t="n"/>
-      <c r="O152" s="26" t="n"/>
+      <c r="K152" s="28" t="n"/>
+      <c r="L152" s="28" t="n"/>
+      <c r="M152" s="28" t="n"/>
+      <c r="N152" s="26" t="n"/>
     </row>
     <row r="153">
       <c r="A153" s="27" t="inlineStr">
@@ -10449,11 +10452,10 @@
       <c r="H153" s="28" t="n"/>
       <c r="I153" s="28" t="n"/>
       <c r="J153" s="28" t="n"/>
-      <c r="K153" s="57" t="inlineStr"/>
-      <c r="L153" s="57" t="inlineStr"/>
-      <c r="M153" s="26" t="n"/>
-      <c r="N153" s="28" t="n"/>
-      <c r="O153" s="26" t="n"/>
+      <c r="K153" s="28" t="n"/>
+      <c r="L153" s="28" t="n"/>
+      <c r="M153" s="28" t="n"/>
+      <c r="N153" s="26" t="n"/>
     </row>
     <row r="154">
       <c r="A154" s="32" t="inlineStr">
@@ -10470,11 +10472,10 @@
       <c r="H154" s="28" t="n"/>
       <c r="I154" s="28" t="n"/>
       <c r="J154" s="28" t="n"/>
-      <c r="K154" s="57" t="inlineStr"/>
-      <c r="L154" s="57" t="inlineStr"/>
-      <c r="M154" s="26" t="n"/>
-      <c r="N154" s="28" t="n"/>
-      <c r="O154" s="26" t="n"/>
+      <c r="K154" s="28" t="n"/>
+      <c r="L154" s="28" t="n"/>
+      <c r="M154" s="28" t="n"/>
+      <c r="N154" s="26" t="n"/>
     </row>
     <row r="155">
       <c r="A155" s="35" t="inlineStr">
@@ -10491,11 +10492,10 @@
       <c r="H155" s="28" t="n"/>
       <c r="I155" s="28" t="n"/>
       <c r="J155" s="28" t="n"/>
-      <c r="K155" s="57" t="inlineStr"/>
-      <c r="L155" s="57" t="inlineStr"/>
-      <c r="M155" s="26" t="n"/>
-      <c r="N155" s="28" t="n"/>
-      <c r="O155" s="26" t="n"/>
+      <c r="K155" s="28" t="n"/>
+      <c r="L155" s="28" t="n"/>
+      <c r="M155" s="28" t="n"/>
+      <c r="N155" s="26" t="n"/>
     </row>
     <row r="156">
       <c r="A156" s="33" t="inlineStr">
@@ -10512,11 +10512,10 @@
       <c r="H156" s="28" t="n"/>
       <c r="I156" s="28" t="n"/>
       <c r="J156" s="28" t="n"/>
-      <c r="K156" s="57" t="inlineStr"/>
-      <c r="L156" s="57" t="inlineStr"/>
-      <c r="M156" s="26" t="n"/>
-      <c r="N156" s="28" t="n"/>
-      <c r="O156" s="26" t="n"/>
+      <c r="K156" s="28" t="n"/>
+      <c r="L156" s="28" t="n"/>
+      <c r="M156" s="28" t="n"/>
+      <c r="N156" s="26" t="n"/>
     </row>
     <row r="157">
       <c r="A157" s="31" t="inlineStr">
@@ -10533,11 +10532,10 @@
       <c r="H157" s="28" t="n"/>
       <c r="I157" s="28" t="n"/>
       <c r="J157" s="28" t="n"/>
-      <c r="K157" s="57" t="inlineStr"/>
-      <c r="L157" s="57" t="inlineStr"/>
-      <c r="M157" s="26" t="n"/>
-      <c r="N157" s="28" t="n"/>
-      <c r="O157" s="26" t="n"/>
+      <c r="K157" s="28" t="n"/>
+      <c r="L157" s="28" t="n"/>
+      <c r="M157" s="28" t="n"/>
+      <c r="N157" s="26" t="n"/>
     </row>
     <row r="158"/>
     <row r="159"/>
@@ -10569,14 +10567,14 @@
     </row>
   </sheetData>
   <mergeCells count="8">
-    <mergeCell ref="A153:K153"/>
-    <mergeCell ref="A157:K157"/>
-    <mergeCell ref="A154:K154"/>
-    <mergeCell ref="A1:L1"/>
-    <mergeCell ref="A156:K156"/>
-    <mergeCell ref="A152:K152"/>
-    <mergeCell ref="A155:K155"/>
-    <mergeCell ref="A151:K151"/>
+    <mergeCell ref="A154:N154"/>
+    <mergeCell ref="A153:N153"/>
+    <mergeCell ref="A157:N157"/>
+    <mergeCell ref="A156:N156"/>
+    <mergeCell ref="A151:N151"/>
+    <mergeCell ref="A152:N152"/>
+    <mergeCell ref="A155:N155"/>
+    <mergeCell ref="A1:N1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
